--- a/excel/20260805_タイムレコード_01_受入条件表.xlsx
+++ b/excel/20260805_タイムレコード_01_受入条件表.xlsx
@@ -595,6 +595,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -902,6 +903,7 @@
       <c r="H13" s="6" t="n"/>
       <c r="I13" s="6" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
@@ -1077,6 +1079,7 @@
         <v/>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
@@ -1252,6 +1255,7 @@
         <v/>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -4934,7 +4938,7 @@
       </c>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>登録件数が表示され、次にやることが案内される。トップにインポート履歴が残る／成功7・失敗1と表示される。取り込まなかった2行も表示される。失敗行CSVは1行</t>
+          <t>成功7・失敗1と件数が表示される。取り込まなかった2行も表示される。失敗行CSVは1行（件数の食い違い＝0件）。「次にやること」は AC-045、履歴は AC-048 で判定する</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
@@ -5705,7 +5709,7 @@
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t>改善</t>
+          <t>MVP必須</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
@@ -5720,7 +5724,7 @@
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>顧客の既存コード体系を持ち込めない</t>
+          <t>顧客の既存コード体系を持ち込めない。指定コードが無視されると AC-035（退職者と同じ従業員コードはエラー）が成立せず、退職者の復活を止められない。従業員コードは突合キー</t>
         </is>
       </c>
       <c r="I90" s="12" t="inlineStr">
@@ -7206,7 +7210,7 @@
       </c>
       <c r="G111" s="10" t="inlineStr">
         <is>
-          <t>手入力の登録モーダルで登録でき、入力できる項目がCSVテンプレートの列と一致する（差異＝0件）</t>
+          <t>手入力の登録モーダルから登録できる（登録できない種別＝0件）。項目が一致するかは AC-058 で判定する</t>
         </is>
       </c>
       <c r="H111" s="10" t="inlineStr">

--- a/excel/20260805_タイムレコード_01_受入条件表.xlsx
+++ b/excel/20260805_タイムレコード_01_受入条件表.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受入条件表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$28:$Q$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$28:$R$116</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -49,7 +49,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -106,6 +106,11 @@
         <fgColor rgb="00E0E0E0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -133,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -176,6 +181,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -559,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q116"/>
+  <dimension ref="A1:R116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -575,7 +583,7 @@
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
@@ -595,7 +603,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -665,11 +672,11 @@
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A6,$N$29:$N$116,"OK")</f>
+        <f>COUNTIFS($A$29:$A$116,$A6,$O$29:$O$116,"OK")</f>
         <v/>
       </c>
       <c r="G6" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A6,$N$29:$N$116,"NG")</f>
+        <f>COUNTIFS($A$29:$A$116,$A6,$O$29:$O$116,"NG")</f>
         <v/>
       </c>
       <c r="H6" s="6">
@@ -699,11 +706,11 @@
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A7,$N$29:$N$116,"OK")</f>
+        <f>COUNTIFS($A$29:$A$116,$A7,$O$29:$O$116,"OK")</f>
         <v/>
       </c>
       <c r="G7" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A7,$N$29:$N$116,"NG")</f>
+        <f>COUNTIFS($A$29:$A$116,$A7,$O$29:$O$116,"NG")</f>
         <v/>
       </c>
       <c r="H7" s="6">
@@ -733,11 +740,11 @@
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A8,$N$29:$N$116,"OK")</f>
+        <f>COUNTIFS($A$29:$A$116,$A8,$O$29:$O$116,"OK")</f>
         <v/>
       </c>
       <c r="G8" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A8,$N$29:$N$116,"NG")</f>
+        <f>COUNTIFS($A$29:$A$116,$A8,$O$29:$O$116,"NG")</f>
         <v/>
       </c>
       <c r="H8" s="6">
@@ -767,11 +774,11 @@
         <v/>
       </c>
       <c r="F9" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A9,$N$29:$N$116,"OK")</f>
+        <f>COUNTIFS($A$29:$A$116,$A9,$O$29:$O$116,"OK")</f>
         <v/>
       </c>
       <c r="G9" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A9,$N$29:$N$116,"NG")</f>
+        <f>COUNTIFS($A$29:$A$116,$A9,$O$29:$O$116,"NG")</f>
         <v/>
       </c>
       <c r="H9" s="6">
@@ -801,11 +808,11 @@
         <v/>
       </c>
       <c r="F10" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A10,$N$29:$N$116,"OK")</f>
+        <f>COUNTIFS($A$29:$A$116,$A10,$O$29:$O$116,"OK")</f>
         <v/>
       </c>
       <c r="G10" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A10,$N$29:$N$116,"NG")</f>
+        <f>COUNTIFS($A$29:$A$116,$A10,$O$29:$O$116,"NG")</f>
         <v/>
       </c>
       <c r="H10" s="6">
@@ -835,11 +842,11 @@
         <v/>
       </c>
       <c r="F11" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A11,$N$29:$N$116,"OK")</f>
+        <f>COUNTIFS($A$29:$A$116,$A11,$O$29:$O$116,"OK")</f>
         <v/>
       </c>
       <c r="G11" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A11,$N$29:$N$116,"NG")</f>
+        <f>COUNTIFS($A$29:$A$116,$A11,$O$29:$O$116,"NG")</f>
         <v/>
       </c>
       <c r="H11" s="6">
@@ -869,11 +876,11 @@
         <v/>
       </c>
       <c r="F12" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A12,$N$29:$N$116,"OK")</f>
+        <f>COUNTIFS($A$29:$A$116,$A12,$O$29:$O$116,"OK")</f>
         <v/>
       </c>
       <c r="G12" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A12,$N$29:$N$116,"NG")</f>
+        <f>COUNTIFS($A$29:$A$116,$A12,$O$29:$O$116,"NG")</f>
         <v/>
       </c>
       <c r="H12" s="6">
@@ -892,7 +899,7 @@
         </is>
       </c>
       <c r="B13" s="8">
-        <f>IF(COUNTIFS($E$29:$E$116,"MVP必須",$N$29:$N$116,"NG")&gt;0,"MVP未達（MVP必須のNG "&amp;COUNTIFS($E$29:$E$116,"MVP必須",$N$29:$N$116,"NG")&amp;"件）── リリース不可",IF((COUNTIF($E$29:$E$116,"MVP必須")-COUNTIFS($E$29:$E$116,"MVP必須",$N$29:$N$116,"OK")-COUNTIFS($E$29:$E$116,"MVP必須",$N$29:$N$116,"NG"))&gt;0,"判定未完了（MVP必須の残 "&amp;(COUNTIF($E$29:$E$116,"MVP必須")-COUNTIFS($E$29:$E$116,"MVP必須",$N$29:$N$116,"OK")-COUNTIFS($E$29:$E$116,"MVP必須",$N$29:$N$116,"NG"))&amp;"件）",IF(COUNTIFS($E$29:$E$116,"リリース必須",$N$29:$N$116,"NG")&gt;0,"MVP到達。リリース必須にNGあり ── 運用でカバーできるか判断","MVP到達・リリース必須も充足 ── リリース可")))</f>
+        <f>IF(COUNTIFS($E$29:$E$116,"MVP必須",$O$29:$O$116,"NG")&gt;0,"MVP未達（MVP必須のNG "&amp;COUNTIFS($E$29:$E$116,"MVP必須",$O$29:$O$116,"NG")&amp;"件）── リリース不可",IF((COUNTIF($E$29:$E$116,"MVP必須")-COUNTIFS($E$29:$E$116,"MVP必須",$O$29:$O$116,"OK")-COUNTIFS($E$29:$E$116,"MVP必須",$O$29:$O$116,"NG"))&gt;0,"判定未完了（MVP必須の残 "&amp;(COUNTIF($E$29:$E$116,"MVP必須")-COUNTIFS($E$29:$E$116,"MVP必須",$O$29:$O$116,"OK")-COUNTIFS($E$29:$E$116,"MVP必須",$O$29:$O$116,"NG"))&amp;"件）",IF(COUNTIFS($E$29:$E$116,"リリース必須",$O$29:$O$116,"NG")&gt;0,"MVP到達。リリース必須にNGあり ── 運用でカバーできるか判断","MVP到達・リリース必須も充足 ── リリース可")))</f>
         <v/>
       </c>
       <c r="C13" s="6" t="n"/>
@@ -903,7 +910,6 @@
       <c r="H13" s="6" t="n"/>
       <c r="I13" s="6" t="n"/>
     </row>
-    <row r="14"/>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
@@ -961,11 +967,11 @@
         <v/>
       </c>
       <c r="F16" s="6">
-        <f>COUNTIFS($I$29:$I$116,"*1*",$N$29:$N$116,"OK")</f>
+        <f>COUNTIFS($I$29:$I$116,"*1*",$O$29:$O$116,"OK")</f>
         <v/>
       </c>
       <c r="G16" s="6">
-        <f>COUNTIFS($I$29:$I$116,"*1*",$N$29:$N$116,"NG")</f>
+        <f>COUNTIFS($I$29:$I$116,"*1*",$O$29:$O$116,"NG")</f>
         <v/>
       </c>
       <c r="H16" s="6">
@@ -995,11 +1001,11 @@
         <v/>
       </c>
       <c r="F17" s="6">
-        <f>COUNTIFS($I$29:$I$116,"*2*",$N$29:$N$116,"OK")</f>
+        <f>COUNTIFS($I$29:$I$116,"*2*",$O$29:$O$116,"OK")</f>
         <v/>
       </c>
       <c r="G17" s="6">
-        <f>COUNTIFS($I$29:$I$116,"*2*",$N$29:$N$116,"NG")</f>
+        <f>COUNTIFS($I$29:$I$116,"*2*",$O$29:$O$116,"NG")</f>
         <v/>
       </c>
       <c r="H17" s="6">
@@ -1029,11 +1035,11 @@
         <v/>
       </c>
       <c r="F18" s="6">
-        <f>COUNTIFS($I$29:$I$116,"*3*",$N$29:$N$116,"OK")</f>
+        <f>COUNTIFS($I$29:$I$116,"*3*",$O$29:$O$116,"OK")</f>
         <v/>
       </c>
       <c r="G18" s="6">
-        <f>COUNTIFS($I$29:$I$116,"*3*",$N$29:$N$116,"NG")</f>
+        <f>COUNTIFS($I$29:$I$116,"*3*",$O$29:$O$116,"NG")</f>
         <v/>
       </c>
       <c r="H18" s="6">
@@ -1063,11 +1069,11 @@
         <v/>
       </c>
       <c r="F19" s="6">
-        <f>COUNTIFS($I$29:$I$116,"*4*",$N$29:$N$116,"OK")</f>
+        <f>COUNTIFS($I$29:$I$116,"*4*",$O$29:$O$116,"OK")</f>
         <v/>
       </c>
       <c r="G19" s="6">
-        <f>COUNTIFS($I$29:$I$116,"*4*",$N$29:$N$116,"NG")</f>
+        <f>COUNTIFS($I$29:$I$116,"*4*",$O$29:$O$116,"NG")</f>
         <v/>
       </c>
       <c r="H19" s="6">
@@ -1079,7 +1085,6 @@
         <v/>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
@@ -1137,11 +1142,11 @@
         <v/>
       </c>
       <c r="F22" s="6">
-        <f>COUNTIFS($E$29:$E$116,$A22,$N$29:$N$116,"OK")</f>
+        <f>COUNTIFS($E$29:$E$116,$A22,$O$29:$O$116,"OK")</f>
         <v/>
       </c>
       <c r="G22" s="6">
-        <f>COUNTIFS($E$29:$E$116,$A22,$N$29:$N$116,"NG")</f>
+        <f>COUNTIFS($E$29:$E$116,$A22,$O$29:$O$116,"NG")</f>
         <v/>
       </c>
       <c r="H22" s="6">
@@ -1171,11 +1176,11 @@
         <v/>
       </c>
       <c r="F23" s="6">
-        <f>COUNTIFS($E$29:$E$116,$A23,$N$29:$N$116,"OK")</f>
+        <f>COUNTIFS($E$29:$E$116,$A23,$O$29:$O$116,"OK")</f>
         <v/>
       </c>
       <c r="G23" s="6">
-        <f>COUNTIFS($E$29:$E$116,$A23,$N$29:$N$116,"NG")</f>
+        <f>COUNTIFS($E$29:$E$116,$A23,$O$29:$O$116,"NG")</f>
         <v/>
       </c>
       <c r="H23" s="6">
@@ -1205,11 +1210,11 @@
         <v/>
       </c>
       <c r="F24" s="6">
-        <f>COUNTIFS($E$29:$E$116,$A24,$N$29:$N$116,"OK")</f>
+        <f>COUNTIFS($E$29:$E$116,$A24,$O$29:$O$116,"OK")</f>
         <v/>
       </c>
       <c r="G24" s="6">
-        <f>COUNTIFS($E$29:$E$116,$A24,$N$29:$N$116,"NG")</f>
+        <f>COUNTIFS($E$29:$E$116,$A24,$O$29:$O$116,"NG")</f>
         <v/>
       </c>
       <c r="H24" s="6">
@@ -1239,11 +1244,11 @@
         <v/>
       </c>
       <c r="F25" s="6">
-        <f>COUNTIFS($E$29:$E$116,$A25,$N$29:$N$116,"OK")</f>
+        <f>COUNTIFS($E$29:$E$116,$A25,$O$29:$O$116,"OK")</f>
         <v/>
       </c>
       <c r="G25" s="6">
-        <f>COUNTIFS($E$29:$E$116,$A25,$N$29:$N$116,"NG")</f>
+        <f>COUNTIFS($E$29:$E$116,$A25,$O$29:$O$116,"NG")</f>
         <v/>
       </c>
       <c r="H25" s="6">
@@ -1255,7 +1260,6 @@
         <v/>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -1336,20 +1340,25 @@
       </c>
       <c r="N28" s="9" t="inlineStr">
         <is>
+          <t>ヘルプ該当箇所</t>
+        </is>
+      </c>
+      <c r="O28" s="9" t="inlineStr">
+        <is>
           <t>合否</t>
         </is>
       </c>
-      <c r="O28" s="9" t="inlineStr">
+      <c r="P28" s="9" t="inlineStr">
         <is>
           <t>実測値</t>
         </is>
       </c>
-      <c r="P28" s="9" t="inlineStr">
+      <c r="Q28" s="9" t="inlineStr">
         <is>
           <t>判定者</t>
         </is>
       </c>
-      <c r="Q28" s="9" t="inlineStr">
+      <c r="R28" s="9" t="inlineStr">
         <is>
           <t>判定日</t>
         </is>
@@ -1421,10 +1430,15 @@
           <t>OP-101</t>
         </is>
       </c>
-      <c r="N29" s="13" t="inlineStr"/>
+      <c r="N29" s="20" t="inlineStr">
+        <is>
+          <t>6番 テンプレートをダウンロードする（サンプル行 ／ UTF-8で保存）</t>
+        </is>
+      </c>
       <c r="O29" s="13" t="inlineStr"/>
       <c r="P29" s="13" t="inlineStr"/>
       <c r="Q29" s="13" t="inlineStr"/>
+      <c r="R29" s="13" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
@@ -1492,10 +1506,15 @@
           <t>OP-101</t>
         </is>
       </c>
-      <c r="N30" s="13" t="inlineStr"/>
+      <c r="N30" s="20" t="inlineStr">
+        <is>
+          <t>6番 テンプレートをダウンロードする（サンプル行 ／ UTF-8で保存）</t>
+        </is>
+      </c>
       <c r="O30" s="13" t="inlineStr"/>
       <c r="P30" s="13" t="inlineStr"/>
       <c r="Q30" s="13" t="inlineStr"/>
+      <c r="R30" s="13" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
@@ -1563,10 +1582,15 @@
           <t>CA-001 / CA-003 / CA-005 / OP-211 / OP-213</t>
         </is>
       </c>
-      <c r="N31" s="13" t="inlineStr"/>
+      <c r="N31" s="20" t="inlineStr">
+        <is>
+          <t>6番 1回に取り込める量（500行） ／ 6番 1回に取り込める量（200行） ／ 6番 1回に取り込める量（5MB） ／ 6番 1回に取り込める量（500行・200行） ／ 11番 ファイルが受け付けられない場合</t>
+        </is>
+      </c>
       <c r="O31" s="13" t="inlineStr"/>
       <c r="P31" s="13" t="inlineStr"/>
       <c r="Q31" s="13" t="inlineStr"/>
+      <c r="R31" s="13" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
@@ -1634,10 +1658,15 @@
           <t>OP-214 / OP-215 / OP-216</t>
         </is>
       </c>
-      <c r="N32" s="13" t="inlineStr"/>
+      <c r="N32" s="20" t="inlineStr">
+        <is>
+          <t>11番 ファイルが受け付けられない場合（文字コード） ／ 6番 UTF-8で保存 ／ 11番 ファイルが受け付けられない場合（テンプレートの列が一致しません） ／ 11番 ファイルが受け付けられない場合（取り込めるデータが1件もありません）</t>
+        </is>
+      </c>
       <c r="O32" s="13" t="inlineStr"/>
       <c r="P32" s="13" t="inlineStr"/>
       <c r="Q32" s="13" t="inlineStr"/>
+      <c r="R32" s="13" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
@@ -1705,10 +1734,15 @@
           <t>OP-201 / OP-202</t>
         </is>
       </c>
-      <c r="N33" s="13" t="inlineStr"/>
+      <c r="N33" s="20" t="inlineStr">
+        <is>
+          <t>1番 はじめて登録するときの順番 ／ 11番 よくあるエラー</t>
+        </is>
+      </c>
       <c r="O33" s="13" t="inlineStr"/>
       <c r="P33" s="13" t="inlineStr"/>
       <c r="Q33" s="13" t="inlineStr"/>
+      <c r="R33" s="13" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
@@ -1776,10 +1810,15 @@
           <t>OP-620 / CA-003</t>
         </is>
       </c>
-      <c r="N34" s="13" t="inlineStr"/>
+      <c r="N34" s="20" t="inlineStr">
+        <is>
+          <t>3番 はじめて登録する方へ（CSVで一括登録） ／ 10番 招待メールを送る ／ 6番 1回に取り込める量（200行）</t>
+        </is>
+      </c>
       <c r="O34" s="13" t="inlineStr"/>
       <c r="P34" s="13" t="inlineStr"/>
       <c r="Q34" s="13" t="inlineStr"/>
+      <c r="R34" s="13" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
@@ -1847,10 +1886,15 @@
           <t>OP-022</t>
         </is>
       </c>
-      <c r="N35" s="13" t="inlineStr"/>
+      <c r="N35" s="20" t="inlineStr">
+        <is>
+          <t>1番 はじめて登録するときの順番（順番を飛ばすと登録できません）</t>
+        </is>
+      </c>
       <c r="O35" s="13" t="inlineStr"/>
       <c r="P35" s="13" t="inlineStr"/>
       <c r="Q35" s="13" t="inlineStr"/>
+      <c r="R35" s="13" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
@@ -1918,10 +1962,15 @@
           <t>OP-025</t>
         </is>
       </c>
-      <c r="N36" s="13" t="inlineStr"/>
+      <c r="N36" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O36" s="13" t="inlineStr"/>
       <c r="P36" s="13" t="inlineStr"/>
       <c r="Q36" s="13" t="inlineStr"/>
+      <c r="R36" s="13" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
@@ -1989,10 +2038,15 @@
           <t>OP-021</t>
         </is>
       </c>
-      <c r="N37" s="13" t="inlineStr"/>
+      <c r="N37" s="20" t="inlineStr">
+        <is>
+          <t>2番 登録の手順</t>
+        </is>
+      </c>
       <c r="O37" s="13" t="inlineStr"/>
       <c r="P37" s="13" t="inlineStr"/>
       <c r="Q37" s="13" t="inlineStr"/>
+      <c r="R37" s="13" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
@@ -2060,10 +2114,15 @@
           <t>OP-101</t>
         </is>
       </c>
-      <c r="N38" s="13" t="inlineStr"/>
+      <c r="N38" s="20" t="inlineStr">
+        <is>
+          <t>6番 テンプレートをダウンロードする（サンプル行 ／ UTF-8で保存）</t>
+        </is>
+      </c>
       <c r="O38" s="13" t="inlineStr"/>
       <c r="P38" s="13" t="inlineStr"/>
       <c r="Q38" s="13" t="inlineStr"/>
+      <c r="R38" s="13" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
@@ -2131,10 +2190,15 @@
           <t>OP-101</t>
         </is>
       </c>
-      <c r="N39" s="13" t="inlineStr"/>
+      <c r="N39" s="20" t="inlineStr">
+        <is>
+          <t>6番 テンプレートをダウンロードする（サンプル行 ／ UTF-8で保存）</t>
+        </is>
+      </c>
       <c r="O39" s="13" t="inlineStr"/>
       <c r="P39" s="13" t="inlineStr"/>
       <c r="Q39" s="13" t="inlineStr"/>
+      <c r="R39" s="13" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
@@ -2202,10 +2266,15 @@
           <t>OP-008</t>
         </is>
       </c>
-      <c r="N40" s="13" t="inlineStr"/>
+      <c r="N40" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O40" s="13" t="inlineStr"/>
       <c r="P40" s="13" t="inlineStr"/>
       <c r="Q40" s="13" t="inlineStr"/>
+      <c r="R40" s="13" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
@@ -2273,10 +2342,15 @@
           <t>OP-009</t>
         </is>
       </c>
-      <c r="N41" s="13" t="inlineStr"/>
+      <c r="N41" s="20" t="inlineStr">
+        <is>
+          <t>5番 終わったあとは、入ってきた画面に戻ります</t>
+        </is>
+      </c>
       <c r="O41" s="13" t="inlineStr"/>
       <c r="P41" s="13" t="inlineStr"/>
       <c r="Q41" s="13" t="inlineStr"/>
+      <c r="R41" s="13" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
@@ -2344,10 +2418,15 @@
           <t>OP-211</t>
         </is>
       </c>
-      <c r="N42" s="13" t="inlineStr"/>
+      <c r="N42" s="20" t="inlineStr">
+        <is>
+          <t>6番 1回に取り込める量（500行・200行） ／ 11番 ファイルが受け付けられない場合</t>
+        </is>
+      </c>
       <c r="O42" s="13" t="inlineStr"/>
       <c r="P42" s="13" t="inlineStr"/>
       <c r="Q42" s="13" t="inlineStr"/>
+      <c r="R42" s="13" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
@@ -2415,10 +2494,15 @@
           <t>OP-219</t>
         </is>
       </c>
-      <c r="N43" s="13" t="inlineStr"/>
+      <c r="N43" s="20" t="inlineStr">
+        <is>
+          <t>11番 ファイルが受け付けられない場合（直して再アップロード）</t>
+        </is>
+      </c>
       <c r="O43" s="13" t="inlineStr"/>
       <c r="P43" s="13" t="inlineStr"/>
       <c r="Q43" s="13" t="inlineStr"/>
+      <c r="R43" s="13" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
@@ -2486,10 +2570,15 @@
           <t>OP-023</t>
         </is>
       </c>
-      <c r="N44" s="13" t="inlineStr"/>
+      <c r="N44" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O44" s="13" t="inlineStr"/>
       <c r="P44" s="13" t="inlineStr"/>
       <c r="Q44" s="13" t="inlineStr"/>
+      <c r="R44" s="13" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
@@ -2557,10 +2646,15 @@
           <t>OP-024 / OP-029</t>
         </is>
       </c>
-      <c r="N45" s="13" t="inlineStr"/>
+      <c r="N45" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O45" s="13" t="inlineStr"/>
       <c r="P45" s="13" t="inlineStr"/>
       <c r="Q45" s="13" t="inlineStr"/>
+      <c r="R45" s="13" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
@@ -2628,10 +2722,15 @@
           <t>OP-030</t>
         </is>
       </c>
-      <c r="N46" s="13" t="inlineStr"/>
+      <c r="N46" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O46" s="13" t="inlineStr"/>
       <c r="P46" s="13" t="inlineStr"/>
       <c r="Q46" s="13" t="inlineStr"/>
+      <c r="R46" s="13" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
@@ -2699,10 +2798,15 @@
           <t>OP-033</t>
         </is>
       </c>
-      <c r="N47" s="13" t="inlineStr"/>
+      <c r="N47" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O47" s="13" t="inlineStr"/>
       <c r="P47" s="13" t="inlineStr"/>
       <c r="Q47" s="13" t="inlineStr"/>
+      <c r="R47" s="13" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
@@ -2770,10 +2874,15 @@
           <t>OP-008</t>
         </is>
       </c>
-      <c r="N48" s="13" t="inlineStr"/>
+      <c r="N48" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O48" s="13" t="inlineStr"/>
       <c r="P48" s="13" t="inlineStr"/>
       <c r="Q48" s="13" t="inlineStr"/>
+      <c r="R48" s="13" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
@@ -2841,10 +2950,15 @@
           <t>OP-218</t>
         </is>
       </c>
-      <c r="N49" s="13" t="inlineStr"/>
+      <c r="N49" s="20" t="inlineStr">
+        <is>
+          <t>7番 雇用区分（給与体系は月給または時給）</t>
+        </is>
+      </c>
       <c r="O49" s="13" t="inlineStr"/>
       <c r="P49" s="13" t="inlineStr"/>
       <c r="Q49" s="13" t="inlineStr"/>
+      <c r="R49" s="13" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
@@ -2912,10 +3026,15 @@
           <t>CA-051</t>
         </is>
       </c>
-      <c r="N50" s="13" t="inlineStr"/>
+      <c r="N50" s="20" t="inlineStr">
+        <is>
+          <t>8番 画面上部に件数が表示されます（新規登録・更新・スキップ・エラー）</t>
+        </is>
+      </c>
       <c r="O50" s="13" t="inlineStr"/>
       <c r="P50" s="13" t="inlineStr"/>
       <c r="Q50" s="13" t="inlineStr"/>
+      <c r="R50" s="13" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
@@ -2983,10 +3102,15 @@
           <t>OP-303 / OP-304</t>
         </is>
       </c>
-      <c r="N51" s="13" t="inlineStr"/>
+      <c r="N51" s="20" t="inlineStr">
+        <is>
+          <t>11番 一部の行にエラーがある場合（赤く表示・画面上では直せません） ／ 11番 よくあるエラー（〇〇が登録されていません）</t>
+        </is>
+      </c>
       <c r="O51" s="13" t="inlineStr"/>
       <c r="P51" s="13" t="inlineStr"/>
       <c r="Q51" s="13" t="inlineStr"/>
+      <c r="R51" s="13" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
@@ -3054,10 +3178,15 @@
           <t>OP-303</t>
         </is>
       </c>
-      <c r="N52" s="13" t="inlineStr"/>
+      <c r="N52" s="20" t="inlineStr">
+        <is>
+          <t>11番 一部の行にエラーがある場合（赤く表示・画面上では直せません）</t>
+        </is>
+      </c>
       <c r="O52" s="13" t="inlineStr"/>
       <c r="P52" s="13" t="inlineStr"/>
       <c r="Q52" s="13" t="inlineStr"/>
+      <c r="R52" s="13" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
@@ -3125,10 +3254,15 @@
           <t>OP-306 / OP-307 / CA-053</t>
         </is>
       </c>
-      <c r="N53" s="13" t="inlineStr"/>
+      <c r="N53" s="20" t="inlineStr">
+        <is>
+          <t>11番 一部の行にエラーがある場合（エラー行をCSVでダウンロード） ／ 11番 一部の行にエラーがある場合（直し方1〜5） ／ 10番 完了画面で確認する（成功・失敗の件数）</t>
+        </is>
+      </c>
       <c r="O53" s="13" t="inlineStr"/>
       <c r="P53" s="13" t="inlineStr"/>
       <c r="Q53" s="13" t="inlineStr"/>
+      <c r="R53" s="13" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
@@ -3196,10 +3330,15 @@
           <t>OP-308</t>
         </is>
       </c>
-      <c r="N54" s="13" t="inlineStr"/>
+      <c r="N54" s="20" t="inlineStr">
+        <is>
+          <t>8番 管理者の判定について（新規登録・権限付与・差し替え・スキップ）</t>
+        </is>
+      </c>
       <c r="O54" s="13" t="inlineStr"/>
       <c r="P54" s="13" t="inlineStr"/>
       <c r="Q54" s="13" t="inlineStr"/>
+      <c r="R54" s="13" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
@@ -3267,10 +3406,15 @@
           <t>OP-310</t>
         </is>
       </c>
-      <c r="N55" s="13" t="inlineStr"/>
+      <c r="N55" s="20" t="inlineStr">
+        <is>
+          <t>11番 よくあるエラー（退職済みの従業員と同じ従業員コード） ／ 12番 退職した方を復帰させたい</t>
+        </is>
+      </c>
       <c r="O55" s="13" t="inlineStr"/>
       <c r="P55" s="13" t="inlineStr"/>
       <c r="Q55" s="13" t="inlineStr"/>
+      <c r="R55" s="13" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
@@ -3338,10 +3482,15 @@
           <t>CA-016</t>
         </is>
       </c>
-      <c r="N56" s="13" t="inlineStr"/>
+      <c r="N56" s="20" t="inlineStr">
+        <is>
+          <t>7番 雇用区分（金額は1以上） ／ 11番 よくあるエラー</t>
+        </is>
+      </c>
       <c r="O56" s="13" t="inlineStr"/>
       <c r="P56" s="13" t="inlineStr"/>
       <c r="Q56" s="13" t="inlineStr"/>
+      <c r="R56" s="13" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
@@ -3409,10 +3558,15 @@
           <t>CA-031 / CA-033</t>
         </is>
       </c>
-      <c r="N57" s="13" t="inlineStr"/>
+      <c r="N57" s="20" t="inlineStr">
+        <is>
+          <t>7番 従業員 ※未記載。README §11.1 が確定したらヘルプに追記する ／ 7番 雇用区分（最大100文字・コード50文字） ／ 店舗（営業時間200文字）</t>
+        </is>
+      </c>
       <c r="O57" s="13" t="inlineStr"/>
       <c r="P57" s="13" t="inlineStr"/>
       <c r="Q57" s="13" t="inlineStr"/>
+      <c r="R57" s="13" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
@@ -3480,10 +3634,15 @@
           <t>CA-036 / CA-041 / CA-044</t>
         </is>
       </c>
-      <c r="N58" s="13" t="inlineStr"/>
+      <c r="N58" s="20" t="inlineStr">
+        <is>
+          <t>11番 一部の行にエラーがある場合（メールアドレスの形式） ／ 7番 店舗（郵便番号の書き方） ／ 7番 従業員（電話番号はハイフン付き）</t>
+        </is>
+      </c>
       <c r="O58" s="13" t="inlineStr"/>
       <c r="P58" s="13" t="inlineStr"/>
       <c r="Q58" s="13" t="inlineStr"/>
+      <c r="R58" s="13" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
@@ -3551,10 +3710,15 @@
           <t>OP-027</t>
         </is>
       </c>
-      <c r="N59" s="13" t="inlineStr"/>
+      <c r="N59" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O59" s="13" t="inlineStr"/>
       <c r="P59" s="13" t="inlineStr"/>
       <c r="Q59" s="13" t="inlineStr"/>
+      <c r="R59" s="13" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
@@ -3622,10 +3786,15 @@
           <t>OP-026</t>
         </is>
       </c>
-      <c r="N60" s="13" t="inlineStr"/>
+      <c r="N60" s="20" t="inlineStr">
+        <is>
+          <t>1番 はじめて登録するときの順番（先に必要なもの）</t>
+        </is>
+      </c>
       <c r="O60" s="13" t="inlineStr"/>
       <c r="P60" s="13" t="inlineStr"/>
       <c r="Q60" s="13" t="inlineStr"/>
+      <c r="R60" s="13" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
@@ -3693,10 +3862,15 @@
           <t>OP-306 / OP-307 / OP-219</t>
         </is>
       </c>
-      <c r="N61" s="13" t="inlineStr"/>
+      <c r="N61" s="20" t="inlineStr">
+        <is>
+          <t>11番 一部の行にエラーがある場合（エラー行をCSVでダウンロード） ／ 11番 一部の行にエラーがある場合（直し方1〜5） ／ 11番 ファイルが受け付けられない場合（直して再アップロード）</t>
+        </is>
+      </c>
       <c r="O61" s="13" t="inlineStr"/>
       <c r="P61" s="13" t="inlineStr"/>
       <c r="Q61" s="13" t="inlineStr"/>
+      <c r="R61" s="13" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
@@ -3764,10 +3938,15 @@
           <t>OP-108 / CA-056</t>
         </is>
       </c>
-      <c r="N62" s="13" t="inlineStr"/>
+      <c r="N62" s="20" t="inlineStr">
+        <is>
+          <t>7番 業態（同じ業態名は重複を自動で除外） ／ 7番 業態（重複は自動で除外されます）</t>
+        </is>
+      </c>
       <c r="O62" s="13" t="inlineStr"/>
       <c r="P62" s="13" t="inlineStr"/>
       <c r="Q62" s="13" t="inlineStr"/>
+      <c r="R62" s="13" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
@@ -3835,10 +4014,15 @@
           <t>OP-312</t>
         </is>
       </c>
-      <c r="N63" s="13" t="inlineStr"/>
+      <c r="N63" s="20" t="inlineStr">
+        <is>
+          <t>11番 よくあるエラー（〇〇が登録されていません）</t>
+        </is>
+      </c>
       <c r="O63" s="13" t="inlineStr"/>
       <c r="P63" s="13" t="inlineStr"/>
       <c r="Q63" s="13" t="inlineStr"/>
+      <c r="R63" s="13" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
@@ -3906,10 +4090,15 @@
           <t>OP-311 / OP-608</t>
         </is>
       </c>
-      <c r="N64" s="13" t="inlineStr"/>
+      <c r="N64" s="20" t="inlineStr">
+        <is>
+          <t>7番 従業員（店舗名は1店舗のみ） ／ 12番 1人を複数の店舗に所属させたい ／ 12番 1人を複数の店舗に所属させたい（2店舗目以降は従業員一覧から）</t>
+        </is>
+      </c>
       <c r="O64" s="13" t="inlineStr"/>
       <c r="P64" s="13" t="inlineStr"/>
       <c r="Q64" s="13" t="inlineStr"/>
+      <c r="R64" s="13" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
@@ -3977,10 +4166,15 @@
           <t>CA-014 / CA-015</t>
         </is>
       </c>
-      <c r="N65" s="13" t="inlineStr"/>
+      <c r="N65" s="20" t="inlineStr">
+        <is>
+          <t>7番 雇用区分（カンマや円記号を付けても取り込めます） ／ 11番 よくあるエラー（金額は半角数字で）</t>
+        </is>
+      </c>
       <c r="O65" s="13" t="inlineStr"/>
       <c r="P65" s="13" t="inlineStr"/>
       <c r="Q65" s="13" t="inlineStr"/>
+      <c r="R65" s="13" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
@@ -4048,10 +4242,15 @@
           <t>CA-021 / CA-024</t>
         </is>
       </c>
-      <c r="N66" s="13" t="inlineStr"/>
+      <c r="N66" s="20" t="inlineStr">
+        <is>
+          <t>7番 雇用区分（月次契約労働時間1〜999） ／ 11番 よくあるエラー ／ 7番 雇用区分（月みなし残業時間の単位は時間）</t>
+        </is>
+      </c>
       <c r="O66" s="13" t="inlineStr"/>
       <c r="P66" s="13" t="inlineStr"/>
       <c r="Q66" s="13" t="inlineStr"/>
+      <c r="R66" s="13" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
@@ -4119,10 +4318,15 @@
           <t>OP-301</t>
         </is>
       </c>
-      <c r="N67" s="13" t="inlineStr"/>
+      <c r="N67" s="20" t="inlineStr">
+        <is>
+          <t>8番 内容を確認する</t>
+        </is>
+      </c>
       <c r="O67" s="13" t="inlineStr"/>
       <c r="P67" s="13" t="inlineStr"/>
       <c r="Q67" s="13" t="inlineStr"/>
+      <c r="R67" s="13" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
@@ -4190,10 +4394,15 @@
           <t>OP-312</t>
         </is>
       </c>
-      <c r="N68" s="13" t="inlineStr"/>
+      <c r="N68" s="20" t="inlineStr">
+        <is>
+          <t>11番 よくあるエラー（〇〇が登録されていません）</t>
+        </is>
+      </c>
       <c r="O68" s="13" t="inlineStr"/>
       <c r="P68" s="13" t="inlineStr"/>
       <c r="Q68" s="13" t="inlineStr"/>
+      <c r="R68" s="13" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
@@ -4261,10 +4470,15 @@
           <t>OP-308</t>
         </is>
       </c>
-      <c r="N69" s="13" t="inlineStr"/>
+      <c r="N69" s="20" t="inlineStr">
+        <is>
+          <t>8番 管理者の判定について（新規登録・権限付与・差し替え・スキップ）</t>
+        </is>
+      </c>
       <c r="O69" s="13" t="inlineStr"/>
       <c r="P69" s="13" t="inlineStr"/>
       <c r="Q69" s="13" t="inlineStr"/>
+      <c r="R69" s="13" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
@@ -4332,10 +4546,15 @@
           <t>OP-401</t>
         </is>
       </c>
-      <c r="N70" s="13" t="inlineStr"/>
+      <c r="N70" s="20" t="inlineStr">
+        <is>
+          <t>9番 取り込みを実行する</t>
+        </is>
+      </c>
       <c r="O70" s="13" t="inlineStr"/>
       <c r="P70" s="13" t="inlineStr"/>
       <c r="Q70" s="13" t="inlineStr"/>
+      <c r="R70" s="13" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
@@ -4403,10 +4622,15 @@
           <t>OP-502 / CA-053</t>
         </is>
       </c>
-      <c r="N71" s="13" t="inlineStr"/>
+      <c r="N71" s="20" t="inlineStr">
+        <is>
+          <t>10番 確認画面で除いた行 ／ 11番 エラー行を除いてインポート実行 ／ 10番 完了画面で確認する（成功・失敗の件数）</t>
+        </is>
+      </c>
       <c r="O71" s="13" t="inlineStr"/>
       <c r="P71" s="13" t="inlineStr"/>
       <c r="Q71" s="13" t="inlineStr"/>
+      <c r="R71" s="13" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
@@ -4474,10 +4698,15 @@
           <t>OP-503 / CA-053</t>
         </is>
       </c>
-      <c r="N72" s="13" t="inlineStr"/>
+      <c r="N72" s="20" t="inlineStr">
+        <is>
+          <t>10番 一部が登録できなかった場合 ／ 10番 完了画面で確認する（成功・失敗の件数）</t>
+        </is>
+      </c>
       <c r="O72" s="13" t="inlineStr"/>
       <c r="P72" s="13" t="inlineStr"/>
       <c r="Q72" s="13" t="inlineStr"/>
+      <c r="R72" s="13" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
@@ -4545,10 +4774,15 @@
           <t>OP-503</t>
         </is>
       </c>
-      <c r="N73" s="13" t="inlineStr"/>
+      <c r="N73" s="20" t="inlineStr">
+        <is>
+          <t>10番 一部が登録できなかった場合</t>
+        </is>
+      </c>
       <c r="O73" s="13" t="inlineStr"/>
       <c r="P73" s="13" t="inlineStr"/>
       <c r="Q73" s="13" t="inlineStr"/>
+      <c r="R73" s="13" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
@@ -4616,10 +4850,15 @@
           <t>OP-620</t>
         </is>
       </c>
-      <c r="N74" s="13" t="inlineStr"/>
+      <c r="N74" s="20" t="inlineStr">
+        <is>
+          <t>3番 はじめて登録する方へ（CSVで一括登録） ／ 10番 招待メールを送る</t>
+        </is>
+      </c>
       <c r="O74" s="13" t="inlineStr"/>
       <c r="P74" s="13" t="inlineStr"/>
       <c r="Q74" s="13" t="inlineStr"/>
+      <c r="R74" s="13" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
@@ -4687,10 +4926,15 @@
           <t>OP-031</t>
         </is>
       </c>
-      <c r="N75" s="13" t="inlineStr"/>
+      <c r="N75" s="20" t="inlineStr">
+        <is>
+          <t>2番 登録の手順（4種類そろえば打刻を始められます）</t>
+        </is>
+      </c>
       <c r="O75" s="13" t="inlineStr"/>
       <c r="P75" s="13" t="inlineStr"/>
       <c r="Q75" s="13" t="inlineStr"/>
+      <c r="R75" s="13" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
@@ -4758,10 +5002,15 @@
           <t>OP-032</t>
         </is>
       </c>
-      <c r="N76" s="13" t="inlineStr"/>
+      <c r="N76" s="20" t="inlineStr">
+        <is>
+          <t>7番 管理者（同じメールアドレス） ／ 14番 同じ方が2人登録されてしまった</t>
+        </is>
+      </c>
       <c r="O76" s="13" t="inlineStr"/>
       <c r="P76" s="13" t="inlineStr"/>
       <c r="Q76" s="13" t="inlineStr"/>
+      <c r="R76" s="13" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
@@ -4829,10 +5078,15 @@
           <t>OP-401</t>
         </is>
       </c>
-      <c r="N77" s="13" t="inlineStr"/>
+      <c r="N77" s="20" t="inlineStr">
+        <is>
+          <t>9番 取り込みを実行する</t>
+        </is>
+      </c>
       <c r="O77" s="13" t="inlineStr"/>
       <c r="P77" s="13" t="inlineStr"/>
       <c r="Q77" s="13" t="inlineStr"/>
+      <c r="R77" s="13" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
@@ -4900,10 +5154,15 @@
           <t>OP-404 / CA-051</t>
         </is>
       </c>
-      <c r="N78" s="13" t="inlineStr"/>
+      <c r="N78" s="20" t="inlineStr">
+        <is>
+          <t>11番 ファイルが受け付けられない場合（取り込めるデータが1件もありません） ／ 8番 画面上部に件数が表示されます（新規登録・更新・スキップ・エラー）</t>
+        </is>
+      </c>
       <c r="O78" s="13" t="inlineStr"/>
       <c r="P78" s="13" t="inlineStr"/>
       <c r="Q78" s="13" t="inlineStr"/>
+      <c r="R78" s="13" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
@@ -4971,10 +5230,15 @@
           <t>OP-501 / CA-053</t>
         </is>
       </c>
-      <c r="N79" s="13" t="inlineStr"/>
+      <c r="N79" s="20" t="inlineStr">
+        <is>
+          <t>10番 完了画面で確認する ／ 10番 完了画面で確認する（成功・失敗の件数）</t>
+        </is>
+      </c>
       <c r="O79" s="13" t="inlineStr"/>
       <c r="P79" s="13" t="inlineStr"/>
       <c r="Q79" s="13" t="inlineStr"/>
+      <c r="R79" s="13" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
@@ -5042,10 +5306,15 @@
           <t>OP-503</t>
         </is>
       </c>
-      <c r="N80" s="13" t="inlineStr"/>
+      <c r="N80" s="20" t="inlineStr">
+        <is>
+          <t>10番 一部が登録できなかった場合</t>
+        </is>
+      </c>
       <c r="O80" s="13" t="inlineStr"/>
       <c r="P80" s="13" t="inlineStr"/>
       <c r="Q80" s="13" t="inlineStr"/>
+      <c r="R80" s="13" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
@@ -5113,10 +5382,15 @@
           <t>OP-505</t>
         </is>
       </c>
-      <c r="N81" s="13" t="inlineStr"/>
+      <c r="N81" s="20" t="inlineStr">
+        <is>
+          <t>10番 招待メールを送る</t>
+        </is>
+      </c>
       <c r="O81" s="13" t="inlineStr"/>
       <c r="P81" s="13" t="inlineStr"/>
       <c r="Q81" s="13" t="inlineStr"/>
+      <c r="R81" s="13" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
@@ -5184,10 +5458,15 @@
           <t>OP-401</t>
         </is>
       </c>
-      <c r="N82" s="13" t="inlineStr"/>
+      <c r="N82" s="20" t="inlineStr">
+        <is>
+          <t>9番 取り込みを実行する</t>
+        </is>
+      </c>
       <c r="O82" s="13" t="inlineStr"/>
       <c r="P82" s="13" t="inlineStr"/>
       <c r="Q82" s="13" t="inlineStr"/>
+      <c r="R82" s="13" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
@@ -5255,10 +5534,15 @@
           <t>OP-501</t>
         </is>
       </c>
-      <c r="N83" s="13" t="inlineStr"/>
+      <c r="N83" s="20" t="inlineStr">
+        <is>
+          <t>10番 完了画面で確認する</t>
+        </is>
+      </c>
       <c r="O83" s="13" t="inlineStr"/>
       <c r="P83" s="13" t="inlineStr"/>
       <c r="Q83" s="13" t="inlineStr"/>
+      <c r="R83" s="13" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
@@ -5326,10 +5610,15 @@
           <t>OP-501</t>
         </is>
       </c>
-      <c r="N84" s="13" t="inlineStr"/>
+      <c r="N84" s="20" t="inlineStr">
+        <is>
+          <t>10番 完了画面で確認する</t>
+        </is>
+      </c>
       <c r="O84" s="13" t="inlineStr"/>
       <c r="P84" s="13" t="inlineStr"/>
       <c r="Q84" s="13" t="inlineStr"/>
+      <c r="R84" s="13" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
@@ -5397,10 +5686,15 @@
           <t>OP-601 / OP-604 / OP-605 / OP-606</t>
         </is>
       </c>
-      <c r="N85" s="13" t="inlineStr"/>
+      <c r="N85" s="20" t="inlineStr">
+        <is>
+          <t>7番 従業員（列と入力内容） ／ 7番 従業員（従業員コードは空欄で自動採番） ／ 7番 管理者（管理者名・メールアドレス・担当店舗）</t>
+        </is>
+      </c>
       <c r="O85" s="13" t="inlineStr"/>
       <c r="P85" s="13" t="inlineStr"/>
       <c r="Q85" s="13" t="inlineStr"/>
+      <c r="R85" s="13" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
@@ -5468,10 +5762,15 @@
           <t>OP-605 / CA-071</t>
         </is>
       </c>
-      <c r="N86" s="13" t="inlineStr"/>
+      <c r="N86" s="20" t="inlineStr">
+        <is>
+          <t>7番 従業員（従業員コードは空欄で自動採番）</t>
+        </is>
+      </c>
       <c r="O86" s="13" t="inlineStr"/>
       <c r="P86" s="13" t="inlineStr"/>
       <c r="Q86" s="13" t="inlineStr"/>
+      <c r="R86" s="13" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
@@ -5539,10 +5838,15 @@
           <t>OP-607 / CA-061</t>
         </is>
       </c>
-      <c r="N87" s="13" t="inlineStr"/>
+      <c r="N87" s="20" t="inlineStr">
+        <is>
+          <t>7番 管理者（勤務店舗は自動的に維持されます）</t>
+        </is>
+      </c>
       <c r="O87" s="13" t="inlineStr"/>
       <c r="P87" s="13" t="inlineStr"/>
       <c r="Q87" s="13" t="inlineStr"/>
+      <c r="R87" s="13" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
@@ -5610,10 +5914,15 @@
           <t>CA-062</t>
         </is>
       </c>
-      <c r="N88" s="13" t="inlineStr"/>
+      <c r="N88" s="20" t="inlineStr">
+        <is>
+          <t>7番 管理者（担当店舗は半角カンマ区切り）</t>
+        </is>
+      </c>
       <c r="O88" s="13" t="inlineStr"/>
       <c r="P88" s="13" t="inlineStr"/>
       <c r="Q88" s="13" t="inlineStr"/>
+      <c r="R88" s="13" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
@@ -5681,10 +5990,15 @@
           <t>CA-061</t>
         </is>
       </c>
-      <c r="N89" s="13" t="inlineStr"/>
+      <c r="N89" s="20" t="inlineStr">
+        <is>
+          <t>7番 管理者（勤務店舗は自動的に維持されます）</t>
+        </is>
+      </c>
       <c r="O89" s="13" t="inlineStr"/>
       <c r="P89" s="13" t="inlineStr"/>
       <c r="Q89" s="13" t="inlineStr"/>
+      <c r="R89" s="13" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
@@ -5752,10 +6066,15 @@
           <t>CA-071</t>
         </is>
       </c>
-      <c r="N90" s="13" t="inlineStr"/>
+      <c r="N90" s="20" t="inlineStr">
+        <is>
+          <t>7番 従業員（従業員コードは空欄で自動採番）</t>
+        </is>
+      </c>
       <c r="O90" s="13" t="inlineStr"/>
       <c r="P90" s="13" t="inlineStr"/>
       <c r="Q90" s="13" t="inlineStr"/>
+      <c r="R90" s="13" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
@@ -5823,10 +6142,15 @@
           <t>OP-701</t>
         </is>
       </c>
-      <c r="N91" s="13" t="inlineStr"/>
+      <c r="N91" s="20" t="inlineStr">
+        <is>
+          <t>8番 すでに登録されている内容の扱い（スキップ）</t>
+        </is>
+      </c>
       <c r="O91" s="13" t="inlineStr"/>
       <c r="P91" s="13" t="inlineStr"/>
       <c r="Q91" s="13" t="inlineStr"/>
+      <c r="R91" s="13" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
@@ -5894,10 +6218,15 @@
           <t>OP-703</t>
         </is>
       </c>
-      <c r="N92" s="13" t="inlineStr"/>
+      <c r="N92" s="20" t="inlineStr">
+        <is>
+          <t>8番 空欄にした項目は変更されません ／ 12番 入力済みの値を空にしたい</t>
+        </is>
+      </c>
       <c r="O92" s="13" t="inlineStr"/>
       <c r="P92" s="13" t="inlineStr"/>
       <c r="Q92" s="13" t="inlineStr"/>
+      <c r="R92" s="13" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
@@ -5965,10 +6294,15 @@
           <t>OP-704</t>
         </is>
       </c>
-      <c r="N93" s="13" t="inlineStr"/>
+      <c r="N93" s="20" t="inlineStr">
+        <is>
+          <t>8番 管理者の判定について（重複時の処理の設定によらない）</t>
+        </is>
+      </c>
       <c r="O93" s="13" t="inlineStr"/>
       <c r="P93" s="13" t="inlineStr"/>
       <c r="Q93" s="13" t="inlineStr"/>
+      <c r="R93" s="13" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
@@ -6036,10 +6370,15 @@
           <t>OP-709</t>
         </is>
       </c>
-      <c r="N94" s="13" t="inlineStr"/>
+      <c r="N94" s="20" t="inlineStr">
+        <is>
+          <t>3番 途中でやめて、後日続ける（復元される範囲）</t>
+        </is>
+      </c>
       <c r="O94" s="13" t="inlineStr"/>
       <c r="P94" s="13" t="inlineStr"/>
       <c r="Q94" s="13" t="inlineStr"/>
+      <c r="R94" s="13" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
@@ -6107,10 +6446,15 @@
           <t>OP-710</t>
         </is>
       </c>
-      <c r="N95" s="13" t="inlineStr"/>
+      <c r="N95" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O95" s="13" t="inlineStr"/>
       <c r="P95" s="13" t="inlineStr"/>
       <c r="Q95" s="13" t="inlineStr"/>
+      <c r="R95" s="13" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
@@ -6178,10 +6522,15 @@
           <t>OP-702</t>
         </is>
       </c>
-      <c r="N96" s="13" t="inlineStr"/>
+      <c r="N96" s="20" t="inlineStr">
+        <is>
+          <t>8番 すでに登録されている内容の扱い（上書き更新・従業員のみ）</t>
+        </is>
+      </c>
       <c r="O96" s="13" t="inlineStr"/>
       <c r="P96" s="13" t="inlineStr"/>
       <c r="Q96" s="13" t="inlineStr"/>
+      <c r="R96" s="13" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
@@ -6249,10 +6598,15 @@
           <t>OP-705</t>
         </is>
       </c>
-      <c r="N97" s="13" t="inlineStr"/>
+      <c r="N97" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O97" s="13" t="inlineStr"/>
       <c r="P97" s="13" t="inlineStr"/>
       <c r="Q97" s="13" t="inlineStr"/>
+      <c r="R97" s="13" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
@@ -6320,10 +6674,15 @@
           <t>OP-707</t>
         </is>
       </c>
-      <c r="N98" s="13" t="inlineStr"/>
+      <c r="N98" s="20" t="inlineStr">
+        <is>
+          <t>3番 途中でやめて、後日続ける（一時保存して中断・続きから再開）</t>
+        </is>
+      </c>
       <c r="O98" s="13" t="inlineStr"/>
       <c r="P98" s="13" t="inlineStr"/>
       <c r="Q98" s="13" t="inlineStr"/>
+      <c r="R98" s="13" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
@@ -6391,10 +6750,15 @@
           <t>OP-609</t>
         </is>
       </c>
-      <c r="N99" s="13" t="inlineStr"/>
+      <c r="N99" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O99" s="13" t="inlineStr"/>
       <c r="P99" s="13" t="inlineStr"/>
       <c r="Q99" s="13" t="inlineStr"/>
+      <c r="R99" s="13" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
@@ -6462,10 +6826,15 @@
           <t>OP-615</t>
         </is>
       </c>
-      <c r="N100" s="13" t="inlineStr"/>
+      <c r="N100" s="20" t="inlineStr">
+        <is>
+          <t>4番 登録した内容を直す・消す</t>
+        </is>
+      </c>
       <c r="O100" s="13" t="inlineStr"/>
       <c r="P100" s="13" t="inlineStr"/>
       <c r="Q100" s="13" t="inlineStr"/>
+      <c r="R100" s="13" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
@@ -6533,10 +6902,15 @@
           <t>OP-615</t>
         </is>
       </c>
-      <c r="N101" s="13" t="inlineStr"/>
+      <c r="N101" s="20" t="inlineStr">
+        <is>
+          <t>4番 登録した内容を直す・消す</t>
+        </is>
+      </c>
       <c r="O101" s="13" t="inlineStr"/>
       <c r="P101" s="13" t="inlineStr"/>
       <c r="Q101" s="13" t="inlineStr"/>
+      <c r="R101" s="13" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
@@ -6604,10 +6978,15 @@
           <t>OP-801</t>
         </is>
       </c>
-      <c r="N102" s="13" t="inlineStr"/>
+      <c r="N102" s="20" t="inlineStr">
+        <is>
+          <t>13番 権限による違い</t>
+        </is>
+      </c>
       <c r="O102" s="13" t="inlineStr"/>
       <c r="P102" s="13" t="inlineStr"/>
       <c r="Q102" s="13" t="inlineStr"/>
+      <c r="R102" s="13" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
@@ -6675,10 +7054,15 @@
           <t>OP-803</t>
         </is>
       </c>
-      <c r="N103" s="13" t="inlineStr"/>
+      <c r="N103" s="20" t="inlineStr">
+        <is>
+          <t>13番 担当店舗以外の店舗名が入った行はエラーになります</t>
+        </is>
+      </c>
       <c r="O103" s="13" t="inlineStr"/>
       <c r="P103" s="13" t="inlineStr"/>
       <c r="Q103" s="13" t="inlineStr"/>
+      <c r="R103" s="13" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
@@ -6746,10 +7130,15 @@
           <t>OP-028</t>
         </is>
       </c>
-      <c r="N104" s="13" t="inlineStr"/>
+      <c r="N104" s="20" t="inlineStr">
+        <is>
+          <t>4番 登録した内容を直す・消す</t>
+        </is>
+      </c>
       <c r="O104" s="13" t="inlineStr"/>
       <c r="P104" s="13" t="inlineStr"/>
       <c r="Q104" s="13" t="inlineStr"/>
+      <c r="R104" s="13" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
@@ -6817,10 +7206,15 @@
           <t>OP-029</t>
         </is>
       </c>
-      <c r="N105" s="13" t="inlineStr"/>
+      <c r="N105" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O105" s="13" t="inlineStr"/>
       <c r="P105" s="13" t="inlineStr"/>
       <c r="Q105" s="13" t="inlineStr"/>
+      <c r="R105" s="13" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
@@ -6888,10 +7282,15 @@
           <t>OP-612</t>
         </is>
       </c>
-      <c r="N106" s="13" t="inlineStr"/>
+      <c r="N106" s="20" t="inlineStr">
+        <is>
+          <t>4番 入力する項目はCSVテンプレートと同じです</t>
+        </is>
+      </c>
       <c r="O106" s="13" t="inlineStr"/>
       <c r="P106" s="13" t="inlineStr"/>
       <c r="Q106" s="13" t="inlineStr"/>
+      <c r="R106" s="13" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
@@ -6959,10 +7358,15 @@
           <t>OP-617</t>
         </is>
       </c>
-      <c r="N107" s="13" t="inlineStr"/>
+      <c r="N107" s="20" t="inlineStr">
+        <is>
+          <t>12番 登録した内容を削除したい（削除後の再取り込み）</t>
+        </is>
+      </c>
       <c r="O107" s="13" t="inlineStr"/>
       <c r="P107" s="13" t="inlineStr"/>
       <c r="Q107" s="13" t="inlineStr"/>
+      <c r="R107" s="13" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
@@ -7030,10 +7434,15 @@
           <t>OP-009</t>
         </is>
       </c>
-      <c r="N108" s="13" t="inlineStr"/>
+      <c r="N108" s="20" t="inlineStr">
+        <is>
+          <t>5番 終わったあとは、入ってきた画面に戻ります</t>
+        </is>
+      </c>
       <c r="O108" s="13" t="inlineStr"/>
       <c r="P108" s="13" t="inlineStr"/>
       <c r="Q108" s="13" t="inlineStr"/>
+      <c r="R108" s="13" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
@@ -7101,10 +7510,15 @@
           <t>OP-801</t>
         </is>
       </c>
-      <c r="N109" s="13" t="inlineStr"/>
+      <c r="N109" s="20" t="inlineStr">
+        <is>
+          <t>13番 権限による違い</t>
+        </is>
+      </c>
       <c r="O109" s="13" t="inlineStr"/>
       <c r="P109" s="13" t="inlineStr"/>
       <c r="Q109" s="13" t="inlineStr"/>
+      <c r="R109" s="13" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
@@ -7172,10 +7586,15 @@
           <t>OP-804</t>
         </is>
       </c>
-      <c r="N110" s="13" t="inlineStr"/>
+      <c r="N110" s="20" t="inlineStr">
+        <is>
+          <t>13番 権限による違い（従業員は担当店舗のみ）</t>
+        </is>
+      </c>
       <c r="O110" s="13" t="inlineStr"/>
       <c r="P110" s="13" t="inlineStr"/>
       <c r="Q110" s="13" t="inlineStr"/>
+      <c r="R110" s="13" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
@@ -7243,10 +7662,15 @@
           <t>OP-612</t>
         </is>
       </c>
-      <c r="N111" s="13" t="inlineStr"/>
+      <c r="N111" s="20" t="inlineStr">
+        <is>
+          <t>4番 入力する項目はCSVテンプレートと同じです</t>
+        </is>
+      </c>
       <c r="O111" s="13" t="inlineStr"/>
       <c r="P111" s="13" t="inlineStr"/>
       <c r="Q111" s="13" t="inlineStr"/>
+      <c r="R111" s="13" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
@@ -7314,10 +7738,15 @@
           <t>OP-001</t>
         </is>
       </c>
-      <c r="N112" s="13" t="inlineStr"/>
+      <c r="N112" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O112" s="13" t="inlineStr"/>
       <c r="P112" s="13" t="inlineStr"/>
       <c r="Q112" s="13" t="inlineStr"/>
+      <c r="R112" s="13" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
@@ -7385,10 +7814,15 @@
           <t>OP-001</t>
         </is>
       </c>
-      <c r="N113" s="13" t="inlineStr"/>
+      <c r="N113" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O113" s="13" t="inlineStr"/>
       <c r="P113" s="13" t="inlineStr"/>
       <c r="Q113" s="13" t="inlineStr"/>
+      <c r="R113" s="13" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
@@ -7456,10 +7890,15 @@
           <t>OP-007</t>
         </is>
       </c>
-      <c r="N114" s="13" t="inlineStr"/>
+      <c r="N114" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O114" s="13" t="inlineStr"/>
       <c r="P114" s="13" t="inlineStr"/>
       <c r="Q114" s="13" t="inlineStr"/>
+      <c r="R114" s="13" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
@@ -7527,10 +7966,15 @@
           <t>OP-901</t>
         </is>
       </c>
-      <c r="N115" s="13" t="inlineStr"/>
+      <c r="N115" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O115" s="13" t="inlineStr"/>
       <c r="P115" s="13" t="inlineStr"/>
       <c r="Q115" s="13" t="inlineStr"/>
+      <c r="R115" s="13" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
@@ -7598,13 +8042,18 @@
           <t>OP-901</t>
         </is>
       </c>
-      <c r="N116" s="13" t="inlineStr"/>
+      <c r="N116" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O116" s="13" t="inlineStr"/>
       <c r="P116" s="13" t="inlineStr"/>
       <c r="Q116" s="13" t="inlineStr"/>
+      <c r="R116" s="13" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A28:Q116"/>
+  <autoFilter ref="A28:R116"/>
   <conditionalFormatting sqref="N29:N116">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
@@ -7764,7 +8213,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N29:N116" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O29:O116" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/excel/20260805_タイムレコード_01_受入条件表.xlsx
+++ b/excel/20260805_タイムレコード_01_受入条件表.xlsx
@@ -1625,7 +1625,7 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>「文字コードがUTF-8ではない可能性があります」と表示される／「テンプレートの列が一致しません」と表示され、必要な列と見つかった列が併記される／「取り込めるデータがありません」と表示される</t>
+          <t>OP-214（文字コード不正）「文字コードがUTF-8ではない可能性があります」と表示される ／ OP-215（列名不一致）「テンプレートの列が一致しません」と表示され、必要な列と見つかった列が併記される ／ OP-216（データ0件）「取り込めるデータがありません」と表示される</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>元テンプレートと同じ列＋末尾に「エラー理由」列のファイルが落ちる／エラーが解消され、全件が取り込める状態になる／成功7・失敗1と表示される。取り込まなかった2行も表示される。失敗行CSVは1行</t>
+          <t>OP-306（エラー行CSVのダウンロード）元テンプレートと同じ列＋末尾に「エラー理由」列のファイルが落ちる ／ OP-307（エラー行CSVで修正して再取り込み）エラーが解消され、全件が取り込める状態になる ／ CA-053（完了画面の件数）成功7・失敗1と表示される。取り込まなかった2行も表示される。失敗行CSVは1行</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>100文字は登録できる。101文字はエラー／いずれもエラーになり、列名と上限がメッセージに出る</t>
+          <t>CA-031（従業員名の桁数）100文字は登録できる。101文字はエラー ／ CA-033（その他の桁数）いずれもエラーになり、列名と上限がメッセージに出る</t>
         </is>
       </c>
       <c r="H57" s="10" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>エラー行として赤く表示され、「メールアドレスの形式が正しくありません」と理由が出る。取り込まれない／前2つは登録できる。3つ目はエラー／全角ハイフンは半角に正規化される。英字混じりはエラー</t>
+          <t>CA-036（メールアドレスの形式）エラー行として赤く表示され、「メールアドレスの形式が正しくありません」と理由が出る。取り込まれない ／ CA-041（郵便番号の形式）前2つは登録できる。3つ目はエラー ／ CA-044（電話番号の正規化と文字種）全角ハイフンは半角に正規化される。英字混じりはエラー</t>
         </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>重複が自動で除外され、1件として登録される／3件として登録される</t>
+          <t>OP-108（設定マスタの重複排除）重複が自動で除外され、1件として登録される ／ CA-056（重複排除後の件数）3件として登録される</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>どちらも 200000 として登録される／エラー。「金額は半角数字で入力してください」</t>
+          <t>CA-014（金額の正規化）どちらも 200000 として登録される ／ CA-015（金額の正規化（不可））エラー。「金額は半角数字で入力してください」</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>0と1000はエラー。160は登録できる／0と999は登録できる。1000はエラー。「20時間」は単位付きのためエラー</t>
+          <t>CA-021（月次契約労働時間の範囲）0と1000はエラー。160は登録できる ／ CA-024（月みなし残業時間の範囲）0と999は登録できる。1000はエラー。「20時間」は単位付きのためエラー</t>
         </is>
       </c>
       <c r="H66" s="10" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>完了画面に「取り込まなかった行（N件）」が表示され、除外理由が分かる／成功7・失敗1と表示される。取り込まなかった2行も表示される。失敗行CSVは1行</t>
+          <t>OP-502（取り込まなかった行の開示）完了画面に「取り込まなかった行（N件）」が表示され、除外理由が分かる ／ CA-053（完了画面の件数）成功7・失敗1と表示される。取り込まなかった2行も表示される。失敗行CSVは1行</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>失敗した行だけが落ちる。文字化けせず、失敗理由の列が付いている／成功7・失敗1と表示される。取り込まなかった2行も表示される。失敗行CSVは1行</t>
+          <t>OP-503（失敗行CSVのダウンロードと書式）失敗した行だけが落ちる。文字化けせず、失敗理由の列が付いている ／ CA-053（完了画面の件数）成功7・失敗1と表示される。取り込まなかった2行も表示される。失敗行CSVは1行</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>実行ボタンが押せない状態になり「取り込めるデータが1件もありません」と表示される／新規6・更新2・エラー2と表示され、実行ボタンは「8件をインポート」と出る</t>
+          <t>OP-404（取り込み対象0件）実行ボタンが押せない状態になり「取り込めるデータが1件もありません」と表示される ／ CA-051（プレビューの件数集計）新規6・更新2・エラー2と表示され、実行ボタンは「8件をインポート」と出る</t>
         </is>
       </c>
       <c r="H78" s="10" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>元の2店舗の所属が維持されている／どちらも2店舗のまま。消えず、重複もしない</t>
+          <t>OP-607（昇格時の勤務店舗維持）元の2店舗の所属が維持されている ／ CA-061（担当店舗のマージ）どちらも2店舗のまま。消えず、重複もしない</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">

--- a/excel/20260805_タイムレコード_01_受入条件表.xlsx
+++ b/excel/20260805_タイムレコード_01_受入条件表.xlsx
@@ -1402,7 +1402,13 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>**テンプレートが文字化けし、そもそも入力できない**</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>テンプレートが文字化けし、そもそも入力できない</t>
+          </r>
         </is>
       </c>
       <c r="I29" s="12" t="inlineStr">
@@ -1478,7 +1484,19 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>**サンプルのコードが他社と衝突する。** 全社横断でユニークなため</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>サンプルのコードが他社と衝突する。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 全社横断でユニークなため</t>
+          </r>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr">
@@ -1554,7 +1572,13 @@
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>**上限超過のまま処理が走り、タイムアウトや部分登録が起きる**</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>上限超過のまま処理が走り、タイムアウトや部分登録が起きる</t>
+          </r>
         </is>
       </c>
       <c r="I31" s="12" t="inlineStr">
@@ -1630,7 +1654,13 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>**壊れたファイルがプレビューまで進み、意味不明なエラーが大量に出る**</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>壊れたファイルがプレビューまで進み、意味不明なエラーが大量に出る</t>
+          </r>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
@@ -1706,7 +1736,19 @@
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>**参照先が未登録で全行エラーになる。** 顧客は原因が分からない</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>参照先が未登録で全行エラーになる。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 顧客は原因が分からない</t>
+          </r>
         </is>
       </c>
       <c r="I33" s="12" t="inlineStr">
@@ -1782,7 +1824,19 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>**分割が必要だと1件ずつ入力するのと手間が変わらず、機能の価値が消える。** 上限が実運用の規模に足りているかの確認</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>分割が必要だと1件ずつ入力するのと手間が変わらず、機能の価値が消える。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 上限が実運用の規模に足りているかの確認</t>
+          </r>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
@@ -1858,7 +1912,19 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>**参照先が無い状態で登録され、データが繋がらない。** インポートの順序依存と同じ問題</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>参照先が無い状態で登録され、データが繋がらない。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> インポートの順序依存と同じ問題</t>
+          </r>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
@@ -1934,7 +2000,19 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>**運用開始後も初期セットアップ画面が出続ける。** 順序ガードが残り、追加登録ができない</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>運用開始後も初期セットアップ画面が出続ける。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 順序ガードが残り、追加登録ができない</t>
+          </r>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
@@ -2010,7 +2088,19 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>**セルフスタートの入口が動かない。** CSVインポートも同じ画面から入るため全体が止まる</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>セルフスタートの入口が動かない。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> CSVインポートも同じ画面から入るため全体が止まる</t>
+          </r>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
@@ -2238,7 +2328,19 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>設定画面のリンクを踏んでも方式選択が再度出る。**パラメータ名が2つの仕様で食い違っている（要確定）**</t>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>設定画面のリンクを踏んでも方式選択が再度出る。</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>パラメータ名が2つの仕様で食い違っている（要確定）</t>
+          </r>
         </is>
       </c>
       <c r="I40" s="16" t="inlineStr">
@@ -2922,7 +3024,19 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>**DB制約違反で登録が落ちる。** enumは時給・月給の2値</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DB制約違反で登録が落ちる。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> enumは時給・月給の2値</t>
+          </r>
         </is>
       </c>
       <c r="I49" s="12" t="inlineStr">
@@ -2998,7 +3112,19 @@
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>**何が登録されるか分からないまま実行させることになる。** プレビューがこの機能の要</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>何が登録されるか分からないまま実行させることになる。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> プレビューがこの機能の要</t>
+          </r>
         </is>
       </c>
       <c r="I50" s="12" t="inlineStr">
@@ -3074,7 +3200,13 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>**なぜ取り込めないのか分からず、顧客が問い合わせる**</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>なぜ取り込めないのか分からず、顧客が問い合わせる</t>
+          </r>
         </is>
       </c>
       <c r="I51" s="12" t="inlineStr">
@@ -3150,7 +3282,19 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>**画面で直すと元CSVに残らず再発する。** プレビューが編集画面になり状態管理が跳ね上がる（J-029）</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>画面で直すと元CSVに残らず再発する。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> プレビューが編集画面になり状態管理が跳ね上がる（J-029）</t>
+          </r>
         </is>
       </c>
       <c r="I52" s="12" t="inlineStr">
@@ -3170,7 +3314,19 @@
       </c>
       <c r="L52" s="10" t="inlineStr">
         <is>
-          <t>**設計の背骨①**／仕様書 4.1</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>設計の背骨①</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>／仕様書 4.1</t>
+          </r>
         </is>
       </c>
       <c r="M52" s="10" t="inlineStr">
@@ -3226,7 +3382,19 @@
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>**エラー行を直す手段が無くなる。** 30人中1人の誤りで全体が止まる</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>エラー行を直す手段が無くなる。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 30人中1人の誤りで全体が止まる</t>
+          </r>
         </is>
       </c>
       <c r="I53" s="12" t="inlineStr">
@@ -3302,7 +3470,19 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>**店長のアカウントが2つできる。** 打刻の記録が分断され、給与計算が合わなくなる</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>店長のアカウントが2つできる。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 打刻の記録が分断され、給与計算が合わなくなる</t>
+          </r>
         </is>
       </c>
       <c r="I54" s="12" t="inlineStr">
@@ -3322,7 +3502,19 @@
       </c>
       <c r="L54" s="10" t="inlineStr">
         <is>
-          <t>**設計の背骨④**／フローD</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>設計の背骨④</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>／フローD</t>
+          </r>
         </is>
       </c>
       <c r="M54" s="10" t="inlineStr">
@@ -3378,7 +3570,19 @@
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>**退職者が勝手に復活する。** 給与計算と打刻に退職者が混ざる</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>退職者が勝手に復活する。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 給与計算と打刻に退職者が混ざる</t>
+          </r>
         </is>
       </c>
       <c r="I55" s="12" t="inlineStr">
@@ -3454,7 +3658,19 @@
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>**0円や桁溢れがDBに入る。** 給与計算が壊れる</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>0円や桁溢れがDBに入る。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 給与計算が壊れる</t>
+          </r>
         </is>
       </c>
       <c r="I56" s="12" t="inlineStr">
@@ -3530,7 +3746,19 @@
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>**DBの桁を超えて登録に失敗する。** どの行かも分からない</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DBの桁を超えて登録に失敗する。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> どの行かも分からない</t>
+          </r>
         </is>
       </c>
       <c r="I57" s="12" t="inlineStr">
@@ -3606,7 +3834,19 @@
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>**誤ったメールアドレスに招待が飛ぶ。** 本人はログインできない</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>誤ったメールアドレスに招待が飛ぶ。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 本人はログインできない</t>
+          </r>
         </is>
       </c>
       <c r="I58" s="12" t="inlineStr">
@@ -3682,7 +3922,19 @@
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>**編集で開いたのに前回の入力が残る、または新規で開いたのに既存が出る。** 誤ったデータを上書きする</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>編集で開いたのに前回の入力が残る、または新規で開いたのに既存が出る。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 誤ったデータを上書きする</t>
+          </r>
         </is>
       </c>
       <c r="I59" s="14" t="inlineStr">
@@ -3758,7 +4010,19 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>**未登録の業態や店舗を選べてしまい、存在しない参照ができる。** または登録したのに選べない</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>未登録の業態や店舗を選べてしまい、存在しない参照ができる。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> または登録したのに選べない</t>
+          </r>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
@@ -3834,7 +4098,19 @@
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>**導入作業の途中で誤りに気づいても直せない。** 最初からやり直しになり、導入で離脱する</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>導入作業の途中で誤りに気づいても直せない。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 最初からやり直しになり、導入で離脱する</t>
+          </r>
         </is>
       </c>
       <c r="I61" s="12" t="inlineStr">
@@ -4518,7 +4794,19 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>**二重登録される。** 取り返しがつかない</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>二重登録される。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 取り返しがつかない</t>
+          </r>
         </is>
       </c>
       <c r="I70" s="12" t="inlineStr">
@@ -4594,7 +4882,19 @@
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>**除外した行を忘れる。** 登録されたつもりで運用が始まる</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>除外した行を忘れる。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 登録されたつもりで運用が始まる</t>
+          </r>
         </is>
       </c>
       <c r="I71" s="12" t="inlineStr">
@@ -4670,7 +4970,19 @@
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>**失敗した行が分からず回収できない。** どれが登録されたか顧客が追えない</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>失敗した行が分からず回収できない。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> どれが登録されたか顧客が追えない</t>
+          </r>
         </is>
       </c>
       <c r="I72" s="12" t="inlineStr">
@@ -4746,7 +5058,19 @@
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>**中途半端なレコードがDBに残る。** 招待も届かず、再取り込みもできない幽霊データになる</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>中途半端なレコードがDBに残る。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 招待も届かず、再取り込みもできない幽霊データになる</t>
+          </r>
         </is>
       </c>
       <c r="I73" s="12" t="inlineStr">
@@ -4766,7 +5090,19 @@
       </c>
       <c r="L73" s="10" t="inlineStr">
         <is>
-          <t>**設計の背骨②**／README §7.7</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>設計の背骨②</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>／README §7.7</t>
+          </r>
         </is>
       </c>
       <c r="M73" s="10" t="inlineStr">
@@ -4822,7 +5158,19 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>**個々の条件が合格でも、通しで完了しなければこの機能の価値が出ない。** 導入の障壁を下げるための機能であり、途中で止まれば意味がない</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>個々の条件が合格でも、通しで完了しなければこの機能の価値が出ない。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 導入の障壁を下げるための機能であり、途中で止まれば意味がない</t>
+          </r>
         </is>
       </c>
       <c r="I74" s="12" t="inlineStr">
@@ -4898,7 +5246,19 @@
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>**CSVを使わない顧客がセルフスタートできない。** 導入の障壁を下げる機能として成立しない</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>CSVを使わない顧客がセルフスタートできない。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 導入の障壁を下げる機能として成立しない</t>
+          </r>
         </is>
       </c>
       <c r="I75" s="14" t="inlineStr">
@@ -4974,7 +5334,19 @@
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>**同じ人に2通の招待が届き、パスワード設定URLが2つできる。** 利用者が混乱し、アカウントが分裂する</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>同じ人に2通の招待が届き、パスワード設定URLが2つできる。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 利用者が混乱し、アカウントが分裂する</t>
+          </r>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
@@ -5658,7 +6030,13 @@
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>**列が取りこぼされ、登録したはずの情報が入っていない**</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>列が取りこぼされ、登録したはずの情報が入っていない</t>
+          </r>
         </is>
       </c>
       <c r="I85" s="12" t="inlineStr">
@@ -5734,7 +6112,19 @@
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>**コードが重複してDB制約違反になる。** 全社横断でユニーク</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>コードが重複してDB制約違反になる。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 全社横断でユニーク</t>
+          </r>
         </is>
       </c>
       <c r="I86" s="12" t="inlineStr">
@@ -5810,7 +6200,19 @@
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>**昇格した店長が打刻できなくなる。** 勤務店舗が消えると出退勤が記録できない</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>昇格した店長が打刻できなくなる。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 勤務店舗が消えると出退勤が記録できない</t>
+          </r>
         </is>
       </c>
       <c r="I87" s="12" t="inlineStr">
@@ -5830,7 +6232,19 @@
       </c>
       <c r="L87" s="10" t="inlineStr">
         <is>
-          <t>**設計の背骨⑤**／フローD／README §7.1</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>設計の背骨⑤</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>／フローD／README §7.1</t>
+          </r>
         </is>
       </c>
       <c r="M87" s="10" t="inlineStr">
@@ -6038,7 +6452,19 @@
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>顧客の既存コード体系を持ち込めない。指定コードが無視されると AC-035（退職者と同じ従業員コードはエラー）が成立せず、退職者の復活を止められない。従業員コードは突合キー</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>顧客の既存コード体系を持ち込めない。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 指定コードが無視されると AC-035（退職者と同じ従業員コードはエラー）が成立せず、退職者の復活を止められない。従業員コードは突合キー（README §4.4）</t>
+          </r>
         </is>
       </c>
       <c r="I90" s="12" t="inlineStr">
@@ -6114,7 +6540,19 @@
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>**再取り込みで既存が勝手に書き換わる。** 「スキップ」が効かないと運用で事故る</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>再取り込みで既存が勝手に書き換わる。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 「スキップ」が効かないと運用で事故る</t>
+          </r>
         </is>
       </c>
       <c r="I91" s="16" t="inlineStr">
@@ -6190,7 +6628,19 @@
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>**空欄で既存の値が消える。** 顧客が意図せずデータを失い、元に戻せない</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>空欄で既存の値が消える。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 顧客が意図せずデータを失い、元に戻せない</t>
+          </r>
         </is>
       </c>
       <c r="I92" s="16" t="inlineStr">
@@ -6210,7 +6660,19 @@
       </c>
       <c r="L92" s="10" t="inlineStr">
         <is>
-          <t>**設計の背骨③**／フローE／README §8.2</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>設計の背骨③</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t>／フローE／README §8.2</t>
+          </r>
         </is>
       </c>
       <c r="M92" s="10" t="inlineStr">
@@ -6342,7 +6804,19 @@
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>**再開しても中身が違えば、顧客は入力し直しになる。** 中断機能の意味が無くなる</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>再開しても中身が違えば、顧客は入力し直しになる。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 中断機能の意味が無くなる</t>
+          </r>
         </is>
       </c>
       <c r="I94" s="12" t="inlineStr">
@@ -6418,7 +6892,19 @@
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>**身に覚えのないデータが登録される。** 中断分が新規の取り込みに混ざる</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>身に覚えのないデータが登録される。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 中断分が新規の取り込みに混ざる</t>
+          </r>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr">
@@ -6722,7 +7208,19 @@
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>**インポートの仕様が成立しない。** 「できないこと」の受け皿が無くなる</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>インポートの仕様が成立しない。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 「できないこと」の受け皿が無くなる</t>
+          </r>
         </is>
       </c>
       <c r="I99" s="18" t="inlineStr">
@@ -6798,7 +7296,19 @@
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>**取り込んだデータを後から直せない。** 運用が回らない</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>取り込んだデータを後から直せない。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 運用が回らない</t>
+          </r>
         </is>
       </c>
       <c r="I100" s="18" t="inlineStr">
@@ -6874,7 +7384,19 @@
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
-          <t>**誤って取り込んだデータを消せない。** インポートに削除は無く、手入力が唯一の出口</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>誤って取り込んだデータを消せない。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> インポートに削除は無く、手入力が唯一の出口</t>
+          </r>
         </is>
       </c>
       <c r="I101" s="18" t="inlineStr">
@@ -6950,7 +7472,19 @@
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>**店長が全社マスタを書き換えられる。** 他店舗に影響が及ぶ</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>店長が全社マスタを書き換えられる。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 他店舗に影響が及ぶ</t>
+          </r>
         </is>
       </c>
       <c r="I102" s="12" t="inlineStr">
@@ -7026,7 +7560,19 @@
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>**店長が他店舗の従業員を登録できる。** 権限設計が破綻する</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>店長が他店舗の従業員を登録できる。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 権限設計が破綻する</t>
+          </r>
         </is>
       </c>
       <c r="I103" s="12" t="inlineStr">
@@ -7102,7 +7648,19 @@
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
-          <t>**登録した内容を直せない・消せない。** インポートの出口も塞がる</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>登録した内容を直せない・消せない。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> インポートの出口も塞がる</t>
+          </r>
         </is>
       </c>
       <c r="I104" s="18" t="inlineStr">
@@ -7178,7 +7736,19 @@
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
-          <t>**1人だけ増えたときにCSVを作らせることになる。** 日常運用の大半は1〜2件の追加。運用更新モードには順序ガードが無く、どの種別からでも追加できる必要がある</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>1人だけ増えたときにCSVを作らせることになる。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 日常運用の大半は1〜2件の追加。運用更新モードには順序ガードが無く、どの種別からでも追加できる必要がある</t>
+          </r>
         </is>
       </c>
       <c r="I105" s="18" t="inlineStr">

--- a/excel/20260805_タイムレコード_01_受入条件表.xlsx
+++ b/excel/20260805_タイムレコード_01_受入条件表.xlsx
@@ -1438,7 +1438,7 @@
       </c>
       <c r="N29" s="20" t="inlineStr">
         <is>
-          <t>6番 テンプレートをダウンロードする（サンプル行 ／ UTF-8で保存）</t>
+          <t>6番 テンプレートをダウンロードする（サンプル行・CSV UTF-8で保存）</t>
         </is>
       </c>
       <c r="O29" s="13" t="inlineStr"/>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="N30" s="20" t="inlineStr">
         <is>
-          <t>6番 テンプレートをダウンロードする（サンプル行 ／ UTF-8で保存）</t>
+          <t>6番 テンプレートをダウンロードする（サンプル行・CSV UTF-8で保存）</t>
         </is>
       </c>
       <c r="O30" s="13" t="inlineStr"/>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="N32" s="20" t="inlineStr">
         <is>
-          <t>11番 ファイルが受け付けられない場合（文字コード） ／ 6番 UTF-8で保存 ／ 11番 ファイルが受け付けられない場合（テンプレートの列が一致しません） ／ 11番 ファイルが受け付けられない場合（取り込めるデータが1件もありません）</t>
+          <t>11番 ファイルが受け付けられない場合（文字コード） ／ 6番 CSV UTF-8 ／ 11番 ファイルが受け付けられない場合（テンプレートの列が一致しません） ／ 11番 ファイルが受け付けられない場合（取り込めるデータが1件もありません）</t>
         </is>
       </c>
       <c r="O32" s="13" t="inlineStr"/>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
-          <t>6番 テンプレートをダウンロードする（サンプル行 ／ UTF-8で保存）</t>
+          <t>6番 テンプレートをダウンロードする（サンプル行・CSV UTF-8で保存）</t>
         </is>
       </c>
       <c r="O38" s="13" t="inlineStr"/>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
-          <t>6番 テンプレートをダウンロードする（サンプル行 ／ UTF-8で保存）</t>
+          <t>6番 テンプレートをダウンロードする（サンプル行・CSV UTF-8で保存）</t>
         </is>
       </c>
       <c r="O39" s="13" t="inlineStr"/>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="N57" s="20" t="inlineStr">
         <is>
-          <t>7番 従業員 ※未記載。README §11.1 が確定したらヘルプに追記する ／ 7番 雇用区分（最大100文字・コード50文字） ／ 店舗（営業時間200文字）</t>
+          <t>—（7番 従業員に未記載。README §11.1 が確定したら追記する） ／ 7番 雇用区分（最大100文字・コード50文字） ／ 7番 店舗（営業時間200文字）</t>
         </is>
       </c>
       <c r="O57" s="13" t="inlineStr"/>

--- a/excel/20260805_タイムレコード_01_受入条件表.xlsx
+++ b/excel/20260805_タイムレコード_01_受入条件表.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受入条件表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$28:$R$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$28:$S$116</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -567,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R116"/>
+  <dimension ref="A1:S116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -643,12 +643,12 @@
           <t>NG</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>未判定</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>到達率</t>
         </is>
@@ -672,18 +672,18 @@
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A6,$O$29:$O$116,"OK")</f>
+        <f>COUNTIFS($A$29:$A$116,$A6,$P$29:$P$116,"OK")</f>
         <v/>
       </c>
       <c r="G6" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A6,$O$29:$O$116,"NG")</f>
+        <f>COUNTIFS($A$29:$A$116,$A6,$P$29:$P$116,"NG")</f>
         <v/>
       </c>
-      <c r="H6" s="6">
+      <c r="I6" s="6">
         <f>E6-F6-G6</f>
         <v/>
       </c>
-      <c r="I6" s="7">
+      <c r="J6" s="7">
         <f>IF(E6=0,"",F6/E6)</f>
         <v/>
       </c>
@@ -706,18 +706,18 @@
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A7,$O$29:$O$116,"OK")</f>
+        <f>COUNTIFS($A$29:$A$116,$A7,$P$29:$P$116,"OK")</f>
         <v/>
       </c>
       <c r="G7" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A7,$O$29:$O$116,"NG")</f>
+        <f>COUNTIFS($A$29:$A$116,$A7,$P$29:$P$116,"NG")</f>
         <v/>
       </c>
-      <c r="H7" s="6">
+      <c r="I7" s="6">
         <f>E7-F7-G7</f>
         <v/>
       </c>
-      <c r="I7" s="7">
+      <c r="J7" s="7">
         <f>IF(E7=0,"",F7/E7)</f>
         <v/>
       </c>
@@ -740,18 +740,18 @@
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A8,$O$29:$O$116,"OK")</f>
+        <f>COUNTIFS($A$29:$A$116,$A8,$P$29:$P$116,"OK")</f>
         <v/>
       </c>
       <c r="G8" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A8,$O$29:$O$116,"NG")</f>
+        <f>COUNTIFS($A$29:$A$116,$A8,$P$29:$P$116,"NG")</f>
         <v/>
       </c>
-      <c r="H8" s="6">
+      <c r="I8" s="6">
         <f>E8-F8-G8</f>
         <v/>
       </c>
-      <c r="I8" s="7">
+      <c r="J8" s="7">
         <f>IF(E8=0,"",F8/E8)</f>
         <v/>
       </c>
@@ -774,18 +774,18 @@
         <v/>
       </c>
       <c r="F9" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A9,$O$29:$O$116,"OK")</f>
+        <f>COUNTIFS($A$29:$A$116,$A9,$P$29:$P$116,"OK")</f>
         <v/>
       </c>
       <c r="G9" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A9,$O$29:$O$116,"NG")</f>
+        <f>COUNTIFS($A$29:$A$116,$A9,$P$29:$P$116,"NG")</f>
         <v/>
       </c>
-      <c r="H9" s="6">
+      <c r="I9" s="6">
         <f>E9-F9-G9</f>
         <v/>
       </c>
-      <c r="I9" s="7">
+      <c r="J9" s="7">
         <f>IF(E9=0,"",F9/E9)</f>
         <v/>
       </c>
@@ -808,18 +808,18 @@
         <v/>
       </c>
       <c r="F10" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A10,$O$29:$O$116,"OK")</f>
+        <f>COUNTIFS($A$29:$A$116,$A10,$P$29:$P$116,"OK")</f>
         <v/>
       </c>
       <c r="G10" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A10,$O$29:$O$116,"NG")</f>
+        <f>COUNTIFS($A$29:$A$116,$A10,$P$29:$P$116,"NG")</f>
         <v/>
       </c>
-      <c r="H10" s="6">
+      <c r="I10" s="6">
         <f>E10-F10-G10</f>
         <v/>
       </c>
-      <c r="I10" s="7">
+      <c r="J10" s="7">
         <f>IF(E10=0,"",F10/E10)</f>
         <v/>
       </c>
@@ -842,18 +842,18 @@
         <v/>
       </c>
       <c r="F11" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A11,$O$29:$O$116,"OK")</f>
+        <f>COUNTIFS($A$29:$A$116,$A11,$P$29:$P$116,"OK")</f>
         <v/>
       </c>
       <c r="G11" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A11,$O$29:$O$116,"NG")</f>
+        <f>COUNTIFS($A$29:$A$116,$A11,$P$29:$P$116,"NG")</f>
         <v/>
       </c>
-      <c r="H11" s="6">
+      <c r="I11" s="6">
         <f>E11-F11-G11</f>
         <v/>
       </c>
-      <c r="I11" s="7">
+      <c r="J11" s="7">
         <f>IF(E11=0,"",F11/E11)</f>
         <v/>
       </c>
@@ -876,18 +876,18 @@
         <v/>
       </c>
       <c r="F12" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A12,$O$29:$O$116,"OK")</f>
+        <f>COUNTIFS($A$29:$A$116,$A12,$P$29:$P$116,"OK")</f>
         <v/>
       </c>
       <c r="G12" s="6">
-        <f>COUNTIFS($A$29:$A$116,$A12,$O$29:$O$116,"NG")</f>
+        <f>COUNTIFS($A$29:$A$116,$A12,$P$29:$P$116,"NG")</f>
         <v/>
       </c>
-      <c r="H12" s="6">
+      <c r="I12" s="6">
         <f>E12-F12-G12</f>
         <v/>
       </c>
-      <c r="I12" s="7">
+      <c r="J12" s="7">
         <f>IF(E12=0,"",F12/E12)</f>
         <v/>
       </c>
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="B13" s="8">
-        <f>IF(COUNTIFS($E$29:$E$116,"MVP必須",$O$29:$O$116,"NG")&gt;0,"MVP未達（MVP必須のNG "&amp;COUNTIFS($E$29:$E$116,"MVP必須",$O$29:$O$116,"NG")&amp;"件）── リリース不可",IF((COUNTIF($E$29:$E$116,"MVP必須")-COUNTIFS($E$29:$E$116,"MVP必須",$O$29:$O$116,"OK")-COUNTIFS($E$29:$E$116,"MVP必須",$O$29:$O$116,"NG"))&gt;0,"判定未完了（MVP必須の残 "&amp;(COUNTIF($E$29:$E$116,"MVP必須")-COUNTIFS($E$29:$E$116,"MVP必須",$O$29:$O$116,"OK")-COUNTIFS($E$29:$E$116,"MVP必須",$O$29:$O$116,"NG"))&amp;"件）",IF(COUNTIFS($E$29:$E$116,"リリース必須",$O$29:$O$116,"NG")&gt;0,"MVP到達。リリース必須にNGあり ── 運用でカバーできるか判断","MVP到達・リリース必須も充足 ── リリース可")))</f>
+        <f>IF(COUNTIFS($E$29:$E$116,"MVP必須",$P$29:$P$116,"NG")&gt;0,"MVP未達（MVP必須のNG "&amp;COUNTIFS($E$29:$E$116,"MVP必須",$P$29:$P$116,"NG")&amp;"件）── リリース不可",IF((COUNTIF($E$29:$E$116,"MVP必須")-COUNTIFS($E$29:$E$116,"MVP必須",$P$29:$P$116,"OK")-COUNTIFS($E$29:$E$116,"MVP必須",$P$29:$P$116,"NG"))&gt;0,"判定未完了（MVP必須の残 "&amp;(COUNTIF($E$29:$E$116,"MVP必須")-COUNTIFS($E$29:$E$116,"MVP必須",$P$29:$P$116,"OK")-COUNTIFS($E$29:$E$116,"MVP必須",$P$29:$P$116,"NG"))&amp;"件）",IF(COUNTIFS($E$29:$E$116,"リリース必須",$P$29:$P$116,"NG")&gt;0,"MVP到達。リリース必須にNGあり ── 運用でカバーできるか判断","MVP到達・リリース必須も充足 ── リリース可")))</f>
         <v/>
       </c>
       <c r="C13" s="6" t="n"/>
@@ -907,8 +907,8 @@
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
       <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -938,12 +938,12 @@
           <t>NG</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>未判定</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>到達率</t>
         </is>
@@ -967,18 +967,18 @@
         <v/>
       </c>
       <c r="F16" s="6">
-        <f>COUNTIFS($I$29:$I$116,"*1*",$O$29:$O$116,"OK")</f>
+        <f>COUNTIFS($I$29:$I$116,"*1*",$P$29:$P$116,"OK")</f>
         <v/>
       </c>
       <c r="G16" s="6">
-        <f>COUNTIFS($I$29:$I$116,"*1*",$O$29:$O$116,"NG")</f>
+        <f>COUNTIFS($I$29:$I$116,"*1*",$P$29:$P$116,"NG")</f>
         <v/>
       </c>
-      <c r="H16" s="6">
+      <c r="I16" s="6">
         <f>E16-F16-G16</f>
         <v/>
       </c>
-      <c r="I16" s="7">
+      <c r="J16" s="7">
         <f>IF(E16=0,"",F16/E16)</f>
         <v/>
       </c>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="F17" s="6">
-        <f>COUNTIFS($I$29:$I$116,"*2*",$O$29:$O$116,"OK")</f>
+        <f>COUNTIFS($I$29:$I$116,"*2*",$P$29:$P$116,"OK")</f>
         <v/>
       </c>
       <c r="G17" s="6">
-        <f>COUNTIFS($I$29:$I$116,"*2*",$O$29:$O$116,"NG")</f>
+        <f>COUNTIFS($I$29:$I$116,"*2*",$P$29:$P$116,"NG")</f>
         <v/>
       </c>
-      <c r="H17" s="6">
+      <c r="I17" s="6">
         <f>E17-F17-G17</f>
         <v/>
       </c>
-      <c r="I17" s="7">
+      <c r="J17" s="7">
         <f>IF(E17=0,"",F17/E17)</f>
         <v/>
       </c>
@@ -1035,18 +1035,18 @@
         <v/>
       </c>
       <c r="F18" s="6">
-        <f>COUNTIFS($I$29:$I$116,"*3*",$O$29:$O$116,"OK")</f>
+        <f>COUNTIFS($I$29:$I$116,"*3*",$P$29:$P$116,"OK")</f>
         <v/>
       </c>
       <c r="G18" s="6">
-        <f>COUNTIFS($I$29:$I$116,"*3*",$O$29:$O$116,"NG")</f>
+        <f>COUNTIFS($I$29:$I$116,"*3*",$P$29:$P$116,"NG")</f>
         <v/>
       </c>
-      <c r="H18" s="6">
+      <c r="I18" s="6">
         <f>E18-F18-G18</f>
         <v/>
       </c>
-      <c r="I18" s="7">
+      <c r="J18" s="7">
         <f>IF(E18=0,"",F18/E18)</f>
         <v/>
       </c>
@@ -1069,18 +1069,18 @@
         <v/>
       </c>
       <c r="F19" s="6">
-        <f>COUNTIFS($I$29:$I$116,"*4*",$O$29:$O$116,"OK")</f>
+        <f>COUNTIFS($I$29:$I$116,"*4*",$P$29:$P$116,"OK")</f>
         <v/>
       </c>
       <c r="G19" s="6">
-        <f>COUNTIFS($I$29:$I$116,"*4*",$O$29:$O$116,"NG")</f>
+        <f>COUNTIFS($I$29:$I$116,"*4*",$P$29:$P$116,"NG")</f>
         <v/>
       </c>
-      <c r="H19" s="6">
+      <c r="I19" s="6">
         <f>E19-F19-G19</f>
         <v/>
       </c>
-      <c r="I19" s="7">
+      <c r="J19" s="7">
         <f>IF(E19=0,"",F19/E19)</f>
         <v/>
       </c>
@@ -1113,12 +1113,12 @@
           <t>NG</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>未判定</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>到達率</t>
         </is>
@@ -1142,18 +1142,18 @@
         <v/>
       </c>
       <c r="F22" s="6">
-        <f>COUNTIFS($E$29:$E$116,$A22,$O$29:$O$116,"OK")</f>
+        <f>COUNTIFS($E$29:$E$116,$A22,$P$29:$P$116,"OK")</f>
         <v/>
       </c>
       <c r="G22" s="6">
-        <f>COUNTIFS($E$29:$E$116,$A22,$O$29:$O$116,"NG")</f>
+        <f>COUNTIFS($E$29:$E$116,$A22,$P$29:$P$116,"NG")</f>
         <v/>
       </c>
-      <c r="H22" s="6">
+      <c r="I22" s="6">
         <f>E22-F22-G22</f>
         <v/>
       </c>
-      <c r="I22" s="7">
+      <c r="J22" s="7">
         <f>IF(E22=0,"",F22/E22)</f>
         <v/>
       </c>
@@ -1176,18 +1176,18 @@
         <v/>
       </c>
       <c r="F23" s="6">
-        <f>COUNTIFS($E$29:$E$116,$A23,$O$29:$O$116,"OK")</f>
+        <f>COUNTIFS($E$29:$E$116,$A23,$P$29:$P$116,"OK")</f>
         <v/>
       </c>
       <c r="G23" s="6">
-        <f>COUNTIFS($E$29:$E$116,$A23,$O$29:$O$116,"NG")</f>
+        <f>COUNTIFS($E$29:$E$116,$A23,$P$29:$P$116,"NG")</f>
         <v/>
       </c>
-      <c r="H23" s="6">
+      <c r="I23" s="6">
         <f>E23-F23-G23</f>
         <v/>
       </c>
-      <c r="I23" s="7">
+      <c r="J23" s="7">
         <f>IF(E23=0,"",F23/E23)</f>
         <v/>
       </c>
@@ -1210,18 +1210,18 @@
         <v/>
       </c>
       <c r="F24" s="6">
-        <f>COUNTIFS($E$29:$E$116,$A24,$O$29:$O$116,"OK")</f>
+        <f>COUNTIFS($E$29:$E$116,$A24,$P$29:$P$116,"OK")</f>
         <v/>
       </c>
       <c r="G24" s="6">
-        <f>COUNTIFS($E$29:$E$116,$A24,$O$29:$O$116,"NG")</f>
+        <f>COUNTIFS($E$29:$E$116,$A24,$P$29:$P$116,"NG")</f>
         <v/>
       </c>
-      <c r="H24" s="6">
+      <c r="I24" s="6">
         <f>E24-F24-G24</f>
         <v/>
       </c>
-      <c r="I24" s="7">
+      <c r="J24" s="7">
         <f>IF(E24=0,"",F24/E24)</f>
         <v/>
       </c>
@@ -1244,18 +1244,18 @@
         <v/>
       </c>
       <c r="F25" s="6">
-        <f>COUNTIFS($E$29:$E$116,$A25,$O$29:$O$116,"OK")</f>
+        <f>COUNTIFS($E$29:$E$116,$A25,$P$29:$P$116,"OK")</f>
         <v/>
       </c>
       <c r="G25" s="6">
-        <f>COUNTIFS($E$29:$E$116,$A25,$O$29:$O$116,"NG")</f>
+        <f>COUNTIFS($E$29:$E$116,$A25,$P$29:$P$116,"NG")</f>
         <v/>
       </c>
-      <c r="H25" s="6">
+      <c r="I25" s="6">
         <f>E25-F25-G25</f>
         <v/>
       </c>
-      <c r="I25" s="7">
+      <c r="J25" s="7">
         <f>IF(E25=0,"",F25/E25)</f>
         <v/>
       </c>
@@ -1310,55 +1310,60 @@
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
+          <t>前提となる条件</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
           <t>実装できていないと起きること</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>フロー</t>
         </is>
       </c>
-      <c r="J28" s="9" t="inlineStr">
+      <c r="K28" s="9" t="inlineStr">
         <is>
           <t>確認する画面</t>
         </is>
       </c>
-      <c r="K28" s="9" t="inlineStr">
+      <c r="L28" s="9" t="inlineStr">
         <is>
           <t>確認方法</t>
         </is>
       </c>
-      <c r="L28" s="9" t="inlineStr">
+      <c r="M28" s="9" t="inlineStr">
         <is>
           <t>仕様書の根拠</t>
         </is>
       </c>
-      <c r="M28" s="9" t="inlineStr">
+      <c r="N28" s="9" t="inlineStr">
         <is>
           <t>対応検証ID</t>
         </is>
       </c>
-      <c r="N28" s="9" t="inlineStr">
+      <c r="O28" s="9" t="inlineStr">
         <is>
           <t>ヘルプ該当箇所</t>
         </is>
       </c>
-      <c r="O28" s="9" t="inlineStr">
+      <c r="P28" s="9" t="inlineStr">
         <is>
           <t>合否</t>
         </is>
       </c>
-      <c r="P28" s="9" t="inlineStr">
+      <c r="Q28" s="9" t="inlineStr">
         <is>
           <t>実測値</t>
         </is>
       </c>
-      <c r="Q28" s="9" t="inlineStr">
+      <c r="R28" s="9" t="inlineStr">
         <is>
           <t>判定者</t>
         </is>
       </c>
-      <c r="R28" s="9" t="inlineStr">
+      <c r="S28" s="9" t="inlineStr">
         <is>
           <t>判定日</t>
         </is>
@@ -1400,7 +1405,12 @@
           <t>①〜⑤の5ファイルすべてがダウンロードでき、Excelで開いて文字化けしない（開けない・化けるファイル＝0件）</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1411,40 +1421,40 @@
           </r>
         </is>
       </c>
-      <c r="I29" s="12" t="inlineStr">
+      <c r="J29" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J29" s="10" t="inlineStr">
+      <c r="K29" s="10" t="inlineStr">
         <is>
           <t>インポート</t>
         </is>
       </c>
-      <c r="K29" s="10" t="inlineStr">
+      <c r="L29" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L29" s="10" t="inlineStr">
+      <c r="M29" s="10" t="inlineStr">
         <is>
           <t>README §9.5</t>
         </is>
       </c>
-      <c r="M29" s="10" t="inlineStr">
+      <c r="N29" s="10" t="inlineStr">
         <is>
           <t>OP-101</t>
         </is>
       </c>
-      <c r="N29" s="20" t="inlineStr">
+      <c r="O29" s="20" t="inlineStr">
         <is>
           <t>6番 テンプレートをダウンロードする（サンプル行・CSV UTF-8で保存）</t>
         </is>
       </c>
-      <c r="O29" s="13" t="inlineStr"/>
       <c r="P29" s="13" t="inlineStr"/>
       <c r="Q29" s="13" t="inlineStr"/>
       <c r="R29" s="13" t="inlineStr"/>
+      <c r="S29" s="13" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
@@ -1482,7 +1492,12 @@
           <t>③雇用区分・④従業員のサンプル行でコード列が空欄（値が入っているファイル＝0件）</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1499,40 +1514,40 @@
           </r>
         </is>
       </c>
-      <c r="I30" s="12" t="inlineStr">
+      <c r="J30" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J30" s="10" t="inlineStr">
+      <c r="K30" s="10" t="inlineStr">
         <is>
           <t>インポート</t>
         </is>
       </c>
-      <c r="K30" s="10" t="inlineStr">
+      <c r="L30" s="10" t="inlineStr">
         <is>
           <t>実装レビュー（配布テンプレート）</t>
         </is>
       </c>
-      <c r="L30" s="10" t="inlineStr">
+      <c r="M30" s="10" t="inlineStr">
         <is>
           <t>README §8.1</t>
         </is>
       </c>
-      <c r="M30" s="10" t="inlineStr">
+      <c r="N30" s="10" t="inlineStr">
         <is>
           <t>OP-101</t>
         </is>
       </c>
-      <c r="N30" s="20" t="inlineStr">
+      <c r="O30" s="20" t="inlineStr">
         <is>
           <t>6番 テンプレートをダウンロードする（サンプル行・CSV UTF-8で保存）</t>
         </is>
       </c>
-      <c r="O30" s="13" t="inlineStr"/>
       <c r="P30" s="13" t="inlineStr"/>
       <c r="Q30" s="13" t="inlineStr"/>
       <c r="R30" s="13" t="inlineStr"/>
+      <c r="S30" s="13" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
@@ -1570,7 +1585,12 @@
           <t>①②③⑤は500行が受理・501行が拒否。④従業員は200行が受理・201行が拒否。ファイルサイズは5.0MBが受理・5.1MBが拒否。拒否時は上限と実際の値がメッセージに出る</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1581,40 +1601,40 @@
           </r>
         </is>
       </c>
-      <c r="I31" s="12" t="inlineStr">
+      <c r="J31" s="12" t="inlineStr">
         <is>
           <t>2 / 4</t>
         </is>
       </c>
-      <c r="J31" s="10" t="inlineStr">
+      <c r="K31" s="10" t="inlineStr">
         <is>
           <t>アップロード</t>
         </is>
       </c>
-      <c r="K31" s="10" t="inlineStr">
+      <c r="L31" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L31" s="10" t="inlineStr">
+      <c r="M31" s="10" t="inlineStr">
         <is>
           <t>README §7.5</t>
         </is>
       </c>
-      <c r="M31" s="10" t="inlineStr">
+      <c r="N31" s="10" t="inlineStr">
         <is>
           <t>CA-001 / CA-003 / CA-005 / OP-211 / OP-213</t>
         </is>
       </c>
-      <c r="N31" s="20" t="inlineStr">
+      <c r="O31" s="20" t="inlineStr">
         <is>
           <t>6番 1回に取り込める量（500行） ／ 6番 1回に取り込める量（200行） ／ 6番 1回に取り込める量（5MB） ／ 6番 1回に取り込める量（500行・200行） ／ 11番 ファイルが受け付けられない場合</t>
         </is>
       </c>
-      <c r="O31" s="13" t="inlineStr"/>
       <c r="P31" s="13" t="inlineStr"/>
       <c r="Q31" s="13" t="inlineStr"/>
       <c r="R31" s="13" t="inlineStr"/>
+      <c r="S31" s="13" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
@@ -1652,7 +1672,12 @@
           <t>OP-214（文字コード不正）「文字コードがUTF-8ではない可能性があります」と表示される ／ OP-215（列名不一致）「テンプレートの列が一致しません」と表示され、必要な列と見つかった列が併記される ／ OP-216（データ0件）「取り込めるデータがありません」と表示される</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1663,40 +1688,40 @@
           </r>
         </is>
       </c>
-      <c r="I32" s="12" t="inlineStr">
+      <c r="J32" s="12" t="inlineStr">
         <is>
           <t>2 / 4</t>
         </is>
       </c>
-      <c r="J32" s="10" t="inlineStr">
+      <c r="K32" s="10" t="inlineStr">
         <is>
           <t>アップロード</t>
         </is>
       </c>
-      <c r="K32" s="10" t="inlineStr">
+      <c r="L32" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L32" s="10" t="inlineStr">
+      <c r="M32" s="10" t="inlineStr">
         <is>
           <t>README §9.5</t>
         </is>
       </c>
-      <c r="M32" s="10" t="inlineStr">
+      <c r="N32" s="10" t="inlineStr">
         <is>
           <t>OP-214 / OP-215 / OP-216</t>
         </is>
       </c>
-      <c r="N32" s="20" t="inlineStr">
+      <c r="O32" s="20" t="inlineStr">
         <is>
           <t>11番 ファイルが受け付けられない場合（文字コード） ／ 6番 CSV UTF-8 ／ 11番 ファイルが受け付けられない場合（テンプレートの列が一致しません） ／ 11番 ファイルが受け付けられない場合（取り込めるデータが1件もありません）</t>
         </is>
       </c>
-      <c r="O32" s="13" t="inlineStr"/>
       <c r="P32" s="13" t="inlineStr"/>
       <c r="Q32" s="13" t="inlineStr"/>
       <c r="R32" s="13" t="inlineStr"/>
+      <c r="S32" s="13" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
@@ -1734,7 +1759,12 @@
           <t>①未登録の状態で②を取り込むと、所属業態が引き当てられずエラー（取り込まれた件数＝0件）。①→②の順なら全件が「新規」と表示される</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1751,40 +1781,40 @@
           </r>
         </is>
       </c>
-      <c r="I33" s="12" t="inlineStr">
+      <c r="J33" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J33" s="10" t="inlineStr">
+      <c r="K33" s="10" t="inlineStr">
         <is>
           <t>プレビュー</t>
         </is>
       </c>
-      <c r="K33" s="10" t="inlineStr">
+      <c r="L33" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L33" s="10" t="inlineStr">
+      <c r="M33" s="10" t="inlineStr">
         <is>
           <t>README §1.3</t>
         </is>
       </c>
-      <c r="M33" s="10" t="inlineStr">
+      <c r="N33" s="10" t="inlineStr">
         <is>
           <t>OP-201 / OP-202</t>
         </is>
       </c>
-      <c r="N33" s="20" t="inlineStr">
+      <c r="O33" s="20" t="inlineStr">
         <is>
           <t>1番 はじめて登録するときの順番 ／ 11番 よくあるエラー</t>
         </is>
       </c>
-      <c r="O33" s="13" t="inlineStr"/>
       <c r="P33" s="13" t="inlineStr"/>
       <c r="Q33" s="13" t="inlineStr"/>
       <c r="R33" s="13" t="inlineStr"/>
+      <c r="S33" s="13" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
@@ -1822,7 +1852,12 @@
           <t>分割せずに受理される（④は200行、他は500行の範囲に収まる）</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1839,40 +1874,40 @@
           </r>
         </is>
       </c>
-      <c r="I34" s="12" t="inlineStr">
+      <c r="J34" s="12" t="inlineStr">
         <is>
           <t>2 / 4</t>
         </is>
       </c>
-      <c r="J34" s="10" t="inlineStr">
+      <c r="K34" s="10" t="inlineStr">
         <is>
           <t>アップロード</t>
         </is>
       </c>
-      <c r="K34" s="10" t="inlineStr">
+      <c r="L34" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L34" s="10" t="inlineStr">
+      <c r="M34" s="10" t="inlineStr">
         <is>
           <t>仕様書 1.1 何を解決しているか／README §7.5</t>
         </is>
       </c>
-      <c r="M34" s="10" t="inlineStr">
+      <c r="N34" s="10" t="inlineStr">
         <is>
           <t>OP-620 / CA-003</t>
         </is>
       </c>
-      <c r="N34" s="20" t="inlineStr">
+      <c r="O34" s="20" t="inlineStr">
         <is>
           <t>3番 はじめて登録する方へ（CSVで一括登録） ／ 10番 招待メールを送る ／ 6番 1回に取り込める量（200行）</t>
         </is>
       </c>
-      <c r="O34" s="13" t="inlineStr"/>
       <c r="P34" s="13" t="inlineStr"/>
       <c r="Q34" s="13" t="inlineStr"/>
       <c r="R34" s="13" t="inlineStr"/>
+      <c r="S34" s="13" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
@@ -1910,7 +1945,12 @@
           <t>未到達のステップで登録できた件数＝0件（警告バナーが出てボタンが押せない）</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H35" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1927,40 +1967,40 @@
           </r>
         </is>
       </c>
-      <c r="I35" s="14" t="inlineStr">
+      <c r="J35" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J35" s="10" t="inlineStr">
+      <c r="K35" s="10" t="inlineStr">
         <is>
           <t>初期セットアップ</t>
         </is>
       </c>
-      <c r="K35" s="10" t="inlineStr">
+      <c r="L35" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L35" s="10" t="inlineStr">
+      <c r="M35" s="10" t="inlineStr">
         <is>
           <t>owner-mock §5.3 順序ガード</t>
         </is>
       </c>
-      <c r="M35" s="10" t="inlineStr">
+      <c r="N35" s="10" t="inlineStr">
         <is>
           <t>OP-022</t>
         </is>
       </c>
-      <c r="N35" s="20" t="inlineStr">
+      <c r="O35" s="20" t="inlineStr">
         <is>
           <t>1番 はじめて登録するときの順番（順番を飛ばすと登録できません）</t>
         </is>
       </c>
-      <c r="O35" s="13" t="inlineStr"/>
       <c r="P35" s="13" t="inlineStr"/>
       <c r="Q35" s="13" t="inlineStr"/>
       <c r="R35" s="13" t="inlineStr"/>
+      <c r="S35" s="13" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
@@ -1998,7 +2038,12 @@
           <t>done&gt;=4 で *-settings を開くと *-ops-settings へ転送される（転送されない＝不合格）</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H36" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2015,40 +2060,40 @@
           </r>
         </is>
       </c>
-      <c r="I36" s="14" t="inlineStr">
+      <c r="J36" s="14" t="inlineStr">
         <is>
           <t>1 / 3</t>
         </is>
       </c>
-      <c r="J36" s="10" t="inlineStr">
+      <c r="K36" s="10" t="inlineStr">
         <is>
           <t>各設定画面</t>
         </is>
       </c>
-      <c r="K36" s="10" t="inlineStr">
+      <c r="L36" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L36" s="10" t="inlineStr">
+      <c r="M36" s="10" t="inlineStr">
         <is>
           <t>owner-mock §3.3</t>
         </is>
       </c>
-      <c r="M36" s="10" t="inlineStr">
+      <c r="N36" s="10" t="inlineStr">
         <is>
           <t>OP-025</t>
         </is>
       </c>
-      <c r="N36" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O36" s="13" t="inlineStr"/>
+      <c r="O36" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="P36" s="13" t="inlineStr"/>
       <c r="Q36" s="13" t="inlineStr"/>
       <c r="R36" s="13" t="inlineStr"/>
+      <c r="S36" s="13" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
@@ -2086,7 +2131,12 @@
           <t>初期セットアップから①業態を3件登録でき、登録済み件数＝3件と表示される</t>
         </is>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H37" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2103,40 +2153,40 @@
           </r>
         </is>
       </c>
-      <c r="I37" s="14" t="inlineStr">
+      <c r="J37" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J37" s="10" t="inlineStr">
+      <c r="K37" s="10" t="inlineStr">
         <is>
           <t>初期セットアップ／業態設定</t>
         </is>
       </c>
-      <c r="K37" s="10" t="inlineStr">
+      <c r="L37" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L37" s="10" t="inlineStr">
+      <c r="M37" s="10" t="inlineStr">
         <is>
           <t>owner-mock §3.3.2</t>
         </is>
       </c>
-      <c r="M37" s="10" t="inlineStr">
+      <c r="N37" s="10" t="inlineStr">
         <is>
           <t>OP-021</t>
         </is>
       </c>
-      <c r="N37" s="20" t="inlineStr">
+      <c r="O37" s="20" t="inlineStr">
         <is>
           <t>2番 登録の手順</t>
         </is>
       </c>
-      <c r="O37" s="13" t="inlineStr"/>
       <c r="P37" s="13" t="inlineStr"/>
       <c r="Q37" s="13" t="inlineStr"/>
       <c r="R37" s="13" t="inlineStr"/>
+      <c r="S37" s="13" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
@@ -2174,45 +2224,50 @@
           <t>⑤管理者テンプレートが3列（管理者名・メールアドレス・担当店舗）。権限列＝0個</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H38" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>存在しない権限列を顧客が埋め、混乱する</t>
         </is>
       </c>
-      <c r="I38" s="12" t="inlineStr">
+      <c r="J38" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J38" s="10" t="inlineStr">
+      <c r="K38" s="10" t="inlineStr">
         <is>
           <t>インポート</t>
         </is>
       </c>
-      <c r="K38" s="10" t="inlineStr">
+      <c r="L38" s="10" t="inlineStr">
         <is>
           <t>実装レビュー（配布テンプレート）</t>
         </is>
       </c>
-      <c r="L38" s="10" t="inlineStr">
+      <c r="M38" s="10" t="inlineStr">
         <is>
           <t>README §7.4</t>
         </is>
       </c>
-      <c r="M38" s="10" t="inlineStr">
+      <c r="N38" s="10" t="inlineStr">
         <is>
           <t>OP-101</t>
         </is>
       </c>
-      <c r="N38" s="20" t="inlineStr">
+      <c r="O38" s="20" t="inlineStr">
         <is>
           <t>6番 テンプレートをダウンロードする（サンプル行・CSV UTF-8で保存）</t>
         </is>
       </c>
-      <c r="O38" s="13" t="inlineStr"/>
       <c r="P38" s="13" t="inlineStr"/>
       <c r="Q38" s="13" t="inlineStr"/>
       <c r="R38" s="13" t="inlineStr"/>
+      <c r="S38" s="13" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
@@ -2250,45 +2305,50 @@
           <t>②店舗テンプレートの営業時間が1列（開店時間・閉店時間に分かれている＝不合格）</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H39" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>列構成がDBと合わず取り込めない</t>
         </is>
       </c>
-      <c r="I39" s="12" t="inlineStr">
+      <c r="J39" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J39" s="10" t="inlineStr">
+      <c r="K39" s="10" t="inlineStr">
         <is>
           <t>インポート</t>
         </is>
       </c>
-      <c r="K39" s="10" t="inlineStr">
+      <c r="L39" s="10" t="inlineStr">
         <is>
           <t>実装レビュー（配布テンプレート）</t>
         </is>
       </c>
-      <c r="L39" s="10" t="inlineStr">
+      <c r="M39" s="10" t="inlineStr">
         <is>
           <t>README §7.3</t>
         </is>
       </c>
-      <c r="M39" s="10" t="inlineStr">
+      <c r="N39" s="10" t="inlineStr">
         <is>
           <t>OP-101</t>
         </is>
       </c>
-      <c r="N39" s="20" t="inlineStr">
+      <c r="O39" s="20" t="inlineStr">
         <is>
           <t>6番 テンプレートをダウンロードする（サンプル行・CSV UTF-8で保存）</t>
         </is>
       </c>
-      <c r="O39" s="13" t="inlineStr"/>
       <c r="P39" s="13" t="inlineStr"/>
       <c r="Q39" s="13" t="inlineStr"/>
       <c r="R39" s="13" t="inlineStr"/>
+      <c r="S39" s="13" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
@@ -2326,7 +2386,12 @@
           <t>設定画面から起動 → 方式選択画面の表示回数＝0回（該当画面へ直行）</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H40" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2343,40 +2408,40 @@
           </r>
         </is>
       </c>
-      <c r="I40" s="16" t="inlineStr">
+      <c r="J40" s="16" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J40" s="10" t="inlineStr">
+      <c r="K40" s="10" t="inlineStr">
         <is>
           <t>業態設定→インポート</t>
         </is>
       </c>
-      <c r="K40" s="10" t="inlineStr">
+      <c r="L40" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L40" s="10" t="inlineStr">
+      <c r="M40" s="10" t="inlineStr">
         <is>
           <t>仕様書「連携要件A」</t>
         </is>
       </c>
-      <c r="M40" s="10" t="inlineStr">
+      <c r="N40" s="10" t="inlineStr">
         <is>
           <t>OP-008</t>
         </is>
       </c>
-      <c r="N40" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O40" s="13" t="inlineStr"/>
+      <c r="O40" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="P40" s="13" t="inlineStr"/>
       <c r="Q40" s="13" t="inlineStr"/>
       <c r="R40" s="13" t="inlineStr"/>
+      <c r="S40" s="13" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
@@ -2414,45 +2479,50 @@
           <t>3経路それぞれで戻り先が正しい（誤った戻り先＝0件）</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H41" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>元の作業に戻れず、運用で使われなくなる</t>
         </is>
       </c>
-      <c r="I41" s="16" t="inlineStr">
+      <c r="J41" s="16" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J41" s="10" t="inlineStr">
+      <c r="K41" s="10" t="inlineStr">
         <is>
           <t>完了画面</t>
         </is>
       </c>
-      <c r="K41" s="10" t="inlineStr">
+      <c r="L41" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L41" s="10" t="inlineStr">
+      <c r="M41" s="10" t="inlineStr">
         <is>
           <t>仕様書「入口と取り込み範囲」</t>
         </is>
       </c>
-      <c r="M41" s="10" t="inlineStr">
+      <c r="N41" s="10" t="inlineStr">
         <is>
           <t>OP-009</t>
         </is>
       </c>
-      <c r="N41" s="20" t="inlineStr">
+      <c r="O41" s="20" t="inlineStr">
         <is>
           <t>5番 終わったあとは、入ってきた画面に戻ります</t>
         </is>
       </c>
-      <c r="O41" s="13" t="inlineStr"/>
       <c r="P41" s="13" t="inlineStr"/>
       <c r="Q41" s="13" t="inlineStr"/>
       <c r="R41" s="13" t="inlineStr"/>
+      <c r="S41" s="13" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
@@ -2490,45 +2560,50 @@
           <t>どちらも拒否され、種別ごとの上限（500行／200行）と実際の行数を含むメッセージが出る。プレビューに進めない</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H42" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>拒否されたファイルが残り、取り込んだと誤解する</t>
         </is>
       </c>
-      <c r="I42" s="12" t="inlineStr">
+      <c r="J42" s="12" t="inlineStr">
         <is>
           <t>2 / 4</t>
         </is>
       </c>
-      <c r="J42" s="10" t="inlineStr">
+      <c r="K42" s="10" t="inlineStr">
         <is>
           <t>アップロード</t>
         </is>
       </c>
-      <c r="K42" s="10" t="inlineStr">
+      <c r="L42" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L42" s="10" t="inlineStr">
+      <c r="M42" s="10" t="inlineStr">
         <is>
           <t>README §9</t>
         </is>
       </c>
-      <c r="M42" s="10" t="inlineStr">
+      <c r="N42" s="10" t="inlineStr">
         <is>
           <t>OP-211</t>
         </is>
       </c>
-      <c r="N42" s="20" t="inlineStr">
+      <c r="O42" s="20" t="inlineStr">
         <is>
           <t>6番 1回に取り込める量（500行・200行） ／ 11番 ファイルが受け付けられない場合</t>
         </is>
       </c>
-      <c r="O42" s="13" t="inlineStr"/>
       <c r="P42" s="13" t="inlineStr"/>
       <c r="Q42" s="13" t="inlineStr"/>
       <c r="R42" s="13" t="inlineStr"/>
+      <c r="S42" s="13" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
@@ -2566,45 +2641,50 @@
           <t>拒否後に正しいファイルを上げ直すと受理され、プレビューに進める（再アップロード成功＝1回で可）</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="H43" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>拒否されたあと何をすれば進めるのか分からず止まる</t>
         </is>
       </c>
-      <c r="I43" s="12" t="inlineStr">
+      <c r="J43" s="12" t="inlineStr">
         <is>
           <t>2 / 4</t>
         </is>
       </c>
-      <c r="J43" s="10" t="inlineStr">
+      <c r="K43" s="10" t="inlineStr">
         <is>
           <t>アップロード</t>
         </is>
       </c>
-      <c r="K43" s="10" t="inlineStr">
+      <c r="L43" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L43" s="10" t="inlineStr">
+      <c r="M43" s="10" t="inlineStr">
         <is>
           <t>フローC</t>
         </is>
       </c>
-      <c r="M43" s="10" t="inlineStr">
+      <c r="N43" s="10" t="inlineStr">
         <is>
           <t>OP-219</t>
         </is>
       </c>
-      <c r="N43" s="20" t="inlineStr">
+      <c r="O43" s="20" t="inlineStr">
         <is>
           <t>11番 ファイルが受け付けられない場合（直して再アップロード）</t>
         </is>
       </c>
-      <c r="O43" s="13" t="inlineStr"/>
       <c r="P43" s="13" t="inlineStr"/>
       <c r="Q43" s="13" t="inlineStr"/>
       <c r="R43" s="13" t="inlineStr"/>
+      <c r="S43" s="13" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
@@ -2642,45 +2722,50 @@
           <t>登録済みステップを開くと再編集モードで開き、追加登録できる（開けない件数＝0件）</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H44" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>入力を間違えたときに戻れず、最初からやり直しになる</t>
         </is>
       </c>
-      <c r="I44" s="14" t="inlineStr">
+      <c r="J44" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J44" s="10" t="inlineStr">
+      <c r="K44" s="10" t="inlineStr">
         <is>
           <t>初期セットアップ</t>
         </is>
       </c>
-      <c r="K44" s="10" t="inlineStr">
+      <c r="L44" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L44" s="10" t="inlineStr">
+      <c r="M44" s="10" t="inlineStr">
         <is>
           <t>owner-mock §5.3</t>
         </is>
       </c>
-      <c r="M44" s="10" t="inlineStr">
+      <c r="N44" s="10" t="inlineStr">
         <is>
           <t>OP-023</t>
         </is>
       </c>
-      <c r="N44" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O44" s="13" t="inlineStr"/>
+      <c r="O44" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="P44" s="13" t="inlineStr"/>
       <c r="Q44" s="13" t="inlineStr"/>
       <c r="R44" s="13" t="inlineStr"/>
+      <c r="S44" s="13" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
@@ -2718,45 +2803,50 @@
           <t>新規登録モード＝中央CTAモーダル。運用更新モード＝右上トースト（8秒）</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="H45" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>運用中に中央モーダルが出ると作業が止まる。初期にトーストだと次へ進めず離脱する</t>
         </is>
       </c>
-      <c r="I45" s="14" t="inlineStr">
+      <c r="J45" s="14" t="inlineStr">
         <is>
           <t>1 / 3</t>
         </is>
       </c>
-      <c r="J45" s="10" t="inlineStr">
+      <c r="K45" s="10" t="inlineStr">
         <is>
           <t>初期セットアップ／各設定画面</t>
         </is>
       </c>
-      <c r="K45" s="10" t="inlineStr">
+      <c r="L45" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L45" s="10" t="inlineStr">
+      <c r="M45" s="10" t="inlineStr">
         <is>
           <t>owner-mock §6</t>
         </is>
       </c>
-      <c r="M45" s="10" t="inlineStr">
+      <c r="N45" s="10" t="inlineStr">
         <is>
           <t>OP-024 / OP-029</t>
         </is>
       </c>
-      <c r="N45" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O45" s="13" t="inlineStr"/>
+      <c r="O45" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="P45" s="13" t="inlineStr"/>
       <c r="Q45" s="13" t="inlineStr"/>
       <c r="R45" s="13" t="inlineStr"/>
+      <c r="S45" s="13" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
@@ -2794,45 +2884,50 @@
           <t>業態名がテキスト入力である（プルダウンでの選択のみ＝不合格。テキスト入力欄＝1個）</t>
         </is>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="H46" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>CSVテンプレート①と食い違い、経路によって作れるデータが変わる</t>
         </is>
       </c>
-      <c r="I46" s="14" t="inlineStr">
+      <c r="J46" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J46" s="10" t="inlineStr">
+      <c r="K46" s="10" t="inlineStr">
         <is>
           <t>業態設定</t>
         </is>
       </c>
-      <c r="K46" s="10" t="inlineStr">
+      <c r="L46" s="10" t="inlineStr">
         <is>
           <t>実装レビュー（登録モーダル）</t>
         </is>
       </c>
-      <c r="L46" s="10" t="inlineStr">
+      <c r="M46" s="10" t="inlineStr">
         <is>
           <t>owner-mock §3.4.2／README §1.2</t>
         </is>
       </c>
-      <c r="M46" s="10" t="inlineStr">
+      <c r="N46" s="10" t="inlineStr">
         <is>
           <t>OP-030</t>
         </is>
       </c>
-      <c r="N46" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O46" s="13" t="inlineStr"/>
+      <c r="O46" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="P46" s="13" t="inlineStr"/>
       <c r="Q46" s="13" t="inlineStr"/>
       <c r="R46" s="13" t="inlineStr"/>
+      <c r="S46" s="13" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
@@ -2870,45 +2965,50 @@
           <t>完了ステップ数（0〜4）と各ステップの登録件数が表示される（表示されない項目＝0件）</t>
         </is>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="H47" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>残りが分からず離脱する</t>
         </is>
       </c>
-      <c r="I47" s="14" t="inlineStr">
+      <c r="J47" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J47" s="10" t="inlineStr">
+      <c r="K47" s="10" t="inlineStr">
         <is>
           <t>初期セットアップ</t>
         </is>
       </c>
-      <c r="K47" s="10" t="inlineStr">
+      <c r="L47" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L47" s="10" t="inlineStr">
+      <c r="M47" s="10" t="inlineStr">
         <is>
           <t>owner-mock §5.1</t>
         </is>
       </c>
-      <c r="M47" s="10" t="inlineStr">
+      <c r="N47" s="10" t="inlineStr">
         <is>
           <t>OP-033</t>
         </is>
       </c>
-      <c r="N47" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O47" s="13" t="inlineStr"/>
+      <c r="O47" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="P47" s="13" t="inlineStr"/>
       <c r="Q47" s="13" t="inlineStr"/>
       <c r="R47" s="13" t="inlineStr"/>
+      <c r="S47" s="13" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
@@ -2946,45 +3046,50 @@
           <t>トップから方式を選び直せる（選び直せない＝不合格。再設定の成功＝1回で可）</t>
         </is>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="H48" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>方式を選び直せず、間違えるとやり直しになる</t>
         </is>
       </c>
-      <c r="I48" s="16" t="inlineStr">
+      <c r="J48" s="16" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J48" s="10" t="inlineStr">
+      <c r="K48" s="10" t="inlineStr">
         <is>
           <t>業態設定→インポート</t>
         </is>
       </c>
-      <c r="K48" s="10" t="inlineStr">
+      <c r="L48" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L48" s="10" t="inlineStr">
+      <c r="M48" s="10" t="inlineStr">
         <is>
           <t>README §9</t>
         </is>
       </c>
-      <c r="M48" s="10" t="inlineStr">
+      <c r="N48" s="10" t="inlineStr">
         <is>
           <t>OP-008</t>
         </is>
       </c>
-      <c r="N48" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O48" s="13" t="inlineStr"/>
+      <c r="O48" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="P48" s="13" t="inlineStr"/>
       <c r="Q48" s="13" t="inlineStr"/>
       <c r="R48" s="13" t="inlineStr"/>
+      <c r="S48" s="13" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
@@ -3022,7 +3127,12 @@
           <t>給与体系「日給」の行＝エラー。取り込まれた件数＝0件</t>
         </is>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="H49" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3039,40 +3149,40 @@
           </r>
         </is>
       </c>
-      <c r="I49" s="12" t="inlineStr">
+      <c r="J49" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J49" s="10" t="inlineStr">
+      <c r="K49" s="10" t="inlineStr">
         <is>
           <t>プレビュー</t>
         </is>
       </c>
-      <c r="K49" s="10" t="inlineStr">
+      <c r="L49" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L49" s="10" t="inlineStr">
+      <c r="M49" s="10" t="inlineStr">
         <is>
           <t>README §0.5／§8.10</t>
         </is>
       </c>
-      <c r="M49" s="10" t="inlineStr">
+      <c r="N49" s="10" t="inlineStr">
         <is>
           <t>OP-218</t>
         </is>
       </c>
-      <c r="N49" s="20" t="inlineStr">
+      <c r="O49" s="20" t="inlineStr">
         <is>
           <t>7番 雇用区分（給与体系は月給または時給）</t>
         </is>
       </c>
-      <c r="O49" s="13" t="inlineStr"/>
       <c r="P49" s="13" t="inlineStr"/>
       <c r="Q49" s="13" t="inlineStr"/>
       <c r="R49" s="13" t="inlineStr"/>
+      <c r="S49" s="13" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
@@ -3110,7 +3220,12 @@
           <t>新規6・更新2・エラー2と表示され、実行ボタンは「8件をインポート」と出る</t>
         </is>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="H50" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3127,40 +3242,40 @@
           </r>
         </is>
       </c>
-      <c r="I50" s="12" t="inlineStr">
+      <c r="J50" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J50" s="10" t="inlineStr">
+      <c r="K50" s="10" t="inlineStr">
         <is>
           <t>プレビュー</t>
         </is>
       </c>
-      <c r="K50" s="10" t="inlineStr">
+      <c r="L50" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L50" s="10" t="inlineStr">
+      <c r="M50" s="10" t="inlineStr">
         <is>
           <t>フローA【2】</t>
         </is>
       </c>
-      <c r="M50" s="10" t="inlineStr">
+      <c r="N50" s="10" t="inlineStr">
         <is>
           <t>CA-051</t>
         </is>
       </c>
-      <c r="N50" s="20" t="inlineStr">
+      <c r="O50" s="20" t="inlineStr">
         <is>
           <t>8番 画面上部に件数が表示されます（新規登録・更新・スキップ・エラー）</t>
         </is>
       </c>
-      <c r="O50" s="13" t="inlineStr"/>
       <c r="P50" s="13" t="inlineStr"/>
       <c r="Q50" s="13" t="inlineStr"/>
       <c r="R50" s="13" t="inlineStr"/>
+      <c r="S50" s="13" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
@@ -3198,7 +3313,12 @@
           <t>エラー行すべてに理由が表示される（理由が空のエラー行＝0件）</t>
         </is>
       </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="H51" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3209,40 +3329,40 @@
           </r>
         </is>
       </c>
-      <c r="I51" s="12" t="inlineStr">
+      <c r="J51" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J51" s="10" t="inlineStr">
+      <c r="K51" s="10" t="inlineStr">
         <is>
           <t>プレビュー</t>
         </is>
       </c>
-      <c r="K51" s="10" t="inlineStr">
+      <c r="L51" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L51" s="10" t="inlineStr">
+      <c r="M51" s="10" t="inlineStr">
         <is>
           <t>フローC</t>
         </is>
       </c>
-      <c r="M51" s="10" t="inlineStr">
+      <c r="N51" s="10" t="inlineStr">
         <is>
           <t>OP-303 / OP-304</t>
         </is>
       </c>
-      <c r="N51" s="20" t="inlineStr">
+      <c r="O51" s="20" t="inlineStr">
         <is>
           <t>11番 一部の行にエラーがある場合（赤く表示・画面上では直せません） ／ 11番 よくあるエラー（〇〇が登録されていません）</t>
         </is>
       </c>
-      <c r="O51" s="13" t="inlineStr"/>
       <c r="P51" s="13" t="inlineStr"/>
       <c r="Q51" s="13" t="inlineStr"/>
       <c r="R51" s="13" t="inlineStr"/>
+      <c r="S51" s="13" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
@@ -3280,7 +3400,12 @@
           <t>エラー行に編集ボタン＝0個。修正はCSVのみ</t>
         </is>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="H52" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3297,22 +3422,22 @@
           </r>
         </is>
       </c>
-      <c r="I52" s="12" t="inlineStr">
+      <c r="J52" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J52" s="10" t="inlineStr">
+      <c r="K52" s="10" t="inlineStr">
         <is>
           <t>プレビュー</t>
         </is>
       </c>
-      <c r="K52" s="10" t="inlineStr">
+      <c r="L52" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L52" s="10" t="inlineStr">
+      <c r="M52" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3329,20 +3454,20 @@
           </r>
         </is>
       </c>
-      <c r="M52" s="10" t="inlineStr">
+      <c r="N52" s="10" t="inlineStr">
         <is>
           <t>OP-303</t>
         </is>
       </c>
-      <c r="N52" s="20" t="inlineStr">
+      <c r="O52" s="20" t="inlineStr">
         <is>
           <t>11番 一部の行にエラーがある場合（赤く表示・画面上では直せません）</t>
         </is>
       </c>
-      <c r="O52" s="13" t="inlineStr"/>
       <c r="P52" s="13" t="inlineStr"/>
       <c r="Q52" s="13" t="inlineStr"/>
       <c r="R52" s="13" t="inlineStr"/>
+      <c r="S52" s="13" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
@@ -3380,7 +3505,12 @@
           <t>OP-306（エラー行CSVのダウンロード）元テンプレートと同じ列＋末尾に「エラー理由」列のファイルが落ちる ／ OP-307（エラー行CSVで修正して再取り込み）エラーが解消され、全件が取り込める状態になる ／ CA-053（完了画面の件数）成功7・失敗1と表示される。取り込まなかった2行も表示される。失敗行CSVは1行</t>
         </is>
       </c>
-      <c r="H53" s="10" t="inlineStr">
+      <c r="H53" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3397,40 +3527,40 @@
           </r>
         </is>
       </c>
-      <c r="I53" s="12" t="inlineStr">
+      <c r="J53" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J53" s="10" t="inlineStr">
+      <c r="K53" s="10" t="inlineStr">
         <is>
           <t>プレビュー / 完了</t>
         </is>
       </c>
-      <c r="K53" s="10" t="inlineStr">
+      <c r="L53" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L53" s="10" t="inlineStr">
+      <c r="M53" s="10" t="inlineStr">
         <is>
           <t>フローC</t>
         </is>
       </c>
-      <c r="M53" s="10" t="inlineStr">
+      <c r="N53" s="10" t="inlineStr">
         <is>
           <t>OP-306 / OP-307 / CA-053</t>
         </is>
       </c>
-      <c r="N53" s="20" t="inlineStr">
+      <c r="O53" s="20" t="inlineStr">
         <is>
           <t>11番 一部の行にエラーがある場合（エラー行をCSVでダウンロード） ／ 11番 一部の行にエラーがある場合（直し方1〜5） ／ 10番 完了画面で確認する（成功・失敗の件数）</t>
         </is>
       </c>
-      <c r="O53" s="13" t="inlineStr"/>
       <c r="P53" s="13" t="inlineStr"/>
       <c r="Q53" s="13" t="inlineStr"/>
       <c r="R53" s="13" t="inlineStr"/>
+      <c r="S53" s="13" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
@@ -3468,7 +3598,12 @@
           <t>4パターン投入 → 新規登録1・権限付与1・差し替え1・スキップ1に振り分けられる（誤判定＝0件）</t>
         </is>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="H54" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3485,22 +3620,22 @@
           </r>
         </is>
       </c>
-      <c r="I54" s="12" t="inlineStr">
+      <c r="J54" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J54" s="10" t="inlineStr">
+      <c r="K54" s="10" t="inlineStr">
         <is>
           <t>プレビュー</t>
         </is>
       </c>
-      <c r="K54" s="10" t="inlineStr">
+      <c r="L54" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L54" s="10" t="inlineStr">
+      <c r="M54" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3517,20 +3652,20 @@
           </r>
         </is>
       </c>
-      <c r="M54" s="10" t="inlineStr">
+      <c r="N54" s="10" t="inlineStr">
         <is>
           <t>OP-308</t>
         </is>
       </c>
-      <c r="N54" s="20" t="inlineStr">
+      <c r="O54" s="20" t="inlineStr">
         <is>
           <t>8番 管理者の判定について（新規登録・権限付与・差し替え・スキップ）</t>
         </is>
       </c>
-      <c r="O54" s="13" t="inlineStr"/>
       <c r="P54" s="13" t="inlineStr"/>
       <c r="Q54" s="13" t="inlineStr"/>
       <c r="R54" s="13" t="inlineStr"/>
+      <c r="S54" s="13" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
@@ -3568,7 +3703,12 @@
           <t>退職者と同じコードの行＝エラー。取り込まれた件数＝0件</t>
         </is>
       </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="H55" s="20" t="inlineStr">
+        <is>
+          <t>AC-056（指定した従業員コードがそのまま登録されること。自動採番に置き換わると本条件は判定できない）</t>
+        </is>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3585,40 +3725,40 @@
           </r>
         </is>
       </c>
-      <c r="I55" s="12" t="inlineStr">
+      <c r="J55" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J55" s="10" t="inlineStr">
+      <c r="K55" s="10" t="inlineStr">
         <is>
           <t>プレビュー</t>
         </is>
       </c>
-      <c r="K55" s="10" t="inlineStr">
+      <c r="L55" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L55" s="10" t="inlineStr">
+      <c r="M55" s="10" t="inlineStr">
         <is>
           <t>README §8.4</t>
         </is>
       </c>
-      <c r="M55" s="10" t="inlineStr">
+      <c r="N55" s="10" t="inlineStr">
         <is>
           <t>OP-310</t>
         </is>
       </c>
-      <c r="N55" s="20" t="inlineStr">
+      <c r="O55" s="20" t="inlineStr">
         <is>
           <t>11番 よくあるエラー（退職済みの従業員と同じ従業員コード） ／ 12番 退職した方を復帰させたい</t>
         </is>
       </c>
-      <c r="O55" s="13" t="inlineStr"/>
       <c r="P55" s="13" t="inlineStr"/>
       <c r="Q55" s="13" t="inlineStr"/>
       <c r="R55" s="13" t="inlineStr"/>
+      <c r="S55" s="13" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
@@ -3656,7 +3796,12 @@
           <t>0はエラー（1以上）。99999999.99は登録できる。100000000はエラー</t>
         </is>
       </c>
-      <c r="H56" s="10" t="inlineStr">
+      <c r="H56" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3673,40 +3818,40 @@
           </r>
         </is>
       </c>
-      <c r="I56" s="12" t="inlineStr">
+      <c r="J56" s="12" t="inlineStr">
         <is>
           <t>2 / 4</t>
         </is>
       </c>
-      <c r="J56" s="10" t="inlineStr">
+      <c r="K56" s="10" t="inlineStr">
         <is>
           <t>プレビュー</t>
         </is>
       </c>
-      <c r="K56" s="10" t="inlineStr">
+      <c r="L56" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L56" s="10" t="inlineStr">
+      <c r="M56" s="10" t="inlineStr">
         <is>
           <t>README §4.5-2</t>
         </is>
       </c>
-      <c r="M56" s="10" t="inlineStr">
+      <c r="N56" s="10" t="inlineStr">
         <is>
           <t>CA-016</t>
         </is>
       </c>
-      <c r="N56" s="20" t="inlineStr">
+      <c r="O56" s="20" t="inlineStr">
         <is>
           <t>7番 雇用区分（金額は1以上） ／ 11番 よくあるエラー</t>
         </is>
       </c>
-      <c r="O56" s="13" t="inlineStr"/>
       <c r="P56" s="13" t="inlineStr"/>
       <c r="Q56" s="13" t="inlineStr"/>
       <c r="R56" s="13" t="inlineStr"/>
+      <c r="S56" s="13" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
@@ -3744,7 +3889,12 @@
           <t>CA-031（従業員名の桁数）100文字は登録できる。101文字はエラー ／ CA-033（その他の桁数）いずれもエラーになり、列名と上限がメッセージに出る</t>
         </is>
       </c>
-      <c r="H57" s="10" t="inlineStr">
+      <c r="H57" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3761,40 +3911,40 @@
           </r>
         </is>
       </c>
-      <c r="I57" s="12" t="inlineStr">
+      <c r="J57" s="12" t="inlineStr">
         <is>
           <t>2 / 4</t>
         </is>
       </c>
-      <c r="J57" s="10" t="inlineStr">
+      <c r="K57" s="10" t="inlineStr">
         <is>
           <t>従業員一覧 / プレビュー</t>
         </is>
       </c>
-      <c r="K57" s="10" t="inlineStr">
+      <c r="L57" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L57" s="10" t="inlineStr">
+      <c r="M57" s="10" t="inlineStr">
         <is>
           <t>README §4.5-4</t>
         </is>
       </c>
-      <c r="M57" s="10" t="inlineStr">
+      <c r="N57" s="10" t="inlineStr">
         <is>
           <t>CA-031 / CA-033</t>
         </is>
       </c>
-      <c r="N57" s="20" t="inlineStr">
+      <c r="O57" s="20" t="inlineStr">
         <is>
           <t>—（7番 従業員に未記載。README §11.1 が確定したら追記する） ／ 7番 雇用区分（最大100文字・コード50文字） ／ 7番 店舗（営業時間200文字）</t>
         </is>
       </c>
-      <c r="O57" s="13" t="inlineStr"/>
       <c r="P57" s="13" t="inlineStr"/>
       <c r="Q57" s="13" t="inlineStr"/>
       <c r="R57" s="13" t="inlineStr"/>
+      <c r="S57" s="13" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
@@ -3832,7 +3982,12 @@
           <t>CA-036（メールアドレスの形式）エラー行として赤く表示され、「メールアドレスの形式が正しくありません」と理由が出る。取り込まれない ／ CA-041（郵便番号の形式）前2つは登録できる。3つ目はエラー ／ CA-044（電話番号の正規化と文字種）全角ハイフンは半角に正規化される。英字混じりはエラー</t>
         </is>
       </c>
-      <c r="H58" s="10" t="inlineStr">
+      <c r="H58" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3849,40 +4004,40 @@
           </r>
         </is>
       </c>
-      <c r="I58" s="12" t="inlineStr">
+      <c r="J58" s="12" t="inlineStr">
         <is>
           <t>2 / 4</t>
         </is>
       </c>
-      <c r="J58" s="10" t="inlineStr">
+      <c r="K58" s="10" t="inlineStr">
         <is>
           <t>プレビュー / 店舗設定 / 従業員一覧</t>
         </is>
       </c>
-      <c r="K58" s="10" t="inlineStr">
+      <c r="L58" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L58" s="10" t="inlineStr">
+      <c r="M58" s="10" t="inlineStr">
         <is>
           <t>README §4.5</t>
         </is>
       </c>
-      <c r="M58" s="10" t="inlineStr">
+      <c r="N58" s="10" t="inlineStr">
         <is>
           <t>CA-036 / CA-041 / CA-044</t>
         </is>
       </c>
-      <c r="N58" s="20" t="inlineStr">
+      <c r="O58" s="20" t="inlineStr">
         <is>
           <t>11番 一部の行にエラーがある場合（メールアドレスの形式） ／ 7番 店舗（郵便番号の書き方） ／ 7番 従業員（電話番号はハイフン付き）</t>
         </is>
       </c>
-      <c r="O58" s="13" t="inlineStr"/>
       <c r="P58" s="13" t="inlineStr"/>
       <c r="Q58" s="13" t="inlineStr"/>
       <c r="R58" s="13" t="inlineStr"/>
+      <c r="S58" s="13" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
@@ -3920,7 +4075,12 @@
           <t>新規＝空1行・複数行追加あり・一時保存あり・主ボタン「登録（N件）」／編集＝プリフィル・複数行なし・一時保存なし・主ボタン「更新」（食い違い＝0件）</t>
         </is>
       </c>
-      <c r="H59" s="10" t="inlineStr">
+      <c r="H59" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3937,40 +4097,40 @@
           </r>
         </is>
       </c>
-      <c r="I59" s="14" t="inlineStr">
+      <c r="J59" s="14" t="inlineStr">
         <is>
           <t>1 / 3</t>
         </is>
       </c>
-      <c r="J59" s="10" t="inlineStr">
+      <c r="K59" s="10" t="inlineStr">
         <is>
           <t>各設定画面</t>
         </is>
       </c>
-      <c r="K59" s="10" t="inlineStr">
+      <c r="L59" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L59" s="10" t="inlineStr">
+      <c r="M59" s="10" t="inlineStr">
         <is>
           <t>owner-mock §3.4.2</t>
         </is>
       </c>
-      <c r="M59" s="10" t="inlineStr">
+      <c r="N59" s="10" t="inlineStr">
         <is>
           <t>OP-027</t>
         </is>
       </c>
-      <c r="N59" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O59" s="13" t="inlineStr"/>
+      <c r="O59" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="P59" s="13" t="inlineStr"/>
       <c r="Q59" s="13" t="inlineStr"/>
       <c r="R59" s="13" t="inlineStr"/>
+      <c r="S59" s="13" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
@@ -4008,7 +4168,12 @@
           <t>登録すると選択肢に出現し、削除すると消える（削除後に残る件数＝0件）</t>
         </is>
       </c>
-      <c r="H60" s="10" t="inlineStr">
+      <c r="H60" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I60" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4025,40 +4190,40 @@
           </r>
         </is>
       </c>
-      <c r="I60" s="14" t="inlineStr">
+      <c r="J60" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J60" s="10" t="inlineStr">
+      <c r="K60" s="10" t="inlineStr">
         <is>
           <t>各設定画面</t>
         </is>
       </c>
-      <c r="K60" s="10" t="inlineStr">
+      <c r="L60" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L60" s="10" t="inlineStr">
+      <c r="M60" s="10" t="inlineStr">
         <is>
           <t>owner-mock §3.4.3</t>
         </is>
       </c>
-      <c r="M60" s="10" t="inlineStr">
+      <c r="N60" s="10" t="inlineStr">
         <is>
           <t>OP-026</t>
         </is>
       </c>
-      <c r="N60" s="20" t="inlineStr">
+      <c r="O60" s="20" t="inlineStr">
         <is>
           <t>1番 はじめて登録するときの順番（先に必要なもの）</t>
         </is>
       </c>
-      <c r="O60" s="13" t="inlineStr"/>
       <c r="P60" s="13" t="inlineStr"/>
       <c r="Q60" s="13" t="inlineStr"/>
       <c r="R60" s="13" t="inlineStr"/>
+      <c r="S60" s="13" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
@@ -4096,7 +4261,12 @@
           <t>エラー行を直して再アップロードすると受理され、取り込める（やり直しになった回数＝0回）</t>
         </is>
       </c>
-      <c r="H61" s="10" t="inlineStr">
+      <c r="H61" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I61" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4113,40 +4283,40 @@
           </r>
         </is>
       </c>
-      <c r="I61" s="12" t="inlineStr">
+      <c r="J61" s="12" t="inlineStr">
         <is>
           <t>2 / 4</t>
         </is>
       </c>
-      <c r="J61" s="10" t="inlineStr">
+      <c r="K61" s="10" t="inlineStr">
         <is>
           <t>プレビュー／アップロード</t>
         </is>
       </c>
-      <c r="K61" s="10" t="inlineStr">
+      <c r="L61" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L61" s="10" t="inlineStr">
+      <c r="M61" s="10" t="inlineStr">
         <is>
           <t>フローC／フローH／仕様書「新規登録と運用更新の違い」</t>
         </is>
       </c>
-      <c r="M61" s="10" t="inlineStr">
+      <c r="N61" s="10" t="inlineStr">
         <is>
           <t>OP-306 / OP-307 / OP-219</t>
         </is>
       </c>
-      <c r="N61" s="20" t="inlineStr">
+      <c r="O61" s="20" t="inlineStr">
         <is>
           <t>11番 一部の行にエラーがある場合（エラー行をCSVでダウンロード） ／ 11番 一部の行にエラーがある場合（直し方1〜5） ／ 11番 ファイルが受け付けられない場合（直して再アップロード）</t>
         </is>
       </c>
-      <c r="O61" s="13" t="inlineStr"/>
       <c r="P61" s="13" t="inlineStr"/>
       <c r="Q61" s="13" t="inlineStr"/>
       <c r="R61" s="13" t="inlineStr"/>
+      <c r="S61" s="13" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
@@ -4184,45 +4354,50 @@
           <t>OP-108（設定マスタの重複排除）重複が自動で除外され、1件として登録される ／ CA-056（重複排除後の件数）3件として登録される</t>
         </is>
       </c>
-      <c r="H62" s="10" t="inlineStr">
+      <c r="H62" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I62" s="10" t="inlineStr">
         <is>
           <t>同じ業態が2件登録され、以後の参照が壊れる</t>
         </is>
       </c>
-      <c r="I62" s="12" t="inlineStr">
+      <c r="J62" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J62" s="10" t="inlineStr">
+      <c r="K62" s="10" t="inlineStr">
         <is>
           <t>プレビュー / 業態設定</t>
         </is>
       </c>
-      <c r="K62" s="10" t="inlineStr">
+      <c r="L62" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L62" s="10" t="inlineStr">
+      <c r="M62" s="10" t="inlineStr">
         <is>
           <t>README §4.1</t>
         </is>
       </c>
-      <c r="M62" s="10" t="inlineStr">
+      <c r="N62" s="10" t="inlineStr">
         <is>
           <t>OP-108 / CA-056</t>
         </is>
       </c>
-      <c r="N62" s="20" t="inlineStr">
+      <c r="O62" s="20" t="inlineStr">
         <is>
           <t>7番 業態（同じ業態名は重複を自動で除外） ／ 7番 業態（重複は自動で除外されます）</t>
         </is>
       </c>
-      <c r="O62" s="13" t="inlineStr"/>
       <c r="P62" s="13" t="inlineStr"/>
       <c r="Q62" s="13" t="inlineStr"/>
       <c r="R62" s="13" t="inlineStr"/>
+      <c r="S62" s="13" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
@@ -4260,45 +4435,50 @@
           <t>DB側に同名の業態が2件ある状態で取り込む → その行＝エラー（誤って紐づく件数＝0件）</t>
         </is>
       </c>
-      <c r="H63" s="10" t="inlineStr">
+      <c r="H63" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I63" s="10" t="inlineStr">
         <is>
           <t>同名の業態のどちらに紐づくか不定になり、店舗が誤った業態に入る</t>
         </is>
       </c>
-      <c r="I63" s="12" t="inlineStr">
+      <c r="J63" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J63" s="10" t="inlineStr">
+      <c r="K63" s="10" t="inlineStr">
         <is>
           <t>プレビュー</t>
         </is>
       </c>
-      <c r="K63" s="10" t="inlineStr">
+      <c r="L63" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L63" s="10" t="inlineStr">
+      <c r="M63" s="10" t="inlineStr">
         <is>
           <t>README §4.5-6</t>
         </is>
       </c>
-      <c r="M63" s="10" t="inlineStr">
+      <c r="N63" s="10" t="inlineStr">
         <is>
           <t>OP-312</t>
         </is>
       </c>
-      <c r="N63" s="20" t="inlineStr">
+      <c r="O63" s="20" t="inlineStr">
         <is>
           <t>11番 よくあるエラー（〇〇が登録されていません）</t>
         </is>
       </c>
-      <c r="O63" s="13" t="inlineStr"/>
       <c r="P63" s="13" t="inlineStr"/>
       <c r="Q63" s="13" t="inlineStr"/>
       <c r="R63" s="13" t="inlineStr"/>
+      <c r="S63" s="13" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
@@ -4336,45 +4516,50 @@
           <t>④のCSVに「渋谷店,新宿店」と書いた行はエラーになる（取り込まれた件数＝0件）。2店舗目は取り込み後に従業員一覧から追加して所属＝2件になる</t>
         </is>
       </c>
-      <c r="H64" s="10" t="inlineStr">
+      <c r="H64" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I64" s="10" t="inlineStr">
         <is>
           <t>複数店舗を書いて取り込めず、原因が分からない</t>
         </is>
       </c>
-      <c r="I64" s="12" t="inlineStr">
+      <c r="J64" s="12" t="inlineStr">
         <is>
           <t>2 / 3</t>
         </is>
       </c>
-      <c r="J64" s="10" t="inlineStr">
+      <c r="K64" s="10" t="inlineStr">
         <is>
           <t>プレビュー / 従業員一覧</t>
         </is>
       </c>
-      <c r="K64" s="10" t="inlineStr">
+      <c r="L64" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L64" s="10" t="inlineStr">
+      <c r="M64" s="10" t="inlineStr">
         <is>
           <t>README §8.3</t>
         </is>
       </c>
-      <c r="M64" s="10" t="inlineStr">
+      <c r="N64" s="10" t="inlineStr">
         <is>
           <t>OP-311 / OP-608</t>
         </is>
       </c>
-      <c r="N64" s="20" t="inlineStr">
+      <c r="O64" s="20" t="inlineStr">
         <is>
           <t>7番 従業員（店舗名は1店舗のみ） ／ 12番 1人を複数の店舗に所属させたい ／ 12番 1人を複数の店舗に所属させたい（2店舗目以降は従業員一覧から）</t>
         </is>
       </c>
-      <c r="O64" s="13" t="inlineStr"/>
       <c r="P64" s="13" t="inlineStr"/>
       <c r="Q64" s="13" t="inlineStr"/>
       <c r="R64" s="13" t="inlineStr"/>
+      <c r="S64" s="13" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
@@ -4412,45 +4597,50 @@
           <t>CA-014（金額の正規化）どちらも 200000 として登録される ／ CA-015（金額の正規化（不可））エラー。「金額は半角数字で入力してください」</t>
         </is>
       </c>
-      <c r="H65" s="10" t="inlineStr">
+      <c r="H65" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I65" s="10" t="inlineStr">
         <is>
           <t>「200,000」がエラーになり、顧客が原因を特定できない</t>
         </is>
       </c>
-      <c r="I65" s="12" t="inlineStr">
+      <c r="J65" s="12" t="inlineStr">
         <is>
           <t>2 / 4</t>
         </is>
       </c>
-      <c r="J65" s="10" t="inlineStr">
+      <c r="K65" s="10" t="inlineStr">
         <is>
           <t>雇用区分設定 / プレビュー</t>
         </is>
       </c>
-      <c r="K65" s="10" t="inlineStr">
+      <c r="L65" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L65" s="10" t="inlineStr">
+      <c r="M65" s="10" t="inlineStr">
         <is>
           <t>README §4.5-3</t>
         </is>
       </c>
-      <c r="M65" s="10" t="inlineStr">
+      <c r="N65" s="10" t="inlineStr">
         <is>
           <t>CA-014 / CA-015</t>
         </is>
       </c>
-      <c r="N65" s="20" t="inlineStr">
+      <c r="O65" s="20" t="inlineStr">
         <is>
           <t>7番 雇用区分（カンマや円記号を付けても取り込めます） ／ 11番 よくあるエラー（金額は半角数字で）</t>
         </is>
       </c>
-      <c r="O65" s="13" t="inlineStr"/>
       <c r="P65" s="13" t="inlineStr"/>
       <c r="Q65" s="13" t="inlineStr"/>
       <c r="R65" s="13" t="inlineStr"/>
+      <c r="S65" s="13" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
@@ -4488,45 +4678,50 @@
           <t>CA-021（月次契約労働時間の範囲）0と1000はエラー。160は登録できる ／ CA-024（月みなし残業時間の範囲）0と999は登録できる。1000はエラー。「20時間」は単位付きのためエラー</t>
         </is>
       </c>
-      <c r="H66" s="10" t="inlineStr">
+      <c r="H66" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I66" s="10" t="inlineStr">
         <is>
           <t>契約労働時間0で登録され、残業計算が破綻する</t>
         </is>
       </c>
-      <c r="I66" s="12" t="inlineStr">
+      <c r="J66" s="12" t="inlineStr">
         <is>
           <t>2 / 4</t>
         </is>
       </c>
-      <c r="J66" s="10" t="inlineStr">
+      <c r="K66" s="10" t="inlineStr">
         <is>
           <t>プレビュー / 雇用区分設定</t>
         </is>
       </c>
-      <c r="K66" s="10" t="inlineStr">
+      <c r="L66" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L66" s="10" t="inlineStr">
+      <c r="M66" s="10" t="inlineStr">
         <is>
           <t>README §4.5-3</t>
         </is>
       </c>
-      <c r="M66" s="10" t="inlineStr">
+      <c r="N66" s="10" t="inlineStr">
         <is>
           <t>CA-021 / CA-024</t>
         </is>
       </c>
-      <c r="N66" s="20" t="inlineStr">
+      <c r="O66" s="20" t="inlineStr">
         <is>
           <t>7番 雇用区分（月次契約労働時間1〜999） ／ 11番 よくあるエラー ／ 7番 雇用区分（月みなし残業時間の単位は時間）</t>
         </is>
       </c>
-      <c r="O66" s="13" t="inlineStr"/>
       <c r="P66" s="13" t="inlineStr"/>
       <c r="Q66" s="13" t="inlineStr"/>
       <c r="R66" s="13" t="inlineStr"/>
+      <c r="S66" s="13" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
@@ -4564,45 +4759,50 @@
           <t>①〜③＝種別タブ、④⑤＝判定タブ。タブ構成の取り違え＝0件</t>
         </is>
       </c>
-      <c r="H67" s="10" t="inlineStr">
+      <c r="H67" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I67" s="10" t="inlineStr">
         <is>
           <t>タブの役割が種別と判定で混在し、読み違える</t>
         </is>
       </c>
-      <c r="I67" s="12" t="inlineStr">
+      <c r="J67" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J67" s="10" t="inlineStr">
+      <c r="K67" s="10" t="inlineStr">
         <is>
           <t>プレビュー</t>
         </is>
       </c>
-      <c r="K67" s="10" t="inlineStr">
+      <c r="L67" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L67" s="10" t="inlineStr">
+      <c r="M67" s="10" t="inlineStr">
         <is>
           <t>仕様書 7.2</t>
         </is>
       </c>
-      <c r="M67" s="10" t="inlineStr">
+      <c r="N67" s="10" t="inlineStr">
         <is>
           <t>OP-301</t>
         </is>
       </c>
-      <c r="N67" s="20" t="inlineStr">
+      <c r="O67" s="20" t="inlineStr">
         <is>
           <t>8番 内容を確認する</t>
         </is>
       </c>
-      <c r="O67" s="13" t="inlineStr"/>
       <c r="P67" s="13" t="inlineStr"/>
       <c r="Q67" s="13" t="inlineStr"/>
       <c r="R67" s="13" t="inlineStr"/>
+      <c r="S67" s="13" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
@@ -4640,45 +4840,50 @@
           <t>「 飲食店 」（前後空白）で取り込む → 引き当て成功。エラー＝0件</t>
         </is>
       </c>
-      <c r="H68" s="10" t="inlineStr">
+      <c r="H68" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="10" t="inlineStr">
         <is>
           <t>前後の空白で引き当てに失敗する。Excelの貼り付けで頻出</t>
         </is>
       </c>
-      <c r="I68" s="12" t="inlineStr">
+      <c r="J68" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J68" s="10" t="inlineStr">
+      <c r="K68" s="10" t="inlineStr">
         <is>
           <t>プレビュー</t>
         </is>
       </c>
-      <c r="K68" s="10" t="inlineStr">
+      <c r="L68" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L68" s="10" t="inlineStr">
+      <c r="M68" s="10" t="inlineStr">
         <is>
           <t>README §4.5-6</t>
         </is>
       </c>
-      <c r="M68" s="10" t="inlineStr">
+      <c r="N68" s="10" t="inlineStr">
         <is>
           <t>OP-312</t>
         </is>
       </c>
-      <c r="N68" s="20" t="inlineStr">
+      <c r="O68" s="20" t="inlineStr">
         <is>
           <t>11番 よくあるエラー（〇〇が登録されていません）</t>
         </is>
       </c>
-      <c r="O68" s="13" t="inlineStr"/>
       <c r="P68" s="13" t="inlineStr"/>
       <c r="Q68" s="13" t="inlineStr"/>
       <c r="R68" s="13" t="inlineStr"/>
+      <c r="S68" s="13" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
@@ -4716,45 +4921,50 @@
           <t>「判定の見方」が既定で閉じている（開いた状態で表示される画面＝0件）</t>
         </is>
       </c>
-      <c r="H69" s="10" t="inlineStr">
+      <c r="H69" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="10" t="inlineStr">
         <is>
           <t>凡例が常時出て一覧が読みにくい</t>
         </is>
       </c>
-      <c r="I69" s="12" t="inlineStr">
+      <c r="J69" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J69" s="10" t="inlineStr">
+      <c r="K69" s="10" t="inlineStr">
         <is>
           <t>プレビュー</t>
         </is>
       </c>
-      <c r="K69" s="10" t="inlineStr">
+      <c r="L69" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L69" s="10" t="inlineStr">
+      <c r="M69" s="10" t="inlineStr">
         <is>
           <t>仕様書 4.2</t>
         </is>
       </c>
-      <c r="M69" s="10" t="inlineStr">
+      <c r="N69" s="10" t="inlineStr">
         <is>
           <t>OP-308</t>
         </is>
       </c>
-      <c r="N69" s="20" t="inlineStr">
+      <c r="O69" s="20" t="inlineStr">
         <is>
           <t>8番 管理者の判定について（新規登録・権限付与・差し替え・スキップ）</t>
         </is>
       </c>
-      <c r="O69" s="13" t="inlineStr"/>
       <c r="P69" s="13" t="inlineStr"/>
       <c r="Q69" s="13" t="inlineStr"/>
       <c r="R69" s="13" t="inlineStr"/>
+      <c r="S69" s="13" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
@@ -4792,7 +5002,12 @@
           <t>ボタンを5回連打 → 登録された件数＝1回分（重複登録＝0件）</t>
         </is>
       </c>
-      <c r="H70" s="10" t="inlineStr">
+      <c r="H70" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4809,40 +5024,40 @@
           </r>
         </is>
       </c>
-      <c r="I70" s="12" t="inlineStr">
+      <c r="J70" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J70" s="10" t="inlineStr">
+      <c r="K70" s="10" t="inlineStr">
         <is>
           <t>実行中</t>
         </is>
       </c>
-      <c r="K70" s="10" t="inlineStr">
+      <c r="L70" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L70" s="10" t="inlineStr">
+      <c r="M70" s="10" t="inlineStr">
         <is>
           <t>README §9.1</t>
         </is>
       </c>
-      <c r="M70" s="10" t="inlineStr">
+      <c r="N70" s="10" t="inlineStr">
         <is>
           <t>OP-401</t>
         </is>
       </c>
-      <c r="N70" s="20" t="inlineStr">
+      <c r="O70" s="20" t="inlineStr">
         <is>
           <t>9番 取り込みを実行する</t>
         </is>
       </c>
-      <c r="O70" s="13" t="inlineStr"/>
       <c r="P70" s="13" t="inlineStr"/>
       <c r="Q70" s="13" t="inlineStr"/>
       <c r="R70" s="13" t="inlineStr"/>
+      <c r="S70" s="13" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
@@ -4880,7 +5095,12 @@
           <t>OP-502（取り込まなかった行の開示）完了画面に「取り込まなかった行（N件）」が表示され、除外理由が分かる ／ CA-053（完了画面の件数）成功7・失敗1と表示される。取り込まなかった2行も表示される。失敗行CSVは1行</t>
         </is>
       </c>
-      <c r="H71" s="10" t="inlineStr">
+      <c r="H71" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4897,40 +5117,40 @@
           </r>
         </is>
       </c>
-      <c r="I71" s="12" t="inlineStr">
+      <c r="J71" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J71" s="10" t="inlineStr">
+      <c r="K71" s="10" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K71" s="10" t="inlineStr">
+      <c r="L71" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L71" s="10" t="inlineStr">
+      <c r="M71" s="10" t="inlineStr">
         <is>
           <t>README §7.7</t>
         </is>
       </c>
-      <c r="M71" s="10" t="inlineStr">
+      <c r="N71" s="10" t="inlineStr">
         <is>
           <t>OP-502 / CA-053</t>
         </is>
       </c>
-      <c r="N71" s="20" t="inlineStr">
+      <c r="O71" s="20" t="inlineStr">
         <is>
           <t>10番 確認画面で除いた行 ／ 11番 エラー行を除いてインポート実行 ／ 10番 完了画面で確認する（成功・失敗の件数）</t>
         </is>
       </c>
-      <c r="O71" s="13" t="inlineStr"/>
       <c r="P71" s="13" t="inlineStr"/>
       <c r="Q71" s="13" t="inlineStr"/>
       <c r="R71" s="13" t="inlineStr"/>
+      <c r="S71" s="13" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
@@ -4968,7 +5188,12 @@
           <t>OP-503（失敗行CSVのダウンロードと書式）失敗した行だけが落ちる。文字化けせず、失敗理由の列が付いている ／ CA-053（完了画面の件数）成功7・失敗1と表示される。取り込まなかった2行も表示される。失敗行CSVは1行</t>
         </is>
       </c>
-      <c r="H72" s="10" t="inlineStr">
+      <c r="H72" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4985,40 +5210,40 @@
           </r>
         </is>
       </c>
-      <c r="I72" s="12" t="inlineStr">
+      <c r="J72" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J72" s="10" t="inlineStr">
+      <c r="K72" s="10" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K72" s="10" t="inlineStr">
+      <c r="L72" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L72" s="10" t="inlineStr">
+      <c r="M72" s="10" t="inlineStr">
         <is>
           <t>フローC／README §7.7</t>
         </is>
       </c>
-      <c r="M72" s="10" t="inlineStr">
+      <c r="N72" s="10" t="inlineStr">
         <is>
           <t>OP-503 / CA-053</t>
         </is>
       </c>
-      <c r="N72" s="20" t="inlineStr">
+      <c r="O72" s="20" t="inlineStr">
         <is>
           <t>10番 一部が登録できなかった場合 ／ 10番 完了画面で確認する（成功・失敗の件数）</t>
         </is>
       </c>
-      <c r="O72" s="13" t="inlineStr"/>
       <c r="P72" s="13" t="inlineStr"/>
       <c r="Q72" s="13" t="inlineStr"/>
       <c r="R72" s="13" t="inlineStr"/>
+      <c r="S72" s="13" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
@@ -5056,7 +5281,12 @@
           <t>部分成功後、失敗した行のレコード数＝0件。失敗行CSVの行数＝失敗件数と一致</t>
         </is>
       </c>
-      <c r="H73" s="10" t="inlineStr">
+      <c r="H73" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5073,22 +5303,22 @@
           </r>
         </is>
       </c>
-      <c r="I73" s="12" t="inlineStr">
+      <c r="J73" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J73" s="10" t="inlineStr">
+      <c r="K73" s="10" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K73" s="10" t="inlineStr">
+      <c r="L73" s="10" t="inlineStr">
         <is>
           <t>動作確認＋DB確認</t>
         </is>
       </c>
-      <c r="L73" s="10" t="inlineStr">
+      <c r="M73" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5105,20 +5335,20 @@
           </r>
         </is>
       </c>
-      <c r="M73" s="10" t="inlineStr">
+      <c r="N73" s="10" t="inlineStr">
         <is>
           <t>OP-503</t>
         </is>
       </c>
-      <c r="N73" s="20" t="inlineStr">
+      <c r="O73" s="20" t="inlineStr">
         <is>
           <t>10番 一部が登録できなかった場合</t>
         </is>
       </c>
-      <c r="O73" s="13" t="inlineStr"/>
       <c r="P73" s="13" t="inlineStr"/>
       <c r="Q73" s="13" t="inlineStr"/>
       <c r="R73" s="13" t="inlineStr"/>
+      <c r="S73" s="13" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
@@ -5156,7 +5386,12 @@
           <t>5種別すべてが登録され、招待メールが届き、従業員が打刻画面に到達できる</t>
         </is>
       </c>
-      <c r="H74" s="10" t="inlineStr">
+      <c r="H74" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5173,40 +5408,40 @@
           </r>
         </is>
       </c>
-      <c r="I74" s="12" t="inlineStr">
+      <c r="J74" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J74" s="10" t="inlineStr">
+      <c r="K74" s="10" t="inlineStr">
         <is>
           <t>全画面（通し）</t>
         </is>
       </c>
-      <c r="K74" s="10" t="inlineStr">
+      <c r="L74" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L74" s="10" t="inlineStr">
+      <c r="M74" s="10" t="inlineStr">
         <is>
           <t>仕様書 1.1 何を解決しているか</t>
         </is>
       </c>
-      <c r="M74" s="10" t="inlineStr">
+      <c r="N74" s="10" t="inlineStr">
         <is>
           <t>OP-620</t>
         </is>
       </c>
-      <c r="N74" s="20" t="inlineStr">
+      <c r="O74" s="20" t="inlineStr">
         <is>
           <t>3番 はじめて登録する方へ（CSVで一括登録） ／ 10番 招待メールを送る</t>
         </is>
       </c>
-      <c r="O74" s="13" t="inlineStr"/>
       <c r="P74" s="13" t="inlineStr"/>
       <c r="Q74" s="13" t="inlineStr"/>
       <c r="R74" s="13" t="inlineStr"/>
+      <c r="S74" s="13" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
@@ -5244,7 +5479,12 @@
           <t>CSVを使わず①〜④を登録し、4項目完了・運用更新モードへ切替・招待メール送信までできる</t>
         </is>
       </c>
-      <c r="H75" s="10" t="inlineStr">
+      <c r="H75" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5261,40 +5501,40 @@
           </r>
         </is>
       </c>
-      <c r="I75" s="14" t="inlineStr">
+      <c r="J75" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J75" s="10" t="inlineStr">
+      <c r="K75" s="10" t="inlineStr">
         <is>
           <t>初期セットアップ（通し）</t>
         </is>
       </c>
-      <c r="K75" s="10" t="inlineStr">
+      <c r="L75" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L75" s="10" t="inlineStr">
+      <c r="M75" s="10" t="inlineStr">
         <is>
           <t>owner-mock §3.3／仕様書 1.1</t>
         </is>
       </c>
-      <c r="M75" s="10" t="inlineStr">
+      <c r="N75" s="10" t="inlineStr">
         <is>
           <t>OP-031</t>
         </is>
       </c>
-      <c r="N75" s="20" t="inlineStr">
+      <c r="O75" s="20" t="inlineStr">
         <is>
           <t>2番 登録の手順（4種類そろえば打刻を始められます）</t>
         </is>
       </c>
-      <c r="O75" s="13" t="inlineStr"/>
       <c r="P75" s="13" t="inlineStr"/>
       <c r="Q75" s="13" t="inlineStr"/>
       <c r="R75" s="13" t="inlineStr"/>
+      <c r="S75" s="13" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
@@ -5332,7 +5572,12 @@
           <t>従業員と管理者の両方で登録しても招待メール＝1通（2通目＝0通）。1アカウントに両方の権限が付く</t>
         </is>
       </c>
-      <c r="H76" s="10" t="inlineStr">
+      <c r="H76" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5349,40 +5594,40 @@
           </r>
         </is>
       </c>
-      <c r="I76" s="14" t="inlineStr">
+      <c r="J76" s="14" t="inlineStr">
         <is>
           <t>1 / 3</t>
         </is>
       </c>
-      <c r="J76" s="10" t="inlineStr">
+      <c r="K76" s="10" t="inlineStr">
         <is>
           <t>従業員一覧／管理者一覧／メール</t>
         </is>
       </c>
-      <c r="K76" s="10" t="inlineStr">
+      <c r="L76" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L76" s="10" t="inlineStr">
+      <c r="M76" s="10" t="inlineStr">
         <is>
           <t>owner-mock §16 アカウント衝突回避</t>
         </is>
       </c>
-      <c r="M76" s="10" t="inlineStr">
+      <c r="N76" s="10" t="inlineStr">
         <is>
           <t>OP-032</t>
         </is>
       </c>
-      <c r="N76" s="20" t="inlineStr">
+      <c r="O76" s="20" t="inlineStr">
         <is>
           <t>7番 管理者（同じメールアドレス） ／ 14番 同じ方が2人登録されてしまった</t>
         </is>
       </c>
-      <c r="O76" s="13" t="inlineStr"/>
       <c r="P76" s="13" t="inlineStr"/>
       <c r="Q76" s="13" t="inlineStr"/>
       <c r="R76" s="13" t="inlineStr"/>
+      <c r="S76" s="13" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
@@ -5420,45 +5665,50 @@
           <t>実行中に進捗が表示される（進捗が出ない実行＝0件）</t>
         </is>
       </c>
-      <c r="H77" s="10" t="inlineStr">
+      <c r="H77" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="10" t="inlineStr">
         <is>
           <t>固まったと思って離脱・再実行される</t>
         </is>
       </c>
-      <c r="I77" s="12" t="inlineStr">
+      <c r="J77" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J77" s="10" t="inlineStr">
+      <c r="K77" s="10" t="inlineStr">
         <is>
           <t>実行中</t>
         </is>
       </c>
-      <c r="K77" s="10" t="inlineStr">
+      <c r="L77" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L77" s="10" t="inlineStr">
+      <c r="M77" s="10" t="inlineStr">
         <is>
           <t>README §9.1</t>
         </is>
       </c>
-      <c r="M77" s="10" t="inlineStr">
+      <c r="N77" s="10" t="inlineStr">
         <is>
           <t>OP-401</t>
         </is>
       </c>
-      <c r="N77" s="20" t="inlineStr">
+      <c r="O77" s="20" t="inlineStr">
         <is>
           <t>9番 取り込みを実行する</t>
         </is>
       </c>
-      <c r="O77" s="13" t="inlineStr"/>
       <c r="P77" s="13" t="inlineStr"/>
       <c r="Q77" s="13" t="inlineStr"/>
       <c r="R77" s="13" t="inlineStr"/>
+      <c r="S77" s="13" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
@@ -5496,45 +5746,50 @@
           <t>OP-404（取り込み対象0件）実行ボタンが押せない状態になり「取り込めるデータが1件もありません」と表示される ／ CA-051（プレビューの件数集計）新規6・更新2・エラー2と表示され、実行ボタンは「8件をインポート」と出る</t>
         </is>
       </c>
-      <c r="H78" s="10" t="inlineStr">
+      <c r="H78" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="10" t="inlineStr">
         <is>
           <t>0件で実行でき、「完了」と出て顧客が混乱する</t>
         </is>
       </c>
-      <c r="I78" s="12" t="inlineStr">
+      <c r="J78" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J78" s="10" t="inlineStr">
+      <c r="K78" s="10" t="inlineStr">
         <is>
           <t>プレビュー</t>
         </is>
       </c>
-      <c r="K78" s="10" t="inlineStr">
+      <c r="L78" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L78" s="10" t="inlineStr">
+      <c r="M78" s="10" t="inlineStr">
         <is>
           <t>README §9.4</t>
         </is>
       </c>
-      <c r="M78" s="10" t="inlineStr">
+      <c r="N78" s="10" t="inlineStr">
         <is>
           <t>OP-404 / CA-051</t>
         </is>
       </c>
-      <c r="N78" s="20" t="inlineStr">
+      <c r="O78" s="20" t="inlineStr">
         <is>
           <t>11番 ファイルが受け付けられない場合（取り込めるデータが1件もありません） ／ 8番 画面上部に件数が表示されます（新規登録・更新・スキップ・エラー）</t>
         </is>
       </c>
-      <c r="O78" s="13" t="inlineStr"/>
       <c r="P78" s="13" t="inlineStr"/>
       <c r="Q78" s="13" t="inlineStr"/>
       <c r="R78" s="13" t="inlineStr"/>
+      <c r="S78" s="13" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
@@ -5572,45 +5827,50 @@
           <t>成功7・失敗1と件数が表示される。取り込まなかった2行も表示される。失敗行CSVは1行（件数の食い違い＝0件）。「次にやること」は AC-045、履歴は AC-048 で判定する</t>
         </is>
       </c>
-      <c r="H79" s="10" t="inlineStr">
+      <c r="H79" s="20" t="inlineStr">
+        <is>
+          <t>—（「次にやること」は AC-045、履歴は AC-048 が判定する。前提ではない）</t>
+        </is>
+      </c>
+      <c r="I79" s="10" t="inlineStr">
         <is>
           <t>成功したのか失敗したのか分からない</t>
         </is>
       </c>
-      <c r="I79" s="12" t="inlineStr">
+      <c r="J79" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J79" s="10" t="inlineStr">
+      <c r="K79" s="10" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K79" s="10" t="inlineStr">
+      <c r="L79" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L79" s="10" t="inlineStr">
+      <c r="M79" s="10" t="inlineStr">
         <is>
           <t>フローA【4】</t>
         </is>
       </c>
-      <c r="M79" s="10" t="inlineStr">
+      <c r="N79" s="10" t="inlineStr">
         <is>
           <t>OP-501 / CA-053</t>
         </is>
       </c>
-      <c r="N79" s="20" t="inlineStr">
+      <c r="O79" s="20" t="inlineStr">
         <is>
           <t>10番 完了画面で確認する ／ 10番 完了画面で確認する（成功・失敗の件数）</t>
         </is>
       </c>
-      <c r="O79" s="13" t="inlineStr"/>
       <c r="P79" s="13" t="inlineStr"/>
       <c r="Q79" s="13" t="inlineStr"/>
       <c r="R79" s="13" t="inlineStr"/>
+      <c r="S79" s="13" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
@@ -5648,45 +5908,50 @@
           <t>失敗行CSVの列数＝元テンプレート＋1（理由列）。理由列を削除して再アップ → 受理される</t>
         </is>
       </c>
-      <c r="H80" s="10" t="inlineStr">
+      <c r="H80" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="10" t="inlineStr">
         <is>
           <t>落としたCSVをそのまま直せず、手作業で作り直しになる</t>
         </is>
       </c>
-      <c r="I80" s="12" t="inlineStr">
+      <c r="J80" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J80" s="10" t="inlineStr">
+      <c r="K80" s="10" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K80" s="10" t="inlineStr">
+      <c r="L80" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L80" s="10" t="inlineStr">
+      <c r="M80" s="10" t="inlineStr">
         <is>
           <t>フローC</t>
         </is>
       </c>
-      <c r="M80" s="10" t="inlineStr">
+      <c r="N80" s="10" t="inlineStr">
         <is>
           <t>OP-503</t>
         </is>
       </c>
-      <c r="N80" s="20" t="inlineStr">
+      <c r="O80" s="20" t="inlineStr">
         <is>
           <t>10番 一部が登録できなかった場合</t>
         </is>
       </c>
-      <c r="O80" s="13" t="inlineStr"/>
       <c r="P80" s="13" t="inlineStr"/>
       <c r="Q80" s="13" t="inlineStr"/>
       <c r="R80" s="13" t="inlineStr"/>
+      <c r="S80" s="13" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
@@ -5724,45 +5989,50 @@
           <t>新規登録者にのみ送信（既存者・スキップ判定者への送信＝0件）</t>
         </is>
       </c>
-      <c r="H81" s="10" t="inlineStr">
+      <c r="H81" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="10" t="inlineStr">
         <is>
           <t>登録しても誰もログインできない</t>
         </is>
       </c>
-      <c r="I81" s="12" t="inlineStr">
+      <c r="J81" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J81" s="10" t="inlineStr">
+      <c r="K81" s="10" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K81" s="10" t="inlineStr">
+      <c r="L81" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L81" s="10" t="inlineStr">
+      <c r="M81" s="10" t="inlineStr">
         <is>
           <t>フローA【4】</t>
         </is>
       </c>
-      <c r="M81" s="10" t="inlineStr">
+      <c r="N81" s="10" t="inlineStr">
         <is>
           <t>OP-505</t>
         </is>
       </c>
-      <c r="N81" s="20" t="inlineStr">
+      <c r="O81" s="20" t="inlineStr">
         <is>
           <t>10番 招待メールを送る</t>
         </is>
       </c>
-      <c r="O81" s="13" t="inlineStr"/>
       <c r="P81" s="13" t="inlineStr"/>
       <c r="Q81" s="13" t="inlineStr"/>
       <c r="R81" s="13" t="inlineStr"/>
+      <c r="S81" s="13" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
@@ -5800,45 +6070,50 @@
           <t>実行中にタブを閉じようとすると警告が出る（警告なしで閉じられた回数＝0回）</t>
         </is>
       </c>
-      <c r="H82" s="10" t="inlineStr">
+      <c r="H82" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="10" t="inlineStr">
         <is>
           <t>実行中に離脱され、途中状態になる</t>
         </is>
       </c>
-      <c r="I82" s="12" t="inlineStr">
+      <c r="J82" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J82" s="10" t="inlineStr">
+      <c r="K82" s="10" t="inlineStr">
         <is>
           <t>実行中</t>
         </is>
       </c>
-      <c r="K82" s="10" t="inlineStr">
+      <c r="L82" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L82" s="10" t="inlineStr">
+      <c r="M82" s="10" t="inlineStr">
         <is>
           <t>README §9.2</t>
         </is>
       </c>
-      <c r="M82" s="10" t="inlineStr">
+      <c r="N82" s="10" t="inlineStr">
         <is>
           <t>OP-401</t>
         </is>
       </c>
-      <c r="N82" s="20" t="inlineStr">
+      <c r="O82" s="20" t="inlineStr">
         <is>
           <t>9番 取り込みを実行する</t>
         </is>
       </c>
-      <c r="O82" s="13" t="inlineStr"/>
       <c r="P82" s="13" t="inlineStr"/>
       <c r="Q82" s="13" t="inlineStr"/>
       <c r="R82" s="13" t="inlineStr"/>
+      <c r="S82" s="13" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
@@ -5876,45 +6151,50 @@
           <t>完了画面に「次にやること」が表示される（案内が出ない完了画面＝0件）</t>
         </is>
       </c>
-      <c r="H83" s="10" t="inlineStr">
+      <c r="H83" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="10" t="inlineStr">
         <is>
           <t>次に何をすればいいか分からず、複数店舗の設定が漏れる</t>
         </is>
       </c>
-      <c r="I83" s="12" t="inlineStr">
+      <c r="J83" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J83" s="10" t="inlineStr">
+      <c r="K83" s="10" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K83" s="10" t="inlineStr">
+      <c r="L83" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L83" s="10" t="inlineStr">
+      <c r="M83" s="10" t="inlineStr">
         <is>
           <t>README §9.7</t>
         </is>
       </c>
-      <c r="M83" s="10" t="inlineStr">
+      <c r="N83" s="10" t="inlineStr">
         <is>
           <t>OP-501</t>
         </is>
       </c>
-      <c r="N83" s="20" t="inlineStr">
+      <c r="O83" s="20" t="inlineStr">
         <is>
           <t>10番 完了画面で確認する</t>
         </is>
       </c>
-      <c r="O83" s="13" t="inlineStr"/>
       <c r="P83" s="13" t="inlineStr"/>
       <c r="Q83" s="13" t="inlineStr"/>
       <c r="R83" s="13" t="inlineStr"/>
+      <c r="S83" s="13" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
@@ -5952,45 +6232,50 @@
           <t>取り込み完了後、トップに履歴が1件増える</t>
         </is>
       </c>
-      <c r="H84" s="10" t="inlineStr">
+      <c r="H84" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I84" s="10" t="inlineStr">
         <is>
           <t>いつ何を取り込んだか追えない</t>
         </is>
       </c>
-      <c r="I84" s="12" t="inlineStr">
+      <c r="J84" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J84" s="10" t="inlineStr">
+      <c r="K84" s="10" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K84" s="10" t="inlineStr">
+      <c r="L84" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L84" s="10" t="inlineStr">
+      <c r="M84" s="10" t="inlineStr">
         <is>
           <t>README §9.6</t>
         </is>
       </c>
-      <c r="M84" s="10" t="inlineStr">
+      <c r="N84" s="10" t="inlineStr">
         <is>
           <t>OP-501</t>
         </is>
       </c>
-      <c r="N84" s="20" t="inlineStr">
+      <c r="O84" s="20" t="inlineStr">
         <is>
           <t>10番 完了画面で確認する</t>
         </is>
       </c>
-      <c r="O84" s="13" t="inlineStr"/>
       <c r="P84" s="13" t="inlineStr"/>
       <c r="Q84" s="13" t="inlineStr"/>
       <c r="R84" s="13" t="inlineStr"/>
+      <c r="S84" s="13" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
@@ -6028,7 +6313,12 @@
           <t>①〜⑤の各列が対応する設定画面に反映されている（欠落した列＝0件）。②は5列、③は6列、④は8列、⑤は3列すべて</t>
         </is>
       </c>
-      <c r="H85" s="10" t="inlineStr">
+      <c r="H85" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I85" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6039,40 +6329,40 @@
           </r>
         </is>
       </c>
-      <c r="I85" s="12" t="inlineStr">
+      <c r="J85" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J85" s="10" t="inlineStr">
+      <c r="K85" s="10" t="inlineStr">
         <is>
           <t>業態設定 / 従業員一覧 / 管理者一覧</t>
         </is>
       </c>
-      <c r="K85" s="10" t="inlineStr">
+      <c r="L85" s="10" t="inlineStr">
         <is>
           <t>動作確認＋DB確認</t>
         </is>
       </c>
-      <c r="L85" s="10" t="inlineStr">
+      <c r="M85" s="10" t="inlineStr">
         <is>
           <t>README §4.4</t>
         </is>
       </c>
-      <c r="M85" s="10" t="inlineStr">
+      <c r="N85" s="10" t="inlineStr">
         <is>
           <t>OP-601 / OP-604 / OP-605 / OP-606</t>
         </is>
       </c>
-      <c r="N85" s="20" t="inlineStr">
+      <c r="O85" s="20" t="inlineStr">
         <is>
           <t>7番 従業員（列と入力内容） ／ 7番 従業員（従業員コードは空欄で自動採番） ／ 7番 管理者（管理者名・メールアドレス・担当店舗）</t>
         </is>
       </c>
-      <c r="O85" s="13" t="inlineStr"/>
       <c r="P85" s="13" t="inlineStr"/>
       <c r="Q85" s="13" t="inlineStr"/>
       <c r="R85" s="13" t="inlineStr"/>
+      <c r="S85" s="13" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
@@ -6110,7 +6400,12 @@
           <t>コード空欄5件 → 5件すべてに EMP- で始まるコードが付与され、重複＝0件</t>
         </is>
       </c>
-      <c r="H86" s="10" t="inlineStr">
+      <c r="H86" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I86" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6127,40 +6422,40 @@
           </r>
         </is>
       </c>
-      <c r="I86" s="12" t="inlineStr">
+      <c r="J86" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J86" s="10" t="inlineStr">
+      <c r="K86" s="10" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
-      <c r="K86" s="10" t="inlineStr">
+      <c r="L86" s="10" t="inlineStr">
         <is>
           <t>動作確認＋DB確認</t>
         </is>
       </c>
-      <c r="L86" s="10" t="inlineStr">
+      <c r="M86" s="10" t="inlineStr">
         <is>
           <t>README §8.1</t>
         </is>
       </c>
-      <c r="M86" s="10" t="inlineStr">
+      <c r="N86" s="10" t="inlineStr">
         <is>
           <t>OP-605 / CA-071</t>
         </is>
       </c>
-      <c r="N86" s="20" t="inlineStr">
+      <c r="O86" s="20" t="inlineStr">
         <is>
           <t>7番 従業員（従業員コードは空欄で自動採番）</t>
         </is>
       </c>
-      <c r="O86" s="13" t="inlineStr"/>
       <c r="P86" s="13" t="inlineStr"/>
       <c r="Q86" s="13" t="inlineStr"/>
       <c r="R86" s="13" t="inlineStr"/>
+      <c r="S86" s="13" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
@@ -6198,7 +6493,12 @@
           <t>OP-607（昇格時の勤務店舗維持）元の2店舗の所属が維持されている ／ CA-061（担当店舗のマージ）どちらも2店舗のまま。消えず、重複もしない</t>
         </is>
       </c>
-      <c r="H87" s="10" t="inlineStr">
+      <c r="H87" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I87" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6215,22 +6515,22 @@
           </r>
         </is>
       </c>
-      <c r="I87" s="12" t="inlineStr">
+      <c r="J87" s="12" t="inlineStr">
         <is>
           <t>2 / 4</t>
         </is>
       </c>
-      <c r="J87" s="10" t="inlineStr">
+      <c r="K87" s="10" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
-      <c r="K87" s="10" t="inlineStr">
+      <c r="L87" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L87" s="10" t="inlineStr">
+      <c r="M87" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6247,20 +6547,20 @@
           </r>
         </is>
       </c>
-      <c r="M87" s="10" t="inlineStr">
+      <c r="N87" s="10" t="inlineStr">
         <is>
           <t>OP-607 / CA-061</t>
         </is>
       </c>
-      <c r="N87" s="20" t="inlineStr">
+      <c r="O87" s="20" t="inlineStr">
         <is>
           <t>7番 管理者（勤務店舗は自動的に維持されます）</t>
         </is>
       </c>
-      <c r="O87" s="13" t="inlineStr"/>
       <c r="P87" s="13" t="inlineStr"/>
       <c r="Q87" s="13" t="inlineStr"/>
       <c r="R87" s="13" t="inlineStr"/>
+      <c r="S87" s="13" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
@@ -6298,45 +6598,50 @@
           <t>既存の所属が無い人を「渋谷店,新宿店」で登録 → 担当店舗＝2件</t>
         </is>
       </c>
-      <c r="H88" s="10" t="inlineStr">
+      <c r="H88" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I88" s="10" t="inlineStr">
         <is>
           <t>新規管理者に担当店舗が入らず、何も管理できない</t>
         </is>
       </c>
-      <c r="I88" s="12" t="inlineStr">
+      <c r="J88" s="12" t="inlineStr">
         <is>
           <t>2 / 4</t>
         </is>
       </c>
-      <c r="J88" s="10" t="inlineStr">
+      <c r="K88" s="10" t="inlineStr">
         <is>
           <t>管理者一覧</t>
         </is>
       </c>
-      <c r="K88" s="10" t="inlineStr">
+      <c r="L88" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L88" s="10" t="inlineStr">
+      <c r="M88" s="10" t="inlineStr">
         <is>
           <t>README §7.1</t>
         </is>
       </c>
-      <c r="M88" s="10" t="inlineStr">
+      <c r="N88" s="10" t="inlineStr">
         <is>
           <t>CA-062</t>
         </is>
       </c>
-      <c r="N88" s="20" t="inlineStr">
+      <c r="O88" s="20" t="inlineStr">
         <is>
           <t>7番 管理者（担当店舗は半角カンマ区切り）</t>
         </is>
       </c>
-      <c r="O88" s="13" t="inlineStr"/>
       <c r="P88" s="13" t="inlineStr"/>
       <c r="Q88" s="13" t="inlineStr"/>
       <c r="R88" s="13" t="inlineStr"/>
+      <c r="S88" s="13" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
@@ -6374,45 +6679,50 @@
           <t>既に渋谷店を持つ人を渋谷店で昇格 → 担当店舗＝2件のまま（重複＝0件）</t>
         </is>
       </c>
-      <c r="H89" s="10" t="inlineStr">
+      <c r="H89" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
         <is>
           <t>担当店舗が重複して増え続ける</t>
         </is>
       </c>
-      <c r="I89" s="12" t="inlineStr">
+      <c r="J89" s="12" t="inlineStr">
         <is>
           <t>2 / 4</t>
         </is>
       </c>
-      <c r="J89" s="10" t="inlineStr">
+      <c r="K89" s="10" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
-      <c r="K89" s="10" t="inlineStr">
+      <c r="L89" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L89" s="10" t="inlineStr">
+      <c r="M89" s="10" t="inlineStr">
         <is>
           <t>README §7.1</t>
         </is>
       </c>
-      <c r="M89" s="10" t="inlineStr">
+      <c r="N89" s="10" t="inlineStr">
         <is>
           <t>CA-061</t>
         </is>
       </c>
-      <c r="N89" s="20" t="inlineStr">
+      <c r="O89" s="20" t="inlineStr">
         <is>
           <t>7番 管理者（勤務店舗は自動的に維持されます）</t>
         </is>
       </c>
-      <c r="O89" s="13" t="inlineStr"/>
       <c r="P89" s="13" t="inlineStr"/>
       <c r="Q89" s="13" t="inlineStr"/>
       <c r="R89" s="13" t="inlineStr"/>
+      <c r="S89" s="13" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
@@ -6450,7 +6760,12 @@
           <t>コード指定した行は指定値のまま登録（書き換わった件数＝0件）</t>
         </is>
       </c>
-      <c r="H90" s="10" t="inlineStr">
+      <c r="H90" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I90" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6467,40 +6782,40 @@
           </r>
         </is>
       </c>
-      <c r="I90" s="12" t="inlineStr">
+      <c r="J90" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J90" s="10" t="inlineStr">
+      <c r="K90" s="10" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
-      <c r="K90" s="10" t="inlineStr">
+      <c r="L90" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L90" s="10" t="inlineStr">
+      <c r="M90" s="10" t="inlineStr">
         <is>
           <t>README §8.1</t>
         </is>
       </c>
-      <c r="M90" s="10" t="inlineStr">
+      <c r="N90" s="10" t="inlineStr">
         <is>
           <t>CA-071</t>
         </is>
       </c>
-      <c r="N90" s="20" t="inlineStr">
+      <c r="O90" s="20" t="inlineStr">
         <is>
           <t>7番 従業員（従業員コードは空欄で自動採番）</t>
         </is>
       </c>
-      <c r="O90" s="13" t="inlineStr"/>
       <c r="P90" s="13" t="inlineStr"/>
       <c r="Q90" s="13" t="inlineStr"/>
       <c r="R90" s="13" t="inlineStr"/>
+      <c r="S90" s="13" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
@@ -6538,7 +6853,12 @@
           <t>スキップで再取り込み後、既存レコードの変更件数＝0件</t>
         </is>
       </c>
-      <c r="H91" s="10" t="inlineStr">
+      <c r="H91" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I91" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6555,40 +6875,40 @@
           </r>
         </is>
       </c>
-      <c r="I91" s="16" t="inlineStr">
+      <c r="J91" s="16" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J91" s="10" t="inlineStr">
+      <c r="K91" s="10" t="inlineStr">
         <is>
           <t>プレビュー/完了</t>
         </is>
       </c>
-      <c r="K91" s="10" t="inlineStr">
+      <c r="L91" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L91" s="10" t="inlineStr">
+      <c r="M91" s="10" t="inlineStr">
         <is>
           <t>フローE／README §8.2</t>
         </is>
       </c>
-      <c r="M91" s="10" t="inlineStr">
+      <c r="N91" s="10" t="inlineStr">
         <is>
           <t>OP-701</t>
         </is>
       </c>
-      <c r="N91" s="20" t="inlineStr">
+      <c r="O91" s="20" t="inlineStr">
         <is>
           <t>8番 すでに登録されている内容の扱い（スキップ）</t>
         </is>
       </c>
-      <c r="O91" s="13" t="inlineStr"/>
       <c r="P91" s="13" t="inlineStr"/>
       <c r="Q91" s="13" t="inlineStr"/>
       <c r="R91" s="13" t="inlineStr"/>
+      <c r="S91" s="13" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
@@ -6626,7 +6946,12 @@
           <t>空欄にした列の変更件数＝0件（電話番号が元の値のまま）</t>
         </is>
       </c>
-      <c r="H92" s="10" t="inlineStr">
+      <c r="H92" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I92" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6643,22 +6968,22 @@
           </r>
         </is>
       </c>
-      <c r="I92" s="16" t="inlineStr">
+      <c r="J92" s="16" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J92" s="10" t="inlineStr">
+      <c r="K92" s="10" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
-      <c r="K92" s="10" t="inlineStr">
+      <c r="L92" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L92" s="10" t="inlineStr">
+      <c r="M92" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6675,20 +7000,20 @@
           </r>
         </is>
       </c>
-      <c r="M92" s="10" t="inlineStr">
+      <c r="N92" s="10" t="inlineStr">
         <is>
           <t>OP-703</t>
         </is>
       </c>
-      <c r="N92" s="20" t="inlineStr">
+      <c r="O92" s="20" t="inlineStr">
         <is>
           <t>8番 空欄にした項目は変更されません ／ 12番 入力済みの値を空にしたい</t>
         </is>
       </c>
-      <c r="O92" s="13" t="inlineStr"/>
       <c r="P92" s="13" t="inlineStr"/>
       <c r="Q92" s="13" t="inlineStr"/>
       <c r="R92" s="13" t="inlineStr"/>
+      <c r="S92" s="13" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
@@ -6726,45 +7051,50 @@
           <t>「重複時の処理」の設定にかかわらず5分岐で自動判定される</t>
         </is>
       </c>
-      <c r="H93" s="10" t="inlineStr">
+      <c r="H93" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I93" s="10" t="inlineStr">
         <is>
           <t>重複時の処理を「上書き」にすると、既存管理者の権限が壊れる</t>
         </is>
       </c>
-      <c r="I93" s="16" t="inlineStr">
+      <c r="J93" s="16" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J93" s="10" t="inlineStr">
+      <c r="K93" s="10" t="inlineStr">
         <is>
           <t>プレビュー</t>
         </is>
       </c>
-      <c r="K93" s="10" t="inlineStr">
+      <c r="L93" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L93" s="10" t="inlineStr">
+      <c r="M93" s="10" t="inlineStr">
         <is>
           <t>README §8.7</t>
         </is>
       </c>
-      <c r="M93" s="10" t="inlineStr">
+      <c r="N93" s="10" t="inlineStr">
         <is>
           <t>OP-704</t>
         </is>
       </c>
-      <c r="N93" s="20" t="inlineStr">
+      <c r="O93" s="20" t="inlineStr">
         <is>
           <t>8番 管理者の判定について（重複時の処理の設定によらない）</t>
         </is>
       </c>
-      <c r="O93" s="13" t="inlineStr"/>
       <c r="P93" s="13" t="inlineStr"/>
       <c r="Q93" s="13" t="inlineStr"/>
       <c r="R93" s="13" t="inlineStr"/>
+      <c r="S93" s="13" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
@@ -6802,7 +7132,12 @@
           <t>中断前にアップロードした①〜③の件数と内容が一致する。④以降は未アップロードのまま</t>
         </is>
       </c>
-      <c r="H94" s="10" t="inlineStr">
+      <c r="H94" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I94" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6819,40 +7154,40 @@
           </r>
         </is>
       </c>
-      <c r="I94" s="12" t="inlineStr">
+      <c r="J94" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J94" s="10" t="inlineStr">
+      <c r="K94" s="10" t="inlineStr">
         <is>
           <t>アップロード画面</t>
         </is>
       </c>
-      <c r="K94" s="10" t="inlineStr">
+      <c r="L94" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L94" s="10" t="inlineStr">
+      <c r="M94" s="10" t="inlineStr">
         <is>
           <t>フローG</t>
         </is>
       </c>
-      <c r="M94" s="10" t="inlineStr">
+      <c r="N94" s="10" t="inlineStr">
         <is>
           <t>OP-709</t>
         </is>
       </c>
-      <c r="N94" s="20" t="inlineStr">
+      <c r="O94" s="20" t="inlineStr">
         <is>
           <t>3番 途中でやめて、後日続ける（復元される範囲）</t>
         </is>
       </c>
-      <c r="O94" s="13" t="inlineStr"/>
       <c r="P94" s="13" t="inlineStr"/>
       <c r="Q94" s="13" t="inlineStr"/>
       <c r="R94" s="13" t="inlineStr"/>
+      <c r="S94" s="13" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
@@ -6890,7 +7225,12 @@
           <t>再開せず開始したとき、自動で入る中断分＝0件</t>
         </is>
       </c>
-      <c r="H95" s="10" t="inlineStr">
+      <c r="H95" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I95" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6907,40 +7247,40 @@
           </r>
         </is>
       </c>
-      <c r="I95" s="12" t="inlineStr">
+      <c r="J95" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J95" s="10" t="inlineStr">
+      <c r="K95" s="10" t="inlineStr">
         <is>
           <t>アップロード画面</t>
         </is>
       </c>
-      <c r="K95" s="10" t="inlineStr">
+      <c r="L95" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L95" s="10" t="inlineStr">
+      <c r="M95" s="10" t="inlineStr">
         <is>
           <t>フローG</t>
         </is>
       </c>
-      <c r="M95" s="10" t="inlineStr">
+      <c r="N95" s="10" t="inlineStr">
         <is>
           <t>OP-710</t>
         </is>
       </c>
-      <c r="N95" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O95" s="13" t="inlineStr"/>
+      <c r="O95" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="P95" s="13" t="inlineStr"/>
       <c r="Q95" s="13" t="inlineStr"/>
       <c r="R95" s="13" t="inlineStr"/>
+      <c r="S95" s="13" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
@@ -6978,45 +7318,50 @@
           <t>テンプレートに値を書いた列はすべて反映される（反映漏れ＝0件）。空欄の列は対象外（AC-063）。従業員コードは突合キーのため更新しない</t>
         </is>
       </c>
-      <c r="H96" s="10" t="inlineStr">
+      <c r="H96" s="20" t="inlineStr">
+        <is>
+          <t>—（上書き更新の対象列は AC-063 が判定する。前提ではない）</t>
+        </is>
+      </c>
+      <c r="I96" s="10" t="inlineStr">
         <is>
           <t>更新したはずの列が反映されず、顧客が気づかないまま古い値で運用される</t>
         </is>
       </c>
-      <c r="I96" s="16" t="inlineStr">
+      <c r="J96" s="16" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J96" s="10" t="inlineStr">
+      <c r="K96" s="10" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
-      <c r="K96" s="10" t="inlineStr">
+      <c r="L96" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L96" s="10" t="inlineStr">
+      <c r="M96" s="10" t="inlineStr">
         <is>
           <t>フローE</t>
         </is>
       </c>
-      <c r="M96" s="10" t="inlineStr">
+      <c r="N96" s="10" t="inlineStr">
         <is>
           <t>OP-702</t>
         </is>
       </c>
-      <c r="N96" s="20" t="inlineStr">
+      <c r="O96" s="20" t="inlineStr">
         <is>
           <t>8番 すでに登録されている内容の扱い（上書き更新・従業員のみ）</t>
         </is>
       </c>
-      <c r="O96" s="13" t="inlineStr"/>
       <c r="P96" s="13" t="inlineStr"/>
       <c r="Q96" s="13" t="inlineStr"/>
       <c r="R96" s="13" t="inlineStr"/>
+      <c r="S96" s="13" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
@@ -7054,45 +7399,50 @@
           <t>コード指定時はコードで突合（新規作成＝0件）。空欄時は名称で突合（新規作成＝0件）</t>
         </is>
       </c>
-      <c r="H97" s="10" t="inlineStr">
+      <c r="H97" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I97" s="10" t="inlineStr">
         <is>
           <t>突合キーを取り違え、別レコードが増える</t>
         </is>
       </c>
-      <c r="I97" s="16" t="inlineStr">
+      <c r="J97" s="16" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J97" s="10" t="inlineStr">
+      <c r="K97" s="10" t="inlineStr">
         <is>
           <t>雇用区分設定</t>
         </is>
       </c>
-      <c r="K97" s="10" t="inlineStr">
+      <c r="L97" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L97" s="10" t="inlineStr">
+      <c r="M97" s="10" t="inlineStr">
         <is>
           <t>README §8.6</t>
         </is>
       </c>
-      <c r="M97" s="10" t="inlineStr">
+      <c r="N97" s="10" t="inlineStr">
         <is>
           <t>OP-705</t>
         </is>
       </c>
-      <c r="N97" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O97" s="13" t="inlineStr"/>
+      <c r="O97" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="P97" s="13" t="inlineStr"/>
       <c r="Q97" s="13" t="inlineStr"/>
       <c r="R97" s="13" t="inlineStr"/>
+      <c r="S97" s="13" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
@@ -7130,45 +7480,50 @@
           <t>中断地点が保存され、再開すると①〜③はアップロード済みとして復元される。1件も投入していない状態では一時保存を押せない</t>
         </is>
       </c>
-      <c r="H98" s="10" t="inlineStr">
+      <c r="H98" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I98" s="10" t="inlineStr">
         <is>
           <t>5種類を1日で揃えられない顧客が最初からやり直しになる</t>
         </is>
       </c>
-      <c r="I98" s="12" t="inlineStr">
+      <c r="J98" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J98" s="10" t="inlineStr">
+      <c r="K98" s="10" t="inlineStr">
         <is>
           <t>アップロード</t>
         </is>
       </c>
-      <c r="K98" s="10" t="inlineStr">
+      <c r="L98" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L98" s="10" t="inlineStr">
+      <c r="M98" s="10" t="inlineStr">
         <is>
           <t>フローG</t>
         </is>
       </c>
-      <c r="M98" s="10" t="inlineStr">
+      <c r="N98" s="10" t="inlineStr">
         <is>
           <t>OP-707</t>
         </is>
       </c>
-      <c r="N98" s="20" t="inlineStr">
+      <c r="O98" s="20" t="inlineStr">
         <is>
           <t>3番 途中でやめて、後日続ける（一時保存して中断・続きから再開）</t>
         </is>
       </c>
-      <c r="O98" s="13" t="inlineStr"/>
       <c r="P98" s="13" t="inlineStr"/>
       <c r="Q98" s="13" t="inlineStr"/>
       <c r="R98" s="13" t="inlineStr"/>
+      <c r="S98" s="13" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
@@ -7206,7 +7561,12 @@
           <t>値の削除・担当店舗変更・退職者の復帰の3操作すべてが実行できる（実行できない操作＝0件）</t>
         </is>
       </c>
-      <c r="H99" s="10" t="inlineStr">
+      <c r="H99" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I99" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7223,40 +7583,40 @@
           </r>
         </is>
       </c>
-      <c r="I99" s="18" t="inlineStr">
+      <c r="J99" s="18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J99" s="10" t="inlineStr">
+      <c r="K99" s="10" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
-      <c r="K99" s="10" t="inlineStr">
+      <c r="L99" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L99" s="10" t="inlineStr">
+      <c r="M99" s="10" t="inlineStr">
         <is>
           <t>仕様書「インポート単体では成立しない仕様」</t>
         </is>
       </c>
-      <c r="M99" s="10" t="inlineStr">
+      <c r="N99" s="10" t="inlineStr">
         <is>
           <t>OP-609</t>
         </is>
       </c>
-      <c r="N99" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O99" s="13" t="inlineStr"/>
+      <c r="O99" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="P99" s="13" t="inlineStr"/>
       <c r="Q99" s="13" t="inlineStr"/>
       <c r="R99" s="13" t="inlineStr"/>
+      <c r="S99" s="13" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
@@ -7294,7 +7654,12 @@
           <t>編集・削除の2操作とも実行できる（実行できない操作＝0件）</t>
         </is>
       </c>
-      <c r="H100" s="10" t="inlineStr">
+      <c r="H100" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I100" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7311,40 +7676,40 @@
           </r>
         </is>
       </c>
-      <c r="I100" s="18" t="inlineStr">
+      <c r="J100" s="18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J100" s="10" t="inlineStr">
+      <c r="K100" s="10" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
-      <c r="K100" s="10" t="inlineStr">
+      <c r="L100" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L100" s="10" t="inlineStr">
+      <c r="M100" s="10" t="inlineStr">
         <is>
           <t>仕様書「操作ごとの対応」</t>
         </is>
       </c>
-      <c r="M100" s="10" t="inlineStr">
+      <c r="N100" s="10" t="inlineStr">
         <is>
           <t>OP-615</t>
         </is>
       </c>
-      <c r="N100" s="20" t="inlineStr">
+      <c r="O100" s="20" t="inlineStr">
         <is>
           <t>4番 登録した内容を直す・消す</t>
         </is>
       </c>
-      <c r="O100" s="13" t="inlineStr"/>
       <c r="P100" s="13" t="inlineStr"/>
       <c r="Q100" s="13" t="inlineStr"/>
       <c r="R100" s="13" t="inlineStr"/>
+      <c r="S100" s="13" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
@@ -7382,7 +7747,12 @@
           <t>従業員・業態・店舗・雇用区分の4種とも削除できる（削除後の一覧に残る件数＝0件）</t>
         </is>
       </c>
-      <c r="H101" s="10" t="inlineStr">
+      <c r="H101" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I101" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7399,40 +7769,40 @@
           </r>
         </is>
       </c>
-      <c r="I101" s="18" t="inlineStr">
+      <c r="J101" s="18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J101" s="10" t="inlineStr">
+      <c r="K101" s="10" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
-      <c r="K101" s="10" t="inlineStr">
+      <c r="L101" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L101" s="10" t="inlineStr">
+      <c r="M101" s="10" t="inlineStr">
         <is>
           <t>仕様書「削除について」</t>
         </is>
       </c>
-      <c r="M101" s="10" t="inlineStr">
+      <c r="N101" s="10" t="inlineStr">
         <is>
           <t>OP-615</t>
         </is>
       </c>
-      <c r="N101" s="20" t="inlineStr">
+      <c r="O101" s="20" t="inlineStr">
         <is>
           <t>4番 登録した内容を直す・消す</t>
         </is>
       </c>
-      <c r="O101" s="13" t="inlineStr"/>
       <c r="P101" s="13" t="inlineStr"/>
       <c r="Q101" s="13" t="inlineStr"/>
       <c r="R101" s="13" t="inlineStr"/>
+      <c r="S101" s="13" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
@@ -7470,7 +7840,12 @@
           <t>店長で①業態・②店舗・③雇用区分が表示されない（表示された種別＝0件）。④⑤のみ表示される</t>
         </is>
       </c>
-      <c r="H102" s="10" t="inlineStr">
+      <c r="H102" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I102" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7487,40 +7862,40 @@
           </r>
         </is>
       </c>
-      <c r="I102" s="12" t="inlineStr">
+      <c r="J102" s="12" t="inlineStr">
         <is>
           <t>2 / 4</t>
         </is>
       </c>
-      <c r="J102" s="10" t="inlineStr">
+      <c r="K102" s="10" t="inlineStr">
         <is>
           <t>インポート</t>
         </is>
       </c>
-      <c r="K102" s="10" t="inlineStr">
+      <c r="L102" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L102" s="10" t="inlineStr">
+      <c r="M102" s="10" t="inlineStr">
         <is>
           <t>フローF</t>
         </is>
       </c>
-      <c r="M102" s="10" t="inlineStr">
+      <c r="N102" s="10" t="inlineStr">
         <is>
           <t>OP-801</t>
         </is>
       </c>
-      <c r="N102" s="20" t="inlineStr">
+      <c r="O102" s="20" t="inlineStr">
         <is>
           <t>13番 権限による違い</t>
         </is>
       </c>
-      <c r="O102" s="13" t="inlineStr"/>
       <c r="P102" s="13" t="inlineStr"/>
       <c r="Q102" s="13" t="inlineStr"/>
       <c r="R102" s="13" t="inlineStr"/>
+      <c r="S102" s="13" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
@@ -7558,7 +7933,12 @@
           <t>担当外の店舗を含む行＝エラー。取り込まれた件数＝0件</t>
         </is>
       </c>
-      <c r="H103" s="10" t="inlineStr">
+      <c r="H103" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I103" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7575,40 +7955,40 @@
           </r>
         </is>
       </c>
-      <c r="I103" s="12" t="inlineStr">
+      <c r="J103" s="12" t="inlineStr">
         <is>
           <t>2 / 4</t>
         </is>
       </c>
-      <c r="J103" s="10" t="inlineStr">
+      <c r="K103" s="10" t="inlineStr">
         <is>
           <t>プレビュー</t>
         </is>
       </c>
-      <c r="K103" s="10" t="inlineStr">
+      <c r="L103" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L103" s="10" t="inlineStr">
+      <c r="M103" s="10" t="inlineStr">
         <is>
           <t>フローF</t>
         </is>
       </c>
-      <c r="M103" s="10" t="inlineStr">
+      <c r="N103" s="10" t="inlineStr">
         <is>
           <t>OP-803</t>
         </is>
       </c>
-      <c r="N103" s="20" t="inlineStr">
+      <c r="O103" s="20" t="inlineStr">
         <is>
           <t>13番 担当店舗以外の店舗名が入った行はエラーになります</t>
         </is>
       </c>
-      <c r="O103" s="13" t="inlineStr"/>
       <c r="P103" s="13" t="inlineStr"/>
       <c r="Q103" s="13" t="inlineStr"/>
       <c r="R103" s="13" t="inlineStr"/>
+      <c r="S103" s="13" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
@@ -7646,7 +8026,12 @@
           <t>全行に[編集][削除]がある（無い行＝0件）。削除は確認ダイアログの後に消える</t>
         </is>
       </c>
-      <c r="H104" s="10" t="inlineStr">
+      <c r="H104" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I104" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7663,40 +8048,40 @@
           </r>
         </is>
       </c>
-      <c r="I104" s="18" t="inlineStr">
+      <c r="J104" s="18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J104" s="10" t="inlineStr">
+      <c r="K104" s="10" t="inlineStr">
         <is>
           <t>各設定画面</t>
         </is>
       </c>
-      <c r="K104" s="10" t="inlineStr">
+      <c r="L104" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L104" s="10" t="inlineStr">
+      <c r="M104" s="10" t="inlineStr">
         <is>
           <t>owner-mock §3.3.1</t>
         </is>
       </c>
-      <c r="M104" s="10" t="inlineStr">
+      <c r="N104" s="10" t="inlineStr">
         <is>
           <t>OP-028</t>
         </is>
       </c>
-      <c r="N104" s="20" t="inlineStr">
+      <c r="O104" s="20" t="inlineStr">
         <is>
           <t>4番 登録した内容を直す・消す</t>
         </is>
       </c>
-      <c r="O104" s="13" t="inlineStr"/>
       <c r="P104" s="13" t="inlineStr"/>
       <c r="Q104" s="13" t="inlineStr"/>
       <c r="R104" s="13" t="inlineStr"/>
+      <c r="S104" s="13" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
@@ -7734,7 +8119,12 @@
           <t>運用更新画面の「+ 追加」から登録でき、一覧に反映される（登録できない種別＝0件）</t>
         </is>
       </c>
-      <c r="H105" s="10" t="inlineStr">
+      <c r="H105" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I105" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7751,40 +8141,40 @@
           </r>
         </is>
       </c>
-      <c r="I105" s="18" t="inlineStr">
+      <c r="J105" s="18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J105" s="10" t="inlineStr">
+      <c r="K105" s="10" t="inlineStr">
         <is>
           <t>各設定画面（運用）</t>
         </is>
       </c>
-      <c r="K105" s="10" t="inlineStr">
+      <c r="L105" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L105" s="10" t="inlineStr">
+      <c r="M105" s="10" t="inlineStr">
         <is>
           <t>owner-mock §3.3.1／仕様書「ケース別の遷移フロー（手入力）」</t>
         </is>
       </c>
-      <c r="M105" s="10" t="inlineStr">
+      <c r="N105" s="10" t="inlineStr">
         <is>
           <t>OP-029</t>
         </is>
       </c>
-      <c r="N105" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O105" s="13" t="inlineStr"/>
+      <c r="O105" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="P105" s="13" t="inlineStr"/>
       <c r="Q105" s="13" t="inlineStr"/>
       <c r="R105" s="13" t="inlineStr"/>
+      <c r="S105" s="13" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
@@ -7822,45 +8212,50 @@
           <t>手入力の登録モーダルとCSVテンプレートで入力項目が一致する</t>
         </is>
       </c>
-      <c r="H106" s="10" t="inlineStr">
+      <c r="H106" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I106" s="10" t="inlineStr">
         <is>
           <t>経路によって項目が欠落し、データが揃わない</t>
         </is>
       </c>
-      <c r="I106" s="14" t="inlineStr">
+      <c r="J106" s="14" t="inlineStr">
         <is>
           <t>1 / 3</t>
         </is>
       </c>
-      <c r="J106" s="10" t="inlineStr">
+      <c r="K106" s="10" t="inlineStr">
         <is>
           <t>各設定画面</t>
         </is>
       </c>
-      <c r="K106" s="10" t="inlineStr">
+      <c r="L106" s="10" t="inlineStr">
         <is>
           <t>実装レビュー（登録モーダルとテンプレートの項目突合）</t>
         </is>
       </c>
-      <c r="L106" s="10" t="inlineStr">
+      <c r="M106" s="10" t="inlineStr">
         <is>
           <t>owner-mock §3.4.1</t>
         </is>
       </c>
-      <c r="M106" s="10" t="inlineStr">
+      <c r="N106" s="10" t="inlineStr">
         <is>
           <t>OP-612</t>
         </is>
       </c>
-      <c r="N106" s="20" t="inlineStr">
+      <c r="O106" s="20" t="inlineStr">
         <is>
           <t>4番 入力する項目はCSVテンプレートと同じです</t>
         </is>
       </c>
-      <c r="O106" s="13" t="inlineStr"/>
       <c r="P106" s="13" t="inlineStr"/>
       <c r="Q106" s="13" t="inlineStr"/>
       <c r="R106" s="13" t="inlineStr"/>
+      <c r="S106" s="13" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
@@ -7898,45 +8293,50 @@
           <t>削除した対象を再取り込み → 判定が「新規登録」（エラー・スキップ＝0件）</t>
         </is>
       </c>
-      <c r="H107" s="10" t="inlineStr">
+      <c r="H107" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I107" s="10" t="inlineStr">
         <is>
           <t>削除の残骸が残り、再取り込みできない</t>
         </is>
       </c>
-      <c r="I107" s="18" t="inlineStr">
+      <c r="J107" s="18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J107" s="10" t="inlineStr">
+      <c r="K107" s="10" t="inlineStr">
         <is>
           <t>プレビュー／従業員一覧</t>
         </is>
       </c>
-      <c r="K107" s="10" t="inlineStr">
+      <c r="L107" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L107" s="10" t="inlineStr">
+      <c r="M107" s="10" t="inlineStr">
         <is>
           <t>仕様書「削除について」</t>
         </is>
       </c>
-      <c r="M107" s="10" t="inlineStr">
+      <c r="N107" s="10" t="inlineStr">
         <is>
           <t>OP-617</t>
         </is>
       </c>
-      <c r="N107" s="20" t="inlineStr">
+      <c r="O107" s="20" t="inlineStr">
         <is>
           <t>12番 登録した内容を削除したい（削除後の再取り込み）</t>
         </is>
       </c>
-      <c r="O107" s="13" t="inlineStr"/>
       <c r="P107" s="13" t="inlineStr"/>
       <c r="Q107" s="13" t="inlineStr"/>
       <c r="R107" s="13" t="inlineStr"/>
+      <c r="S107" s="13" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
@@ -7974,45 +8374,50 @@
           <t>戻った先の一覧に取り込んだ件数が反映されている（反映漏れ＝0件）</t>
         </is>
       </c>
-      <c r="H108" s="10" t="inlineStr">
+      <c r="H108" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I108" s="10" t="inlineStr">
         <is>
           <t>取り込めたのに一覧が古く、失敗したと誤解する</t>
         </is>
       </c>
-      <c r="I108" s="16" t="inlineStr">
+      <c r="J108" s="16" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J108" s="10" t="inlineStr">
+      <c r="K108" s="10" t="inlineStr">
         <is>
           <t>完了画面</t>
         </is>
       </c>
-      <c r="K108" s="10" t="inlineStr">
+      <c r="L108" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L108" s="10" t="inlineStr">
+      <c r="M108" s="10" t="inlineStr">
         <is>
           <t>仕様書「連携要件C」</t>
         </is>
       </c>
-      <c r="M108" s="10" t="inlineStr">
+      <c r="N108" s="10" t="inlineStr">
         <is>
           <t>OP-009</t>
         </is>
       </c>
-      <c r="N108" s="20" t="inlineStr">
+      <c r="O108" s="20" t="inlineStr">
         <is>
           <t>5番 終わったあとは、入ってきた画面に戻ります</t>
         </is>
       </c>
-      <c r="O108" s="13" t="inlineStr"/>
       <c r="P108" s="13" t="inlineStr"/>
       <c r="Q108" s="13" t="inlineStr"/>
       <c r="R108" s="13" t="inlineStr"/>
+      <c r="S108" s="13" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
@@ -8050,45 +8455,50 @@
           <t>オーナーで①〜⑤の5種別すべてが表示され、取り込める（表示されない種別＝0件）</t>
         </is>
       </c>
-      <c r="H109" s="10" t="inlineStr">
+      <c r="H109" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I109" s="10" t="inlineStr">
         <is>
           <t>オーナーが必要な種別を取り込めない</t>
         </is>
       </c>
-      <c r="I109" s="12" t="inlineStr">
+      <c r="J109" s="12" t="inlineStr">
         <is>
           <t>2 / 4</t>
         </is>
       </c>
-      <c r="J109" s="10" t="inlineStr">
+      <c r="K109" s="10" t="inlineStr">
         <is>
           <t>インポート</t>
         </is>
       </c>
-      <c r="K109" s="10" t="inlineStr">
+      <c r="L109" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L109" s="10" t="inlineStr">
+      <c r="M109" s="10" t="inlineStr">
         <is>
           <t>フローF</t>
         </is>
       </c>
-      <c r="M109" s="10" t="inlineStr">
+      <c r="N109" s="10" t="inlineStr">
         <is>
           <t>OP-801</t>
         </is>
       </c>
-      <c r="N109" s="20" t="inlineStr">
+      <c r="O109" s="20" t="inlineStr">
         <is>
           <t>13番 権限による違い</t>
         </is>
       </c>
-      <c r="O109" s="13" t="inlineStr"/>
       <c r="P109" s="13" t="inlineStr"/>
       <c r="Q109" s="13" t="inlineStr"/>
       <c r="R109" s="13" t="inlineStr"/>
+      <c r="S109" s="13" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
@@ -8126,45 +8536,50 @@
           <t>担当店舗のみのファイル → 全行が登録される（エラー＝0件）</t>
         </is>
       </c>
-      <c r="H110" s="10" t="inlineStr">
+      <c r="H110" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I110" s="10" t="inlineStr">
         <is>
           <t>店長が自店舗の従業員すら登録できず、機能が使えない</t>
         </is>
       </c>
-      <c r="I110" s="12" t="inlineStr">
+      <c r="J110" s="12" t="inlineStr">
         <is>
           <t>2 / 4</t>
         </is>
       </c>
-      <c r="J110" s="10" t="inlineStr">
+      <c r="K110" s="10" t="inlineStr">
         <is>
           <t>プレビュー／従業員一覧</t>
         </is>
       </c>
-      <c r="K110" s="10" t="inlineStr">
+      <c r="L110" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L110" s="10" t="inlineStr">
+      <c r="M110" s="10" t="inlineStr">
         <is>
           <t>フローF</t>
         </is>
       </c>
-      <c r="M110" s="10" t="inlineStr">
+      <c r="N110" s="10" t="inlineStr">
         <is>
           <t>OP-804</t>
         </is>
       </c>
-      <c r="N110" s="20" t="inlineStr">
+      <c r="O110" s="20" t="inlineStr">
         <is>
           <t>13番 権限による違い（従業員は担当店舗のみ）</t>
         </is>
       </c>
-      <c r="O110" s="13" t="inlineStr"/>
       <c r="P110" s="13" t="inlineStr"/>
       <c r="Q110" s="13" t="inlineStr"/>
       <c r="R110" s="13" t="inlineStr"/>
+      <c r="S110" s="13" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
@@ -8202,45 +8617,50 @@
           <t>手入力の登録モーダルから登録できる（登録できない種別＝0件）。項目が一致するかは AC-058 で判定する</t>
         </is>
       </c>
-      <c r="H111" s="10" t="inlineStr">
+      <c r="H111" s="20" t="inlineStr">
+        <is>
+          <t>—（項目の一致は AC-058 が判定する。前提ではない）</t>
+        </is>
+      </c>
+      <c r="I111" s="10" t="inlineStr">
         <is>
           <t>手入力とインポートで作れるデータが違ってしまう</t>
         </is>
       </c>
-      <c r="I111" s="14" t="inlineStr">
+      <c r="J111" s="14" t="inlineStr">
         <is>
           <t>1 / 3</t>
         </is>
       </c>
-      <c r="J111" s="10" t="inlineStr">
+      <c r="K111" s="10" t="inlineStr">
         <is>
           <t>各設定画面</t>
         </is>
       </c>
-      <c r="K111" s="10" t="inlineStr">
+      <c r="L111" s="10" t="inlineStr">
         <is>
           <t>動作確認（検証プラン）</t>
         </is>
       </c>
-      <c r="L111" s="10" t="inlineStr">
+      <c r="M111" s="10" t="inlineStr">
         <is>
           <t>owner-mock §3.4.1</t>
         </is>
       </c>
-      <c r="M111" s="10" t="inlineStr">
+      <c r="N111" s="10" t="inlineStr">
         <is>
           <t>OP-612</t>
         </is>
       </c>
-      <c r="N111" s="20" t="inlineStr">
+      <c r="O111" s="20" t="inlineStr">
         <is>
           <t>4番 入力する項目はCSVテンプレートと同じです</t>
         </is>
       </c>
-      <c r="O111" s="13" t="inlineStr"/>
       <c r="P111" s="13" t="inlineStr"/>
       <c r="Q111" s="13" t="inlineStr"/>
       <c r="R111" s="13" t="inlineStr"/>
+      <c r="S111" s="13" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
@@ -8278,45 +8698,50 @@
           <t>Stagingにオーナーでログインでき、業態・店舗・雇用区分・従業員・管理者すべて0件。取り込み方式＝テンプレート</t>
         </is>
       </c>
-      <c r="H112" s="10" t="inlineStr">
+      <c r="H112" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I112" s="10" t="inlineStr">
         <is>
           <t>本番に接続する／既存データが混ざり判定が読めない</t>
         </is>
       </c>
-      <c r="I112" s="12" t="inlineStr">
+      <c r="J112" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J112" s="10" t="inlineStr">
+      <c r="K112" s="10" t="inlineStr">
         <is>
           <t>ログイン</t>
         </is>
       </c>
-      <c r="K112" s="10" t="inlineStr">
+      <c r="L112" s="10" t="inlineStr">
         <is>
           <t>実装レビュー（検証の前提）</t>
         </is>
       </c>
-      <c r="L112" s="10" t="inlineStr">
+      <c r="M112" s="10" t="inlineStr">
         <is>
           <t>仕様書 8.1</t>
         </is>
       </c>
-      <c r="M112" s="10" t="inlineStr">
+      <c r="N112" s="10" t="inlineStr">
         <is>
           <t>OP-001</t>
         </is>
       </c>
-      <c r="N112" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O112" s="13" t="inlineStr"/>
+      <c r="O112" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="P112" s="13" t="inlineStr"/>
       <c r="Q112" s="13" t="inlineStr"/>
       <c r="R112" s="13" t="inlineStr"/>
+      <c r="S112" s="13" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
@@ -8354,45 +8779,50 @@
           <t>P1〜P6を0件の状態、P7以降を既登録ありの状態で実施する（モードを取り違えた検証＝0件）</t>
         </is>
       </c>
-      <c r="H113" s="10" t="inlineStr">
+      <c r="H113" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I113" s="10" t="inlineStr">
         <is>
           <t>5分岐や重複時の処理が発生せず、検証にならない</t>
         </is>
       </c>
-      <c r="I113" s="12" t="inlineStr">
+      <c r="J113" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J113" s="10" t="inlineStr">
+      <c r="K113" s="10" t="inlineStr">
         <is>
           <t>ログイン</t>
         </is>
       </c>
-      <c r="K113" s="10" t="inlineStr">
+      <c r="L113" s="10" t="inlineStr">
         <is>
           <t>実装レビュー（検証の前提）</t>
         </is>
       </c>
-      <c r="L113" s="10" t="inlineStr">
+      <c r="M113" s="10" t="inlineStr">
         <is>
           <t>仕様書「新規登録と運用更新の違い」</t>
         </is>
       </c>
-      <c r="M113" s="10" t="inlineStr">
+      <c r="N113" s="10" t="inlineStr">
         <is>
           <t>OP-001</t>
         </is>
       </c>
-      <c r="N113" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O113" s="13" t="inlineStr"/>
+      <c r="O113" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="P113" s="13" t="inlineStr"/>
       <c r="Q113" s="13" t="inlineStr"/>
       <c r="R113" s="13" t="inlineStr"/>
+      <c r="S113" s="13" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
@@ -8430,45 +8860,50 @@
           <t>テンプレート側の画面が操作でき、外部勤怠側19画面に凍結バナーが出る</t>
         </is>
       </c>
-      <c r="H114" s="10" t="inlineStr">
+      <c r="H114" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I114" s="10" t="inlineStr">
         <is>
           <t>期待動作の基準が無く、合否を判断できない</t>
         </is>
       </c>
-      <c r="I114" s="12" t="inlineStr">
+      <c r="J114" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J114" s="10" t="inlineStr">
+      <c r="K114" s="10" t="inlineStr">
         <is>
           <t>モック（公開URL）</t>
         </is>
       </c>
-      <c r="K114" s="10" t="inlineStr">
+      <c r="L114" s="10" t="inlineStr">
         <is>
           <t>実装レビュー（モック）</t>
         </is>
       </c>
-      <c r="L114" s="10" t="inlineStr">
+      <c r="M114" s="10" t="inlineStr">
         <is>
           <t>モック</t>
         </is>
       </c>
-      <c r="M114" s="10" t="inlineStr">
+      <c r="N114" s="10" t="inlineStr">
         <is>
           <t>OP-007</t>
         </is>
       </c>
-      <c r="N114" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O114" s="13" t="inlineStr"/>
+      <c r="O114" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="P114" s="13" t="inlineStr"/>
       <c r="Q114" s="13" t="inlineStr"/>
       <c r="R114" s="13" t="inlineStr"/>
+      <c r="S114" s="13" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
@@ -8506,45 +8941,50 @@
           <t>外部勤怠サービスインポートの画面に凍結の案内が出る（実装対象として案内された箇所＝0件）</t>
         </is>
       </c>
-      <c r="H115" s="10" t="inlineStr">
+      <c r="H115" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I115" s="10" t="inlineStr">
         <is>
           <t>凍結中の機能を実装対象と誤解する</t>
         </is>
       </c>
-      <c r="I115" s="12" t="inlineStr">
+      <c r="J115" s="12" t="inlineStr">
         <is>
           <t>2 / 4</t>
         </is>
       </c>
-      <c r="J115" s="10" t="inlineStr">
+      <c r="K115" s="10" t="inlineStr">
         <is>
           <t>インポートのトップ</t>
         </is>
       </c>
-      <c r="K115" s="10" t="inlineStr">
+      <c r="L115" s="10" t="inlineStr">
         <is>
           <t>実装レビュー（対象外の確認）</t>
         </is>
       </c>
-      <c r="L115" s="10" t="inlineStr">
+      <c r="M115" s="10" t="inlineStr">
         <is>
           <t>README §2（凍結）</t>
         </is>
       </c>
-      <c r="M115" s="10" t="inlineStr">
+      <c r="N115" s="10" t="inlineStr">
         <is>
           <t>OP-901</t>
         </is>
       </c>
-      <c r="N115" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O115" s="13" t="inlineStr"/>
+      <c r="O115" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="P115" s="13" t="inlineStr"/>
       <c r="Q115" s="13" t="inlineStr"/>
       <c r="R115" s="13" t="inlineStr"/>
+      <c r="S115" s="13" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
@@ -8582,48 +9022,53 @@
           <t>補完用テンプレート取込とプレビューのデフォルト値設定が、実装対象として案内されない（案内された箇所＝0件）</t>
         </is>
       </c>
-      <c r="H116" s="10" t="inlineStr">
+      <c r="H116" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I116" s="10" t="inlineStr">
         <is>
           <t>外部勤怠専用の機能を実装対象と誤解する</t>
         </is>
       </c>
-      <c r="I116" s="12" t="inlineStr">
+      <c r="J116" s="12" t="inlineStr">
         <is>
           <t>2 / 4</t>
         </is>
       </c>
-      <c r="J116" s="10" t="inlineStr">
+      <c r="K116" s="10" t="inlineStr">
         <is>
           <t>補完テンプレート／プレビュー</t>
         </is>
       </c>
-      <c r="K116" s="10" t="inlineStr">
+      <c r="L116" s="10" t="inlineStr">
         <is>
           <t>実装レビュー（対象外の確認）</t>
         </is>
       </c>
-      <c r="L116" s="10" t="inlineStr">
+      <c r="M116" s="10" t="inlineStr">
         <is>
           <t>README §2（凍結）</t>
         </is>
       </c>
-      <c r="M116" s="10" t="inlineStr">
+      <c r="N116" s="10" t="inlineStr">
         <is>
           <t>OP-901</t>
         </is>
       </c>
-      <c r="N116" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O116" s="13" t="inlineStr"/>
+      <c r="O116" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="P116" s="13" t="inlineStr"/>
       <c r="Q116" s="13" t="inlineStr"/>
       <c r="R116" s="13" t="inlineStr"/>
+      <c r="S116" s="13" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A28:R116"/>
+  <autoFilter ref="A28:S116"/>
   <conditionalFormatting sqref="N29:N116">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
@@ -8783,7 +9228,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="O29:O116" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P29:P116" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/excel/20260805_タイムレコード_01_受入条件表.xlsx
+++ b/excel/20260805_タイムレコード_01_受入条件表.xlsx
@@ -8933,7 +8933,7 @@
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>外部勤怠サービスインポートは対象外</t>
+          <t>外部勤怠サービスインポートは凍結（2026-07-31 確定）で対象外</t>
         </is>
       </c>
       <c r="G115" s="10" t="inlineStr">
@@ -8948,7 +8948,19 @@
       </c>
       <c r="I115" s="10" t="inlineStr">
         <is>
-          <t>凍結中の機能を実装対象と誤解する</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>凍結した機能を実装対象と誤解する。</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 2026-07-31 に凍結を確定済み</t>
+          </r>
         </is>
       </c>
       <c r="J115" s="12" t="inlineStr">
@@ -9014,7 +9026,7 @@
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>補完テンプレート・デフォルト値設定は対象外</t>
+          <t>補完テンプレート・デフォルト値設定は凍結に付随し対象外</t>
         </is>
       </c>
       <c r="G116" s="10" t="inlineStr">
@@ -9029,7 +9041,13 @@
       </c>
       <c r="I116" s="10" t="inlineStr">
         <is>
-          <t>外部勤怠専用の機能を実装対象と誤解する</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>凍結した外部勤怠専用の機能を実装対象と誤解する</t>
+          </r>
         </is>
       </c>
       <c r="J116" s="12" t="inlineStr">
